--- a/AAII_Financials/Yearly/UMC_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/UMC_YR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Yearly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Yearly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
@@ -656,195 +656,207 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>44926</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44561</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44196</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>43830</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43465</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43100</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>42735</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42369</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42004</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>41639</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41274</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>40908</v>
       </c>
-      <c r="P7" s="2"/>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q7" s="2"/>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>8737400</v>
+        <v>7052100</v>
       </c>
       <c r="E8" s="3">
-        <v>6677900</v>
+        <v>8832200</v>
       </c>
       <c r="F8" s="3">
-        <v>5543300</v>
+        <v>6750300</v>
       </c>
       <c r="G8" s="3">
-        <v>4646100</v>
+        <v>5603500</v>
       </c>
       <c r="H8" s="3">
-        <v>4741800</v>
+        <v>4696500</v>
       </c>
       <c r="I8" s="3">
-        <v>4680100</v>
+        <v>4793200</v>
       </c>
       <c r="J8" s="3">
+        <v>4730800</v>
+      </c>
+      <c r="K8" s="3">
         <v>4635700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>4617200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>5043200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>4343300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>3847300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>3805700</v>
       </c>
-      <c r="P8" s="3"/>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q8" s="3"/>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>4794700</v>
+        <v>4588400</v>
       </c>
       <c r="E9" s="3">
-        <v>4419100</v>
+        <v>4846700</v>
       </c>
       <c r="F9" s="3">
-        <v>4320800</v>
+        <v>4467100</v>
       </c>
       <c r="G9" s="3">
-        <v>3977900</v>
+        <v>4367600</v>
       </c>
       <c r="H9" s="3">
-        <v>4025700</v>
+        <v>4021000</v>
       </c>
       <c r="I9" s="3">
-        <v>3831800</v>
+        <v>4069400</v>
       </c>
       <c r="J9" s="3">
+        <v>3873400</v>
+      </c>
+      <c r="K9" s="3">
         <v>3683300</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>3604400</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>3895900</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>3516700</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>6406800</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>3111500</v>
       </c>
-      <c r="P9" s="3"/>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3"/>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>3942700</v>
+        <v>2463700</v>
       </c>
       <c r="E10" s="3">
-        <v>2258800</v>
+        <v>3985500</v>
       </c>
       <c r="F10" s="3">
-        <v>1222600</v>
+        <v>2283300</v>
       </c>
       <c r="G10" s="3">
-        <v>668200</v>
+        <v>1235800</v>
       </c>
       <c r="H10" s="3">
-        <v>716000</v>
+        <v>675500</v>
       </c>
       <c r="I10" s="3">
-        <v>848300</v>
+        <v>723800</v>
       </c>
       <c r="J10" s="3">
+        <v>857500</v>
+      </c>
+      <c r="K10" s="3">
         <v>952400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1012800</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1147300</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>826600</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>-2559500</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>694100</v>
       </c>
-      <c r="P10" s="3"/>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3"/>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -861,50 +873,54 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
-        <v>406100</v>
+        <v>421000</v>
       </c>
       <c r="E12" s="3">
-        <v>405500</v>
+        <v>410500</v>
       </c>
       <c r="F12" s="3">
-        <v>404300</v>
+        <v>409900</v>
       </c>
       <c r="G12" s="3">
-        <v>371800</v>
+        <v>408700</v>
       </c>
       <c r="H12" s="3">
-        <v>408300</v>
+        <v>375900</v>
       </c>
       <c r="I12" s="3">
-        <v>428500</v>
+        <v>412800</v>
       </c>
       <c r="J12" s="3">
+        <v>433200</v>
+      </c>
+      <c r="K12" s="3">
         <v>424200</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>388100</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>492200</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>438300</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>651000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>306400</v>
       </c>
-      <c r="P12" s="3"/>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3"/>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -944,51 +960,57 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-      <c r="P13" s="3"/>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="3"/>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>91</v>
+      <c r="D14" s="3">
+        <v>-15700</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="F14" s="3">
-        <v>0</v>
+      <c r="F14" s="3" t="s">
+        <v>91</v>
       </c>
       <c r="G14" s="3">
+        <v>0</v>
+      </c>
+      <c r="H14" s="3">
         <v>-1700</v>
       </c>
-      <c r="H14" s="3">
-        <v>1400</v>
-      </c>
       <c r="I14" s="3">
-        <v>29600</v>
+        <v>1500</v>
       </c>
       <c r="J14" s="3">
+        <v>30000</v>
+      </c>
+      <c r="K14" s="3">
         <v>65100</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>72300</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>32500</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>46800</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>236100</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>68700</v>
       </c>
-      <c r="P14" s="3"/>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q14" s="3"/>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
@@ -1028,9 +1050,12 @@
       <c r="O15" s="3">
         <v>0</v>
       </c>
-      <c r="P15" s="3"/>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P15" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="3"/>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1044,92 +1069,99 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
-        <v>5467800</v>
+        <v>5201900</v>
       </c>
       <c r="E17" s="3">
-        <v>5057500</v>
+        <v>5527100</v>
       </c>
       <c r="F17" s="3">
-        <v>4853400</v>
+        <v>5112400</v>
       </c>
       <c r="G17" s="3">
-        <v>4494500</v>
+        <v>4906000</v>
       </c>
       <c r="H17" s="3">
-        <v>4561500</v>
+        <v>4543300</v>
       </c>
       <c r="I17" s="3">
-        <v>4503800</v>
+        <v>4610900</v>
       </c>
       <c r="J17" s="3">
+        <v>4552600</v>
+      </c>
+      <c r="K17" s="3">
         <v>4492400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>4311500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>4691300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>4246600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>3849100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>3710000</v>
       </c>
-      <c r="P17" s="3"/>
-    </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q17" s="3"/>
+    </row>
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
-        <v>3269600</v>
+        <v>1850200</v>
       </c>
       <c r="E18" s="3">
-        <v>1620400</v>
+        <v>3305000</v>
       </c>
       <c r="F18" s="3">
-        <v>689900</v>
+        <v>1637900</v>
       </c>
       <c r="G18" s="3">
-        <v>151600</v>
+        <v>697400</v>
       </c>
       <c r="H18" s="3">
-        <v>180300</v>
+        <v>153200</v>
       </c>
       <c r="I18" s="3">
-        <v>176300</v>
+        <v>182200</v>
       </c>
       <c r="J18" s="3">
+        <v>178200</v>
+      </c>
+      <c r="K18" s="3">
         <v>143300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>305700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>352000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>96700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-1800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>95700</v>
       </c>
-      <c r="P18" s="3"/>
-    </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q18" s="3"/>
+    </row>
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1146,218 +1178,234 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
-        <v>112600</v>
+        <v>443700</v>
       </c>
       <c r="E20" s="3">
-        <v>375700</v>
+        <v>113800</v>
       </c>
       <c r="F20" s="3">
-        <v>248400</v>
+        <v>379800</v>
       </c>
       <c r="G20" s="3">
-        <v>120200</v>
+        <v>251100</v>
       </c>
       <c r="H20" s="3">
-        <v>-25000</v>
+        <v>121500</v>
       </c>
       <c r="I20" s="3">
-        <v>143700</v>
+        <v>-25300</v>
       </c>
       <c r="J20" s="3">
+        <v>145200</v>
+      </c>
+      <c r="K20" s="3">
         <v>47800</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>146400</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>161600</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>430900</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>249700</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>222000</v>
       </c>
-      <c r="P20" s="3"/>
-    </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q20" s="3"/>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
-        <v>4763700</v>
+        <v>3581300</v>
       </c>
       <c r="E21" s="3">
-        <v>3468600</v>
+        <v>4823400</v>
       </c>
       <c r="F21" s="3">
-        <v>2468200</v>
+        <v>3514700</v>
       </c>
       <c r="G21" s="3">
-        <v>1816700</v>
+        <v>2503800</v>
       </c>
       <c r="H21" s="3">
-        <v>1783400</v>
+        <v>1845300</v>
       </c>
       <c r="I21" s="3">
-        <v>1980900</v>
+        <v>1812100</v>
       </c>
       <c r="J21" s="3">
+        <v>2011900</v>
+      </c>
+      <c r="K21" s="3">
         <v>1817200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1876300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1973200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>1876200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1442200</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>1371900</v>
       </c>
-      <c r="P21" s="3"/>
-    </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q21" s="3"/>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
-        <v>56000</v>
+        <v>46700</v>
       </c>
       <c r="E22" s="3">
-        <v>58600</v>
+        <v>56600</v>
       </c>
       <c r="F22" s="3">
-        <v>62800</v>
+        <v>59200</v>
       </c>
       <c r="G22" s="3">
-        <v>92000</v>
+        <v>63500</v>
       </c>
       <c r="H22" s="3">
-        <v>86800</v>
+        <v>93000</v>
       </c>
       <c r="I22" s="3">
-        <v>75500</v>
+        <v>87700</v>
       </c>
       <c r="J22" s="3">
+        <v>76300</v>
+      </c>
+      <c r="K22" s="3">
         <v>39200</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>15000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>26900</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>23800</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>35800</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>11700</v>
       </c>
-      <c r="P22" s="3"/>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q22" s="3"/>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
-        <v>3326100</v>
+        <v>2247200</v>
       </c>
       <c r="E23" s="3">
-        <v>1937500</v>
+        <v>3362200</v>
       </c>
       <c r="F23" s="3">
-        <v>875500</v>
+        <v>1958500</v>
       </c>
       <c r="G23" s="3">
-        <v>179800</v>
+        <v>885000</v>
       </c>
       <c r="H23" s="3">
-        <v>68500</v>
+        <v>181800</v>
       </c>
       <c r="I23" s="3">
-        <v>244500</v>
+        <v>69200</v>
       </c>
       <c r="J23" s="3">
+        <v>247100</v>
+      </c>
+      <c r="K23" s="3">
         <v>151900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>437100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>486700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>503800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>212100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>305900</v>
       </c>
-      <c r="P23" s="3"/>
-    </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q23" s="3"/>
+    </row>
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
-        <v>566800</v>
+        <v>300200</v>
       </c>
       <c r="E24" s="3">
-        <v>209800</v>
+        <v>572900</v>
       </c>
       <c r="F24" s="3">
-        <v>23400</v>
+        <v>212100</v>
       </c>
       <c r="G24" s="3">
-        <v>-12300</v>
+        <v>23600</v>
       </c>
       <c r="H24" s="3">
-        <v>-14400</v>
+        <v>-12500</v>
       </c>
       <c r="I24" s="3">
-        <v>36600</v>
+        <v>-14500</v>
       </c>
       <c r="J24" s="3">
+        <v>37000</v>
+      </c>
+      <c r="K24" s="3">
         <v>30800</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>27900</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>73300</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>79200</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>71400</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>29800</v>
       </c>
-      <c r="P24" s="3"/>
-    </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q24" s="3"/>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -1397,93 +1445,102 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-      <c r="P25" s="3"/>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="3"/>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
-        <v>2759400</v>
+        <v>1947000</v>
       </c>
       <c r="E26" s="3">
-        <v>1727800</v>
+        <v>2789300</v>
       </c>
       <c r="F26" s="3">
-        <v>852100</v>
+        <v>1746500</v>
       </c>
       <c r="G26" s="3">
-        <v>192100</v>
+        <v>861300</v>
       </c>
       <c r="H26" s="3">
-        <v>82900</v>
+        <v>194200</v>
       </c>
       <c r="I26" s="3">
-        <v>207900</v>
+        <v>83800</v>
       </c>
       <c r="J26" s="3">
+        <v>210100</v>
+      </c>
+      <c r="K26" s="3">
         <v>121100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>409200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>413500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>424600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>140700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>276100</v>
       </c>
-      <c r="P26" s="3"/>
-    </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q26" s="3"/>
+    </row>
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
-        <v>2733700</v>
+        <v>1932800</v>
       </c>
       <c r="E27" s="3">
-        <v>1748700</v>
+        <v>2763300</v>
       </c>
       <c r="F27" s="3">
-        <v>915100</v>
+        <v>1767700</v>
       </c>
       <c r="G27" s="3">
-        <v>304300</v>
+        <v>925000</v>
       </c>
       <c r="H27" s="3">
-        <v>221700</v>
+        <v>307600</v>
       </c>
       <c r="I27" s="3">
-        <v>301900</v>
+        <v>224100</v>
       </c>
       <c r="J27" s="3">
+        <v>305100</v>
+      </c>
+      <c r="K27" s="3">
         <v>260700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>428700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>437300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>443100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>113500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>215400</v>
       </c>
-      <c r="P27" s="3"/>
-    </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q27" s="3"/>
+    </row>
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -1523,9 +1580,12 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-      <c r="P28" s="3"/>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="3"/>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -1565,9 +1625,12 @@
       <c r="O29" s="3">
         <v>0</v>
       </c>
-      <c r="P29" s="3"/>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="3"/>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>24</v>
       </c>
@@ -1607,9 +1670,12 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-      <c r="P30" s="3"/>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="3"/>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>25</v>
       </c>
@@ -1649,93 +1715,102 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-      <c r="P31" s="3"/>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="3"/>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>26</v>
       </c>
       <c r="D32" s="3">
-        <v>-112600</v>
+        <v>-443700</v>
       </c>
       <c r="E32" s="3">
-        <v>-375700</v>
+        <v>-113800</v>
       </c>
       <c r="F32" s="3">
-        <v>-248400</v>
+        <v>-379800</v>
       </c>
       <c r="G32" s="3">
-        <v>-120200</v>
+        <v>-251100</v>
       </c>
       <c r="H32" s="3">
-        <v>25000</v>
+        <v>-121500</v>
       </c>
       <c r="I32" s="3">
-        <v>-143700</v>
+        <v>25300</v>
       </c>
       <c r="J32" s="3">
+        <v>-145200</v>
+      </c>
+      <c r="K32" s="3">
         <v>-47800</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-146400</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-161600</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-430900</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-249700</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-222000</v>
       </c>
-      <c r="P32" s="3"/>
-    </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q32" s="3"/>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D33" s="3">
-        <v>2733700</v>
+        <v>1932800</v>
       </c>
       <c r="E33" s="3">
-        <v>1748700</v>
+        <v>2763300</v>
       </c>
       <c r="F33" s="3">
-        <v>915100</v>
+        <v>1767700</v>
       </c>
       <c r="G33" s="3">
-        <v>304300</v>
+        <v>925000</v>
       </c>
       <c r="H33" s="3">
-        <v>221700</v>
+        <v>307600</v>
       </c>
       <c r="I33" s="3">
-        <v>301900</v>
+        <v>224100</v>
       </c>
       <c r="J33" s="3">
+        <v>305100</v>
+      </c>
+      <c r="K33" s="3">
         <v>260700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>428700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>437300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>443100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>113500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>215400</v>
       </c>
-      <c r="P33" s="3"/>
-    </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q33" s="3"/>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>28</v>
       </c>
@@ -1775,98 +1850,107 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-      <c r="P34" s="3"/>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="3"/>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D35" s="3">
-        <v>2733700</v>
+        <v>1932800</v>
       </c>
       <c r="E35" s="3">
-        <v>1748700</v>
+        <v>2763300</v>
       </c>
       <c r="F35" s="3">
-        <v>915100</v>
+        <v>1767700</v>
       </c>
       <c r="G35" s="3">
-        <v>304300</v>
+        <v>925000</v>
       </c>
       <c r="H35" s="3">
-        <v>221700</v>
+        <v>307600</v>
       </c>
       <c r="I35" s="3">
-        <v>301900</v>
+        <v>224100</v>
       </c>
       <c r="J35" s="3">
+        <v>305100</v>
+      </c>
+      <c r="K35" s="3">
         <v>260700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>428700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>437300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>443100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>113500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>215400</v>
       </c>
-      <c r="P35" s="3"/>
-    </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q35" s="3"/>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>44926</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44561</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44196</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>43830</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43465</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43100</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>42735</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42369</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42004</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>41639</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41274</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>40908</v>
       </c>
-      <c r="P38" s="2"/>
-    </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q38" s="2"/>
+    </row>
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>31</v>
       </c>
@@ -1883,8 +1967,9 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>32</v>
       </c>
@@ -1901,386 +1986,414 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D41" s="3">
-        <v>5449200</v>
+        <v>4200600</v>
       </c>
       <c r="E41" s="3">
-        <v>4157700</v>
+        <v>5508300</v>
       </c>
       <c r="F41" s="3">
-        <v>2948400</v>
+        <v>4202800</v>
       </c>
       <c r="G41" s="3">
-        <v>2993700</v>
+        <v>2980400</v>
       </c>
       <c r="H41" s="3">
-        <v>2622800</v>
+        <v>3026200</v>
       </c>
       <c r="I41" s="3">
-        <v>2560500</v>
+        <v>2651200</v>
       </c>
       <c r="J41" s="3">
+        <v>2588300</v>
+      </c>
+      <c r="K41" s="3">
         <v>1805100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1698900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1646200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1783100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1565800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>115300</v>
       </c>
-      <c r="P41" s="3"/>
-    </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q41" s="3"/>
+    </row>
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D42" s="3">
-        <v>149900</v>
+        <v>390700</v>
       </c>
       <c r="E42" s="3">
-        <v>296200</v>
+        <v>151500</v>
       </c>
       <c r="F42" s="3">
-        <v>38100</v>
+        <v>299400</v>
       </c>
       <c r="G42" s="3">
+        <v>38600</v>
+      </c>
+      <c r="H42" s="3">
+        <v>22900</v>
+      </c>
+      <c r="I42" s="3">
+        <v>16700</v>
+      </c>
+      <c r="J42" s="3">
         <v>22700</v>
       </c>
-      <c r="H42" s="3">
-        <v>16600</v>
-      </c>
-      <c r="I42" s="3">
-        <v>22500</v>
-      </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>22400</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>21200</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>26700</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>97100</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>1595700</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>1675100</v>
       </c>
-      <c r="P42" s="3"/>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q42" s="3"/>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D43" s="3">
-        <v>1228800</v>
+        <v>1050900</v>
       </c>
       <c r="E43" s="3">
-        <v>1140200</v>
+        <v>1242100</v>
       </c>
       <c r="F43" s="3">
-        <v>916600</v>
+        <v>1152600</v>
       </c>
       <c r="G43" s="3">
-        <v>834700</v>
+        <v>926500</v>
       </c>
       <c r="H43" s="3">
-        <v>774200</v>
+        <v>843700</v>
       </c>
       <c r="I43" s="3">
-        <v>710300</v>
+        <v>782600</v>
       </c>
       <c r="J43" s="3">
+        <v>718000</v>
+      </c>
+      <c r="K43" s="3">
         <v>752500</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>637300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>830700</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>617600</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1142100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>499600</v>
       </c>
-      <c r="P43" s="3"/>
-    </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q43" s="3"/>
+    </row>
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D44" s="3">
-        <v>974000</v>
+        <v>1131700</v>
       </c>
       <c r="E44" s="3">
-        <v>721400</v>
+        <v>984600</v>
       </c>
       <c r="F44" s="3">
-        <v>707000</v>
+        <v>729200</v>
       </c>
       <c r="G44" s="3">
-        <v>680800</v>
+        <v>714700</v>
       </c>
       <c r="H44" s="3">
-        <v>570700</v>
+        <v>688100</v>
       </c>
       <c r="I44" s="3">
-        <v>572400</v>
+        <v>576900</v>
       </c>
       <c r="J44" s="3">
+        <v>578600</v>
+      </c>
+      <c r="K44" s="3">
         <v>532900</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>562400</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>493000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>490900</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>866300</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>414400</v>
       </c>
-      <c r="P44" s="3"/>
-    </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q44" s="3"/>
+    </row>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D45" s="3">
-        <v>109900</v>
+        <v>96400</v>
       </c>
       <c r="E45" s="3">
-        <v>997600</v>
+        <v>111100</v>
       </c>
       <c r="F45" s="3">
-        <v>540800</v>
+        <v>1008500</v>
       </c>
       <c r="G45" s="3">
-        <v>288500</v>
+        <v>546700</v>
       </c>
       <c r="H45" s="3">
-        <v>442100</v>
+        <v>291700</v>
       </c>
       <c r="I45" s="3">
-        <v>497000</v>
+        <v>446900</v>
       </c>
       <c r="J45" s="3">
+        <v>502400</v>
+      </c>
+      <c r="K45" s="3">
         <v>350400</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>103000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>436500</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>126400</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>183000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>36600</v>
       </c>
-      <c r="P45" s="3"/>
-    </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q45" s="3"/>
+    </row>
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D46" s="3">
-        <v>7911800</v>
+        <v>6870300</v>
       </c>
       <c r="E46" s="3">
-        <v>7313100</v>
+        <v>7997600</v>
       </c>
       <c r="F46" s="3">
-        <v>5151000</v>
+        <v>7392400</v>
       </c>
       <c r="G46" s="3">
-        <v>4820300</v>
+        <v>5206900</v>
       </c>
       <c r="H46" s="3">
-        <v>4426400</v>
+        <v>4872600</v>
       </c>
       <c r="I46" s="3">
-        <v>4362700</v>
+        <v>4474400</v>
       </c>
       <c r="J46" s="3">
+        <v>4410000</v>
+      </c>
+      <c r="K46" s="3">
         <v>3463200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>3022800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>3489000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>3115000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>2661700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>2741100</v>
       </c>
-      <c r="P46" s="3"/>
-    </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q46" s="3"/>
+    </row>
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D47" s="3">
-        <v>2033200</v>
+        <v>2353100</v>
       </c>
       <c r="E47" s="3">
-        <v>2274300</v>
+        <v>2055300</v>
       </c>
       <c r="F47" s="3">
-        <v>1773700</v>
+        <v>2299000</v>
       </c>
       <c r="G47" s="3">
-        <v>1296100</v>
+        <v>1793000</v>
       </c>
       <c r="H47" s="3">
-        <v>1050400</v>
+        <v>1310200</v>
       </c>
       <c r="I47" s="3">
-        <v>1066600</v>
+        <v>1061800</v>
       </c>
       <c r="J47" s="3">
+        <v>1078200</v>
+      </c>
+      <c r="K47" s="3">
         <v>1089900</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>1280000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>2227500</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>1056700</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>2310700</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>1301900</v>
       </c>
-      <c r="P47" s="3"/>
-    </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q47" s="3"/>
+    </row>
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D48" s="3">
-        <v>6208400</v>
+        <v>7949400</v>
       </c>
       <c r="E48" s="3">
-        <v>4558000</v>
+        <v>6275700</v>
       </c>
       <c r="F48" s="3">
-        <v>4423800</v>
+        <v>4607500</v>
       </c>
       <c r="G48" s="3">
-        <v>4981000</v>
+        <v>4471700</v>
       </c>
       <c r="H48" s="3">
-        <v>5439500</v>
+        <v>5035000</v>
       </c>
       <c r="I48" s="3">
-        <v>6459000</v>
+        <v>5498500</v>
       </c>
       <c r="J48" s="3">
+        <v>6529000</v>
+      </c>
+      <c r="K48" s="3">
         <v>7090200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>6017900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>6042500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>11405100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>10614700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>4869500</v>
       </c>
-      <c r="P48" s="3"/>
-    </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q48" s="3"/>
+    </row>
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D49" s="3">
-        <v>134000</v>
+        <v>138600</v>
       </c>
       <c r="E49" s="3">
-        <v>114300</v>
+        <v>135500</v>
       </c>
       <c r="F49" s="3">
-        <v>152900</v>
+        <v>115500</v>
       </c>
       <c r="G49" s="3">
-        <v>163000</v>
+        <v>154600</v>
       </c>
       <c r="H49" s="3">
-        <v>93800</v>
+        <v>164700</v>
       </c>
       <c r="I49" s="3">
-        <v>118700</v>
+        <v>94800</v>
       </c>
       <c r="J49" s="3">
+        <v>120000</v>
+      </c>
+      <c r="K49" s="3">
         <v>128200</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>143600</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>163300</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>332500</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>138200</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>11400</v>
       </c>
-      <c r="P49" s="3"/>
-    </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q49" s="3"/>
+    </row>
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>42</v>
       </c>
@@ -2320,9 +2433,12 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-      <c r="P50" s="3"/>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="3"/>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>43</v>
       </c>
@@ -2362,51 +2478,57 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-      <c r="P51" s="3"/>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="3"/>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>44</v>
       </c>
       <c r="D52" s="3">
-        <v>423800</v>
+        <v>409200</v>
       </c>
       <c r="E52" s="3">
-        <v>300000</v>
+        <v>428400</v>
       </c>
       <c r="F52" s="3">
-        <v>333700</v>
+        <v>303300</v>
       </c>
       <c r="G52" s="3">
-        <v>345000</v>
+        <v>337400</v>
       </c>
       <c r="H52" s="3">
-        <v>420300</v>
+        <v>348700</v>
       </c>
       <c r="I52" s="3">
-        <v>348000</v>
+        <v>424800</v>
       </c>
       <c r="J52" s="3">
+        <v>351800</v>
+      </c>
+      <c r="K52" s="3">
         <v>350100</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>291000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>238400</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>262800</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>281300</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>201400</v>
       </c>
-      <c r="P52" s="3"/>
-    </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q52" s="3"/>
+    </row>
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>45</v>
       </c>
@@ -2446,51 +2568,57 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-      <c r="P53" s="3"/>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="3"/>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>46</v>
       </c>
       <c r="D54" s="3">
-        <v>16711200</v>
+        <v>17720600</v>
       </c>
       <c r="E54" s="3">
-        <v>14559800</v>
+        <v>16892400</v>
       </c>
       <c r="F54" s="3">
-        <v>11835100</v>
+        <v>14717700</v>
       </c>
       <c r="G54" s="3">
-        <v>11605400</v>
+        <v>11963500</v>
       </c>
       <c r="H54" s="3">
-        <v>11430400</v>
+        <v>11731200</v>
       </c>
       <c r="I54" s="3">
-        <v>12355000</v>
+        <v>11554300</v>
       </c>
       <c r="J54" s="3">
+        <v>12489000</v>
+      </c>
+      <c r="K54" s="3">
         <v>12121600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>10755300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>11283100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>10310500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>9353200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>9125300</v>
       </c>
-      <c r="P54" s="3"/>
-    </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q54" s="3"/>
+    </row>
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>47</v>
       </c>
@@ -2507,8 +2635,9 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>48</v>
       </c>
@@ -2525,260 +2654,279 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>49</v>
       </c>
       <c r="D57" s="3">
-        <v>281600</v>
+        <v>238500</v>
       </c>
       <c r="E57" s="3">
-        <v>262200</v>
+        <v>284700</v>
       </c>
       <c r="F57" s="3">
-        <v>246500</v>
+        <v>265100</v>
       </c>
       <c r="G57" s="3">
-        <v>278300</v>
+        <v>249200</v>
       </c>
       <c r="H57" s="3">
-        <v>213200</v>
+        <v>281300</v>
       </c>
       <c r="I57" s="3">
-        <v>204900</v>
+        <v>215500</v>
       </c>
       <c r="J57" s="3">
+        <v>207100</v>
+      </c>
+      <c r="K57" s="3">
         <v>214900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>189800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>222100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>260100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>416800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>163400</v>
       </c>
-      <c r="P57" s="3"/>
-    </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q57" s="3"/>
+    </row>
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D58" s="3">
-        <v>254700</v>
+        <v>952300</v>
       </c>
       <c r="E58" s="3">
-        <v>1248200</v>
+        <v>257400</v>
       </c>
       <c r="F58" s="3">
-        <v>1209900</v>
+        <v>1261700</v>
       </c>
       <c r="G58" s="3">
-        <v>1171900</v>
+        <v>1223000</v>
       </c>
       <c r="H58" s="3">
-        <v>571400</v>
+        <v>1184600</v>
       </c>
       <c r="I58" s="3">
-        <v>1655600</v>
+        <v>577600</v>
       </c>
       <c r="J58" s="3">
+        <v>1673500</v>
+      </c>
+      <c r="K58" s="3">
         <v>973500</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>386000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>361100</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>743300</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>975200</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>567900</v>
       </c>
-      <c r="P58" s="3"/>
-    </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q58" s="3"/>
+    </row>
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D59" s="3">
-        <v>2867200</v>
+        <v>1947000</v>
       </c>
       <c r="E59" s="3">
-        <v>1795600</v>
+        <v>2898300</v>
       </c>
       <c r="F59" s="3">
-        <v>996600</v>
+        <v>1815100</v>
       </c>
       <c r="G59" s="3">
-        <v>829400</v>
+        <v>1007400</v>
       </c>
       <c r="H59" s="3">
-        <v>779700</v>
+        <v>838400</v>
       </c>
       <c r="I59" s="3">
-        <v>900300</v>
+        <v>788200</v>
       </c>
       <c r="J59" s="3">
+        <v>910000</v>
+      </c>
+      <c r="K59" s="3">
         <v>1068200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>962300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1149500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>687700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1274000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>667900</v>
       </c>
-      <c r="P59" s="3"/>
-    </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q59" s="3"/>
+    </row>
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D60" s="3">
-        <v>3403500</v>
+        <v>3137800</v>
       </c>
       <c r="E60" s="3">
-        <v>3306000</v>
+        <v>3440400</v>
       </c>
       <c r="F60" s="3">
-        <v>2452900</v>
+        <v>3341800</v>
       </c>
       <c r="G60" s="3">
-        <v>2279600</v>
+        <v>2479500</v>
       </c>
       <c r="H60" s="3">
-        <v>1564300</v>
+        <v>2304300</v>
       </c>
       <c r="I60" s="3">
-        <v>2760700</v>
+        <v>1581300</v>
       </c>
       <c r="J60" s="3">
+        <v>2790700</v>
+      </c>
+      <c r="K60" s="3">
         <v>2256500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1538100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1732800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1691000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1334400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>1399200</v>
       </c>
-      <c r="P60" s="3"/>
-    </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q60" s="3"/>
+    </row>
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D61" s="3">
-        <v>1413200</v>
+        <v>1588100</v>
       </c>
       <c r="E61" s="3">
-        <v>1390100</v>
+        <v>1428500</v>
       </c>
       <c r="F61" s="3">
-        <v>934200</v>
+        <v>1405100</v>
       </c>
       <c r="G61" s="3">
-        <v>1672500</v>
+        <v>944300</v>
       </c>
       <c r="H61" s="3">
-        <v>2103100</v>
+        <v>1690600</v>
       </c>
       <c r="I61" s="3">
-        <v>1671600</v>
+        <v>2125900</v>
       </c>
       <c r="J61" s="3">
+        <v>1689700</v>
+      </c>
+      <c r="K61" s="3">
         <v>1903800</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1515100</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1203100</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>996800</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1069500</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>687900</v>
       </c>
-      <c r="P61" s="3"/>
-    </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q61" s="3"/>
+    </row>
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D62" s="3">
-        <v>1378100</v>
+        <v>1599700</v>
       </c>
       <c r="E62" s="3">
-        <v>1048000</v>
+        <v>1393100</v>
       </c>
       <c r="F62" s="3">
-        <v>1056500</v>
+        <v>1059400</v>
       </c>
       <c r="G62" s="3">
-        <v>1157100</v>
+        <v>1068000</v>
       </c>
       <c r="H62" s="3">
-        <v>1288000</v>
+        <v>1169700</v>
       </c>
       <c r="I62" s="3">
-        <v>1212700</v>
+        <v>1302000</v>
       </c>
       <c r="J62" s="3">
+        <v>1225800</v>
+      </c>
+      <c r="K62" s="3">
         <v>1103700</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>407400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>242400</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>268400</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>365900</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>120800</v>
       </c>
-      <c r="P62" s="3"/>
-    </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q62" s="3"/>
+    </row>
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>55</v>
       </c>
@@ -2818,9 +2966,12 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-      <c r="P63" s="3"/>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="3"/>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -2860,9 +3011,12 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-      <c r="P64" s="3"/>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="3"/>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>56</v>
       </c>
@@ -2902,51 +3056,57 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-      <c r="P65" s="3"/>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="3"/>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>57</v>
       </c>
       <c r="D66" s="3">
-        <v>6205600</v>
+        <v>6336400</v>
       </c>
       <c r="E66" s="3">
-        <v>5751100</v>
+        <v>6272900</v>
       </c>
       <c r="F66" s="3">
-        <v>4447200</v>
+        <v>5813400</v>
       </c>
       <c r="G66" s="3">
-        <v>5122100</v>
+        <v>4495400</v>
       </c>
       <c r="H66" s="3">
-        <v>4970100</v>
+        <v>5177600</v>
       </c>
       <c r="I66" s="3">
-        <v>5674900</v>
+        <v>5024000</v>
       </c>
       <c r="J66" s="3">
+        <v>5736500</v>
+      </c>
+      <c r="K66" s="3">
         <v>5331900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>3525200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>3317000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>3107700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>2730600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>2351000</v>
       </c>
-      <c r="P66" s="3"/>
-    </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q66" s="3"/>
+    </row>
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>58</v>
       </c>
@@ -2963,8 +3123,9 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>59</v>
       </c>
@@ -3004,9 +3165,12 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-      <c r="P68" s="3"/>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="3"/>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>60</v>
       </c>
@@ -3046,9 +3210,12 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-      <c r="P69" s="3"/>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="3"/>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>61</v>
       </c>
@@ -3088,9 +3255,12 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-      <c r="P70" s="3"/>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="3"/>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>62</v>
       </c>
@@ -3130,51 +3300,57 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-      <c r="P71" s="3"/>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="3"/>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>63</v>
       </c>
       <c r="D72" s="3">
-        <v>6340400</v>
+        <v>6878400</v>
       </c>
       <c r="E72" s="3">
-        <v>3617000</v>
+        <v>6409200</v>
       </c>
       <c r="F72" s="3">
-        <v>2513500</v>
+        <v>3656300</v>
       </c>
       <c r="G72" s="3">
-        <v>1917100</v>
+        <v>2540800</v>
       </c>
       <c r="H72" s="3">
-        <v>1930800</v>
+        <v>1937900</v>
       </c>
       <c r="I72" s="3">
-        <v>1506900</v>
+        <v>1951700</v>
       </c>
       <c r="J72" s="3">
+        <v>1523200</v>
+      </c>
+      <c r="K72" s="3">
         <v>1494000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>1616600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>1597100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>1343700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>1872000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>798900</v>
       </c>
-      <c r="P72" s="3"/>
-    </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q72" s="3"/>
+    </row>
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>64</v>
       </c>
@@ -3214,9 +3390,12 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-      <c r="P73" s="3"/>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="3"/>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>65</v>
       </c>
@@ -3256,9 +3435,12 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-      <c r="P74" s="3"/>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="3"/>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>66</v>
       </c>
@@ -3298,51 +3480,57 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-      <c r="P75" s="3"/>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="3"/>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>67</v>
       </c>
       <c r="D76" s="3">
-        <v>10505600</v>
+        <v>11384200</v>
       </c>
       <c r="E76" s="3">
-        <v>8808700</v>
+        <v>10619500</v>
       </c>
       <c r="F76" s="3">
-        <v>7387900</v>
+        <v>8904200</v>
       </c>
       <c r="G76" s="3">
-        <v>6483300</v>
+        <v>7468100</v>
       </c>
       <c r="H76" s="3">
-        <v>6460300</v>
+        <v>6553600</v>
       </c>
       <c r="I76" s="3">
-        <v>6680100</v>
+        <v>6530300</v>
       </c>
       <c r="J76" s="3">
+        <v>6752500</v>
+      </c>
+      <c r="K76" s="3">
         <v>6789800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>7230100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>7966100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>7202800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>6622600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>6774300</v>
       </c>
-      <c r="P76" s="3"/>
-    </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q76" s="3"/>
+    </row>
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>68</v>
       </c>
@@ -3382,98 +3570,107 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-      <c r="P77" s="3"/>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="3"/>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>44926</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44561</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44196</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>43830</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43465</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43100</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>42735</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42369</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42004</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>41639</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41274</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>40908</v>
       </c>
-      <c r="P80" s="2"/>
-    </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q80" s="2"/>
+    </row>
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D81" s="3">
-        <v>2733700</v>
+        <v>1932800</v>
       </c>
       <c r="E81" s="3">
-        <v>1748700</v>
+        <v>2763300</v>
       </c>
       <c r="F81" s="3">
-        <v>915100</v>
+        <v>1767700</v>
       </c>
       <c r="G81" s="3">
-        <v>304300</v>
+        <v>925000</v>
       </c>
       <c r="H81" s="3">
-        <v>221700</v>
+        <v>307600</v>
       </c>
       <c r="I81" s="3">
-        <v>301900</v>
+        <v>224100</v>
       </c>
       <c r="J81" s="3">
+        <v>305100</v>
+      </c>
+      <c r="K81" s="3">
         <v>260700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>428700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>437300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>443100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>113500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>215400</v>
       </c>
-      <c r="P81" s="3"/>
-    </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q81" s="3"/>
+    </row>
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>70</v>
       </c>
@@ -3490,50 +3687,54 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>71</v>
       </c>
       <c r="D83" s="3">
-        <v>1384700</v>
+        <v>1282900</v>
       </c>
       <c r="E83" s="3">
-        <v>1475800</v>
+        <v>1399700</v>
       </c>
       <c r="F83" s="3">
-        <v>1533300</v>
+        <v>1491800</v>
       </c>
       <c r="G83" s="3">
-        <v>1548400</v>
+        <v>1549900</v>
       </c>
       <c r="H83" s="3">
-        <v>1631700</v>
+        <v>1565200</v>
       </c>
       <c r="I83" s="3">
-        <v>1664600</v>
+        <v>1649400</v>
       </c>
       <c r="J83" s="3">
+        <v>1682700</v>
+      </c>
+      <c r="K83" s="3">
         <v>1629700</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>1449700</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>1464500</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>1348200</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>1192100</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>1055600</v>
       </c>
-      <c r="P83" s="3"/>
-    </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q83" s="3"/>
+    </row>
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>72</v>
       </c>
@@ -3573,9 +3774,12 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-      <c r="P84" s="3"/>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="3"/>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>73</v>
       </c>
@@ -3615,9 +3819,12 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-      <c r="P85" s="3"/>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="3"/>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>74</v>
       </c>
@@ -3657,9 +3864,12 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-      <c r="P86" s="3"/>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="3"/>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>75</v>
       </c>
@@ -3699,9 +3909,12 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-      <c r="P87" s="3"/>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="3"/>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>76</v>
       </c>
@@ -3741,51 +3954,57 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-      <c r="P88" s="3"/>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="3"/>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>77</v>
       </c>
       <c r="D89" s="3">
-        <v>4572700</v>
+        <v>2725300</v>
       </c>
       <c r="E89" s="3">
-        <v>2832500</v>
+        <v>4622300</v>
       </c>
       <c r="F89" s="3">
-        <v>2061100</v>
+        <v>2863300</v>
       </c>
       <c r="G89" s="3">
-        <v>1721200</v>
+        <v>2083500</v>
       </c>
       <c r="H89" s="3">
-        <v>1596800</v>
+        <v>1739900</v>
       </c>
       <c r="I89" s="3">
-        <v>1645100</v>
+        <v>1614100</v>
       </c>
       <c r="J89" s="3">
+        <v>1662900</v>
+      </c>
+      <c r="K89" s="3">
         <v>1456200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1906000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>1613300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>1525000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>1343600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>1358300</v>
       </c>
-      <c r="P89" s="3"/>
-    </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q89" s="3"/>
+    </row>
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>78</v>
       </c>
@@ -3802,50 +4021,54 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>79</v>
       </c>
       <c r="D91" s="3">
-        <v>-2512000</v>
+        <v>-2898800</v>
       </c>
       <c r="E91" s="3">
-        <v>-1505900</v>
+        <v>-2539200</v>
       </c>
       <c r="F91" s="3">
-        <v>-825900</v>
+        <v>-1522200</v>
       </c>
       <c r="G91" s="3">
-        <v>-517900</v>
+        <v>-834900</v>
       </c>
       <c r="H91" s="3">
-        <v>-614100</v>
+        <v>-523500</v>
       </c>
       <c r="I91" s="3">
-        <v>-1386800</v>
+        <v>-620800</v>
       </c>
       <c r="J91" s="3">
+        <v>-1401800</v>
+      </c>
+      <c r="K91" s="3">
         <v>-2870400</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-1928900</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-1557400</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-1154500</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-1754100</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-1751400</v>
       </c>
-      <c r="P91" s="3"/>
-    </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q91" s="3"/>
+    </row>
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>80</v>
       </c>
@@ -3885,9 +4108,12 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-      <c r="P92" s="3"/>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q92" s="3"/>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>81</v>
       </c>
@@ -3927,51 +4153,57 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-      <c r="P93" s="3"/>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q93" s="3"/>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>82</v>
       </c>
       <c r="D94" s="3">
-        <v>-1706300</v>
+        <v>-3098900</v>
       </c>
       <c r="E94" s="3">
-        <v>-1948800</v>
+        <v>-1724800</v>
       </c>
       <c r="F94" s="3">
-        <v>-1257500</v>
+        <v>-1970000</v>
       </c>
       <c r="G94" s="3">
-        <v>-993200</v>
+        <v>-1271100</v>
       </c>
       <c r="H94" s="3">
-        <v>-485900</v>
+        <v>-1004000</v>
       </c>
       <c r="I94" s="3">
-        <v>-1110300</v>
+        <v>-491200</v>
       </c>
       <c r="J94" s="3">
+        <v>-1122300</v>
+      </c>
+      <c r="K94" s="3">
         <v>-2510700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-2183200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-1534700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-1105600</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-1633800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-1797500</v>
       </c>
-      <c r="P94" s="3"/>
-    </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q94" s="3"/>
+    </row>
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>83</v>
       </c>
@@ -3988,50 +4220,54 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>84</v>
       </c>
       <c r="D96" s="3">
-        <v>-1173900</v>
+        <v>-1426500</v>
       </c>
       <c r="E96" s="3">
-        <v>-623000</v>
+        <v>-1186600</v>
       </c>
       <c r="F96" s="3">
-        <v>-306200</v>
+        <v>-629700</v>
       </c>
       <c r="G96" s="3">
-        <v>-216700</v>
+        <v>-309500</v>
       </c>
       <c r="H96" s="3">
-        <v>-268300</v>
+        <v>-219000</v>
       </c>
       <c r="I96" s="3">
-        <v>-191300</v>
+        <v>-271200</v>
       </c>
       <c r="J96" s="3">
+        <v>-193400</v>
+      </c>
+      <c r="K96" s="3">
         <v>-216500</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-221200</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-225200</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-177600</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-210100</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-457100</v>
       </c>
-      <c r="P96" s="3"/>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3"/>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>85</v>
       </c>
@@ -4071,9 +4307,12 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-      <c r="P97" s="3"/>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q97" s="3"/>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>86</v>
       </c>
@@ -4113,9 +4352,12 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-      <c r="P98" s="3"/>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="3"/>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>87</v>
       </c>
@@ -4155,133 +4397,145 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-      <c r="P99" s="3"/>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="3"/>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D100" s="3">
-        <v>-1794900</v>
+        <v>-921700</v>
       </c>
       <c r="E100" s="3">
-        <v>391600</v>
+        <v>-1814400</v>
       </c>
       <c r="F100" s="3">
-        <v>-802600</v>
+        <v>395800</v>
       </c>
       <c r="G100" s="3">
-        <v>-309300</v>
+        <v>-811300</v>
       </c>
       <c r="H100" s="3">
-        <v>-1049800</v>
+        <v>-312700</v>
       </c>
       <c r="I100" s="3">
-        <v>287200</v>
+        <v>-1061100</v>
       </c>
       <c r="J100" s="3">
+        <v>290300</v>
+      </c>
+      <c r="K100" s="3">
         <v>1216200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>479800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-297400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-137700</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>119300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>323600</v>
       </c>
-      <c r="P100" s="3"/>
-    </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q100" s="3"/>
+    </row>
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D101" s="3">
-        <v>220000</v>
+        <v>-12400</v>
       </c>
       <c r="E101" s="3">
-        <v>-66000</v>
+        <v>222400</v>
       </c>
       <c r="F101" s="3">
-        <v>-46300</v>
+        <v>-66700</v>
       </c>
       <c r="G101" s="3">
+        <v>-46800</v>
+      </c>
+      <c r="H101" s="3">
+        <v>-48300</v>
+      </c>
+      <c r="I101" s="3">
+        <v>1200</v>
+      </c>
+      <c r="J101" s="3">
+        <v>-67300</v>
+      </c>
+      <c r="K101" s="3">
+        <v>-27300</v>
+      </c>
+      <c r="L101" s="3">
+        <v>23000</v>
+      </c>
+      <c r="M101" s="3">
+        <v>52500</v>
+      </c>
+      <c r="N101" s="3">
+        <v>10900</v>
+      </c>
+      <c r="O101" s="3">
         <v>-47800</v>
       </c>
-      <c r="H101" s="3">
-        <v>1100</v>
-      </c>
-      <c r="I101" s="3">
-        <v>-66600</v>
-      </c>
-      <c r="J101" s="3">
-        <v>-27300</v>
-      </c>
-      <c r="K101" s="3">
-        <v>23000</v>
-      </c>
-      <c r="L101" s="3">
-        <v>52500</v>
-      </c>
-      <c r="M101" s="3">
-        <v>10900</v>
-      </c>
-      <c r="N101" s="3">
-        <v>-47800</v>
-      </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>43800</v>
       </c>
-      <c r="P101" s="3"/>
-    </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q101" s="3"/>
+    </row>
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D102" s="3">
-        <v>1291500</v>
+        <v>-1307700</v>
       </c>
       <c r="E102" s="3">
-        <v>1209300</v>
+        <v>1305500</v>
       </c>
       <c r="F102" s="3">
-        <v>-45300</v>
+        <v>1222400</v>
       </c>
       <c r="G102" s="3">
-        <v>370900</v>
+        <v>-45800</v>
       </c>
       <c r="H102" s="3">
-        <v>62300</v>
+        <v>374900</v>
       </c>
       <c r="I102" s="3">
-        <v>755400</v>
+        <v>63000</v>
       </c>
       <c r="J102" s="3">
+        <v>763600</v>
+      </c>
+      <c r="K102" s="3">
         <v>134400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>225600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-166300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>292600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-218600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-71800</v>
       </c>
-      <c r="P102" s="3"/>
+      <c r="Q102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/UMC_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/UMC_YR_FIN.xlsx
@@ -726,25 +726,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>7052100</v>
+        <v>6900700</v>
       </c>
       <c r="E8" s="3">
-        <v>8832200</v>
+        <v>8642700</v>
       </c>
       <c r="F8" s="3">
-        <v>6750300</v>
+        <v>6605500</v>
       </c>
       <c r="G8" s="3">
-        <v>5603500</v>
+        <v>5483200</v>
       </c>
       <c r="H8" s="3">
-        <v>4696500</v>
+        <v>4595700</v>
       </c>
       <c r="I8" s="3">
-        <v>4793200</v>
+        <v>4690300</v>
       </c>
       <c r="J8" s="3">
-        <v>4730800</v>
+        <v>4629300</v>
       </c>
       <c r="K8" s="3">
         <v>4635700</v>
@@ -771,25 +771,25 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>4588400</v>
+        <v>4489900</v>
       </c>
       <c r="E9" s="3">
-        <v>4846700</v>
+        <v>4742700</v>
       </c>
       <c r="F9" s="3">
-        <v>4467100</v>
+        <v>4371200</v>
       </c>
       <c r="G9" s="3">
-        <v>4367600</v>
+        <v>4273900</v>
       </c>
       <c r="H9" s="3">
-        <v>4021000</v>
+        <v>3934800</v>
       </c>
       <c r="I9" s="3">
-        <v>4069400</v>
+        <v>3982100</v>
       </c>
       <c r="J9" s="3">
-        <v>3873400</v>
+        <v>3790300</v>
       </c>
       <c r="K9" s="3">
         <v>3683300</v>
@@ -816,25 +816,25 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>2463700</v>
+        <v>2410800</v>
       </c>
       <c r="E10" s="3">
-        <v>3985500</v>
+        <v>3900000</v>
       </c>
       <c r="F10" s="3">
-        <v>2283300</v>
+        <v>2234300</v>
       </c>
       <c r="G10" s="3">
-        <v>1235800</v>
+        <v>1209300</v>
       </c>
       <c r="H10" s="3">
-        <v>675500</v>
+        <v>661000</v>
       </c>
       <c r="I10" s="3">
-        <v>723800</v>
+        <v>708300</v>
       </c>
       <c r="J10" s="3">
-        <v>857500</v>
+        <v>839100</v>
       </c>
       <c r="K10" s="3">
         <v>952400</v>
@@ -880,25 +880,25 @@
         <v>7</v>
       </c>
       <c r="D12" s="3">
-        <v>421000</v>
+        <v>411900</v>
       </c>
       <c r="E12" s="3">
-        <v>410500</v>
+        <v>401700</v>
       </c>
       <c r="F12" s="3">
-        <v>409900</v>
+        <v>401100</v>
       </c>
       <c r="G12" s="3">
-        <v>408700</v>
+        <v>399900</v>
       </c>
       <c r="H12" s="3">
-        <v>375900</v>
+        <v>367800</v>
       </c>
       <c r="I12" s="3">
-        <v>412800</v>
+        <v>403900</v>
       </c>
       <c r="J12" s="3">
-        <v>433200</v>
+        <v>423900</v>
       </c>
       <c r="K12" s="3">
         <v>424200</v>
@@ -970,7 +970,7 @@
         <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>-15700</v>
+        <v>-15300</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>91</v>
@@ -985,10 +985,10 @@
         <v>-1700</v>
       </c>
       <c r="I14" s="3">
-        <v>1500</v>
+        <v>1400</v>
       </c>
       <c r="J14" s="3">
-        <v>30000</v>
+        <v>29300</v>
       </c>
       <c r="K14" s="3">
         <v>65100</v>
@@ -1076,25 +1076,25 @@
         <v>11</v>
       </c>
       <c r="D17" s="3">
-        <v>5201900</v>
+        <v>5090200</v>
       </c>
       <c r="E17" s="3">
-        <v>5527100</v>
+        <v>5408500</v>
       </c>
       <c r="F17" s="3">
-        <v>5112400</v>
+        <v>5002700</v>
       </c>
       <c r="G17" s="3">
-        <v>4906000</v>
+        <v>4800800</v>
       </c>
       <c r="H17" s="3">
-        <v>4543300</v>
+        <v>4445800</v>
       </c>
       <c r="I17" s="3">
-        <v>4610900</v>
+        <v>4512000</v>
       </c>
       <c r="J17" s="3">
-        <v>4552600</v>
+        <v>4454900</v>
       </c>
       <c r="K17" s="3">
         <v>4492400</v>
@@ -1121,25 +1121,25 @@
         <v>12</v>
       </c>
       <c r="D18" s="3">
-        <v>1850200</v>
+        <v>1810500</v>
       </c>
       <c r="E18" s="3">
-        <v>3305000</v>
+        <v>3234100</v>
       </c>
       <c r="F18" s="3">
-        <v>1637900</v>
+        <v>1602800</v>
       </c>
       <c r="G18" s="3">
-        <v>697400</v>
+        <v>682400</v>
       </c>
       <c r="H18" s="3">
-        <v>153200</v>
+        <v>150000</v>
       </c>
       <c r="I18" s="3">
-        <v>182200</v>
+        <v>178300</v>
       </c>
       <c r="J18" s="3">
-        <v>178200</v>
+        <v>174400</v>
       </c>
       <c r="K18" s="3">
         <v>143300</v>
@@ -1185,25 +1185,25 @@
         <v>14</v>
       </c>
       <c r="D20" s="3">
-        <v>443700</v>
+        <v>434200</v>
       </c>
       <c r="E20" s="3">
-        <v>113800</v>
+        <v>111300</v>
       </c>
       <c r="F20" s="3">
-        <v>379800</v>
+        <v>371700</v>
       </c>
       <c r="G20" s="3">
-        <v>251100</v>
+        <v>245700</v>
       </c>
       <c r="H20" s="3">
-        <v>121500</v>
+        <v>118900</v>
       </c>
       <c r="I20" s="3">
-        <v>-25300</v>
+        <v>-24700</v>
       </c>
       <c r="J20" s="3">
-        <v>145200</v>
+        <v>142100</v>
       </c>
       <c r="K20" s="3">
         <v>47800</v>
@@ -1230,25 +1230,25 @@
         <v>15</v>
       </c>
       <c r="D21" s="3">
-        <v>3581300</v>
+        <v>3495600</v>
       </c>
       <c r="E21" s="3">
-        <v>4823400</v>
+        <v>4710300</v>
       </c>
       <c r="F21" s="3">
-        <v>3514700</v>
+        <v>3429100</v>
       </c>
       <c r="G21" s="3">
-        <v>2503800</v>
+        <v>2439400</v>
       </c>
       <c r="H21" s="3">
-        <v>1845300</v>
+        <v>1795000</v>
       </c>
       <c r="I21" s="3">
-        <v>1812100</v>
+        <v>1761900</v>
       </c>
       <c r="J21" s="3">
-        <v>2011900</v>
+        <v>1957200</v>
       </c>
       <c r="K21" s="3">
         <v>1817200</v>
@@ -1275,25 +1275,25 @@
         <v>16</v>
       </c>
       <c r="D22" s="3">
-        <v>46700</v>
+        <v>45700</v>
       </c>
       <c r="E22" s="3">
-        <v>56600</v>
+        <v>55400</v>
       </c>
       <c r="F22" s="3">
-        <v>59200</v>
+        <v>57900</v>
       </c>
       <c r="G22" s="3">
-        <v>63500</v>
+        <v>62200</v>
       </c>
       <c r="H22" s="3">
-        <v>93000</v>
+        <v>91000</v>
       </c>
       <c r="I22" s="3">
-        <v>87700</v>
+        <v>85900</v>
       </c>
       <c r="J22" s="3">
-        <v>76300</v>
+        <v>74600</v>
       </c>
       <c r="K22" s="3">
         <v>39200</v>
@@ -1320,25 +1320,25 @@
         <v>17</v>
       </c>
       <c r="D23" s="3">
-        <v>2247200</v>
+        <v>2199000</v>
       </c>
       <c r="E23" s="3">
-        <v>3362200</v>
+        <v>3290100</v>
       </c>
       <c r="F23" s="3">
-        <v>1958500</v>
+        <v>1916500</v>
       </c>
       <c r="G23" s="3">
-        <v>885000</v>
+        <v>866000</v>
       </c>
       <c r="H23" s="3">
-        <v>181800</v>
+        <v>177900</v>
       </c>
       <c r="I23" s="3">
-        <v>69200</v>
+        <v>67700</v>
       </c>
       <c r="J23" s="3">
-        <v>247100</v>
+        <v>241800</v>
       </c>
       <c r="K23" s="3">
         <v>151900</v>
@@ -1365,25 +1365,25 @@
         <v>18</v>
       </c>
       <c r="D24" s="3">
-        <v>300200</v>
+        <v>293700</v>
       </c>
       <c r="E24" s="3">
-        <v>572900</v>
+        <v>560600</v>
       </c>
       <c r="F24" s="3">
-        <v>212100</v>
+        <v>207500</v>
       </c>
       <c r="G24" s="3">
-        <v>23600</v>
+        <v>23100</v>
       </c>
       <c r="H24" s="3">
-        <v>-12500</v>
+        <v>-12200</v>
       </c>
       <c r="I24" s="3">
-        <v>-14500</v>
+        <v>-14200</v>
       </c>
       <c r="J24" s="3">
-        <v>37000</v>
+        <v>36200</v>
       </c>
       <c r="K24" s="3">
         <v>30800</v>
@@ -1455,25 +1455,25 @@
         <v>20</v>
       </c>
       <c r="D26" s="3">
-        <v>1947000</v>
+        <v>1905200</v>
       </c>
       <c r="E26" s="3">
-        <v>2789300</v>
+        <v>2729400</v>
       </c>
       <c r="F26" s="3">
-        <v>1746500</v>
+        <v>1709000</v>
       </c>
       <c r="G26" s="3">
-        <v>861300</v>
+        <v>842900</v>
       </c>
       <c r="H26" s="3">
-        <v>194200</v>
+        <v>190100</v>
       </c>
       <c r="I26" s="3">
-        <v>83800</v>
+        <v>82000</v>
       </c>
       <c r="J26" s="3">
-        <v>210100</v>
+        <v>205600</v>
       </c>
       <c r="K26" s="3">
         <v>121100</v>
@@ -1500,25 +1500,25 @@
         <v>21</v>
       </c>
       <c r="D27" s="3">
-        <v>1932800</v>
+        <v>1891300</v>
       </c>
       <c r="E27" s="3">
-        <v>2763300</v>
+        <v>2704000</v>
       </c>
       <c r="F27" s="3">
-        <v>1767700</v>
+        <v>1729700</v>
       </c>
       <c r="G27" s="3">
-        <v>925000</v>
+        <v>905200</v>
       </c>
       <c r="H27" s="3">
-        <v>307600</v>
+        <v>301000</v>
       </c>
       <c r="I27" s="3">
-        <v>224100</v>
+        <v>219300</v>
       </c>
       <c r="J27" s="3">
-        <v>305100</v>
+        <v>298600</v>
       </c>
       <c r="K27" s="3">
         <v>260700</v>
@@ -1725,25 +1725,25 @@
         <v>26</v>
       </c>
       <c r="D32" s="3">
-        <v>-443700</v>
+        <v>-434200</v>
       </c>
       <c r="E32" s="3">
-        <v>-113800</v>
+        <v>-111300</v>
       </c>
       <c r="F32" s="3">
-        <v>-379800</v>
+        <v>-371700</v>
       </c>
       <c r="G32" s="3">
-        <v>-251100</v>
+        <v>-245700</v>
       </c>
       <c r="H32" s="3">
-        <v>-121500</v>
+        <v>-118900</v>
       </c>
       <c r="I32" s="3">
-        <v>25300</v>
+        <v>24700</v>
       </c>
       <c r="J32" s="3">
-        <v>-145200</v>
+        <v>-142100</v>
       </c>
       <c r="K32" s="3">
         <v>-47800</v>
@@ -1770,25 +1770,25 @@
         <v>27</v>
       </c>
       <c r="D33" s="3">
-        <v>1932800</v>
+        <v>1891300</v>
       </c>
       <c r="E33" s="3">
-        <v>2763300</v>
+        <v>2704000</v>
       </c>
       <c r="F33" s="3">
-        <v>1767700</v>
+        <v>1729700</v>
       </c>
       <c r="G33" s="3">
-        <v>925000</v>
+        <v>905200</v>
       </c>
       <c r="H33" s="3">
-        <v>307600</v>
+        <v>301000</v>
       </c>
       <c r="I33" s="3">
-        <v>224100</v>
+        <v>219300</v>
       </c>
       <c r="J33" s="3">
-        <v>305100</v>
+        <v>298600</v>
       </c>
       <c r="K33" s="3">
         <v>260700</v>
@@ -1860,25 +1860,25 @@
         <v>29</v>
       </c>
       <c r="D35" s="3">
-        <v>1932800</v>
+        <v>1891300</v>
       </c>
       <c r="E35" s="3">
-        <v>2763300</v>
+        <v>2704000</v>
       </c>
       <c r="F35" s="3">
-        <v>1767700</v>
+        <v>1729700</v>
       </c>
       <c r="G35" s="3">
-        <v>925000</v>
+        <v>905200</v>
       </c>
       <c r="H35" s="3">
-        <v>307600</v>
+        <v>301000</v>
       </c>
       <c r="I35" s="3">
-        <v>224100</v>
+        <v>219300</v>
       </c>
       <c r="J35" s="3">
-        <v>305100</v>
+        <v>298600</v>
       </c>
       <c r="K35" s="3">
         <v>260700</v>
@@ -1993,25 +1993,25 @@
         <v>33</v>
       </c>
       <c r="D41" s="3">
-        <v>4200600</v>
+        <v>4110500</v>
       </c>
       <c r="E41" s="3">
-        <v>5508300</v>
+        <v>5390100</v>
       </c>
       <c r="F41" s="3">
-        <v>4202800</v>
+        <v>4112600</v>
       </c>
       <c r="G41" s="3">
-        <v>2980400</v>
+        <v>2916400</v>
       </c>
       <c r="H41" s="3">
-        <v>3026200</v>
+        <v>2961200</v>
       </c>
       <c r="I41" s="3">
-        <v>2651200</v>
+        <v>2594400</v>
       </c>
       <c r="J41" s="3">
-        <v>2588300</v>
+        <v>2532700</v>
       </c>
       <c r="K41" s="3">
         <v>1805100</v>
@@ -2038,25 +2038,25 @@
         <v>34</v>
       </c>
       <c r="D42" s="3">
-        <v>390700</v>
+        <v>382300</v>
       </c>
       <c r="E42" s="3">
-        <v>151500</v>
+        <v>148300</v>
       </c>
       <c r="F42" s="3">
-        <v>299400</v>
+        <v>293000</v>
       </c>
       <c r="G42" s="3">
-        <v>38600</v>
+        <v>37700</v>
       </c>
       <c r="H42" s="3">
-        <v>22900</v>
+        <v>22400</v>
       </c>
       <c r="I42" s="3">
-        <v>16700</v>
+        <v>16400</v>
       </c>
       <c r="J42" s="3">
-        <v>22700</v>
+        <v>22200</v>
       </c>
       <c r="K42" s="3">
         <v>22400</v>
@@ -2083,25 +2083,25 @@
         <v>35</v>
       </c>
       <c r="D43" s="3">
-        <v>1050900</v>
+        <v>1028400</v>
       </c>
       <c r="E43" s="3">
-        <v>1242100</v>
+        <v>1215500</v>
       </c>
       <c r="F43" s="3">
-        <v>1152600</v>
+        <v>1127800</v>
       </c>
       <c r="G43" s="3">
-        <v>926500</v>
+        <v>906700</v>
       </c>
       <c r="H43" s="3">
-        <v>843700</v>
+        <v>825600</v>
       </c>
       <c r="I43" s="3">
-        <v>782600</v>
+        <v>765800</v>
       </c>
       <c r="J43" s="3">
-        <v>718000</v>
+        <v>702600</v>
       </c>
       <c r="K43" s="3">
         <v>752500</v>
@@ -2128,25 +2128,25 @@
         <v>36</v>
       </c>
       <c r="D44" s="3">
-        <v>1131700</v>
+        <v>1107400</v>
       </c>
       <c r="E44" s="3">
-        <v>984600</v>
+        <v>963500</v>
       </c>
       <c r="F44" s="3">
-        <v>729200</v>
+        <v>713600</v>
       </c>
       <c r="G44" s="3">
-        <v>714700</v>
+        <v>699400</v>
       </c>
       <c r="H44" s="3">
-        <v>688100</v>
+        <v>673400</v>
       </c>
       <c r="I44" s="3">
-        <v>576900</v>
+        <v>564500</v>
       </c>
       <c r="J44" s="3">
-        <v>578600</v>
+        <v>566200</v>
       </c>
       <c r="K44" s="3">
         <v>532900</v>
@@ -2173,25 +2173,25 @@
         <v>37</v>
       </c>
       <c r="D45" s="3">
-        <v>96400</v>
+        <v>94300</v>
       </c>
       <c r="E45" s="3">
-        <v>111100</v>
+        <v>108700</v>
       </c>
       <c r="F45" s="3">
-        <v>1008500</v>
+        <v>986800</v>
       </c>
       <c r="G45" s="3">
-        <v>546700</v>
+        <v>535000</v>
       </c>
       <c r="H45" s="3">
-        <v>291700</v>
+        <v>285400</v>
       </c>
       <c r="I45" s="3">
-        <v>446900</v>
+        <v>437400</v>
       </c>
       <c r="J45" s="3">
-        <v>502400</v>
+        <v>491600</v>
       </c>
       <c r="K45" s="3">
         <v>350400</v>
@@ -2218,25 +2218,25 @@
         <v>38</v>
       </c>
       <c r="D46" s="3">
-        <v>6870300</v>
+        <v>6722900</v>
       </c>
       <c r="E46" s="3">
-        <v>7997600</v>
+        <v>7826000</v>
       </c>
       <c r="F46" s="3">
-        <v>7392400</v>
+        <v>7233800</v>
       </c>
       <c r="G46" s="3">
-        <v>5206900</v>
+        <v>5095100</v>
       </c>
       <c r="H46" s="3">
-        <v>4872600</v>
+        <v>4768000</v>
       </c>
       <c r="I46" s="3">
-        <v>4474400</v>
+        <v>4378400</v>
       </c>
       <c r="J46" s="3">
-        <v>4410000</v>
+        <v>4315400</v>
       </c>
       <c r="K46" s="3">
         <v>3463200</v>
@@ -2263,25 +2263,25 @@
         <v>39</v>
       </c>
       <c r="D47" s="3">
-        <v>2353100</v>
+        <v>2302600</v>
       </c>
       <c r="E47" s="3">
-        <v>2055300</v>
+        <v>2011200</v>
       </c>
       <c r="F47" s="3">
-        <v>2299000</v>
+        <v>2249700</v>
       </c>
       <c r="G47" s="3">
-        <v>1793000</v>
+        <v>1754500</v>
       </c>
       <c r="H47" s="3">
-        <v>1310200</v>
+        <v>1282100</v>
       </c>
       <c r="I47" s="3">
-        <v>1061800</v>
+        <v>1039000</v>
       </c>
       <c r="J47" s="3">
-        <v>1078200</v>
+        <v>1055000</v>
       </c>
       <c r="K47" s="3">
         <v>1089900</v>
@@ -2308,25 +2308,25 @@
         <v>40</v>
       </c>
       <c r="D48" s="3">
-        <v>7949400</v>
+        <v>7778800</v>
       </c>
       <c r="E48" s="3">
-        <v>6275700</v>
+        <v>6141000</v>
       </c>
       <c r="F48" s="3">
-        <v>4607500</v>
+        <v>4508600</v>
       </c>
       <c r="G48" s="3">
-        <v>4471700</v>
+        <v>4375800</v>
       </c>
       <c r="H48" s="3">
-        <v>5035000</v>
+        <v>4927000</v>
       </c>
       <c r="I48" s="3">
-        <v>5498500</v>
+        <v>5380500</v>
       </c>
       <c r="J48" s="3">
-        <v>6529000</v>
+        <v>6388900</v>
       </c>
       <c r="K48" s="3">
         <v>7090200</v>
@@ -2353,25 +2353,25 @@
         <v>41</v>
       </c>
       <c r="D49" s="3">
-        <v>138600</v>
+        <v>135600</v>
       </c>
       <c r="E49" s="3">
-        <v>135500</v>
+        <v>132600</v>
       </c>
       <c r="F49" s="3">
-        <v>115500</v>
+        <v>113000</v>
       </c>
       <c r="G49" s="3">
-        <v>154600</v>
+        <v>151300</v>
       </c>
       <c r="H49" s="3">
-        <v>164700</v>
+        <v>161200</v>
       </c>
       <c r="I49" s="3">
-        <v>94800</v>
+        <v>92800</v>
       </c>
       <c r="J49" s="3">
-        <v>120000</v>
+        <v>117500</v>
       </c>
       <c r="K49" s="3">
         <v>128200</v>
@@ -2488,25 +2488,25 @@
         <v>44</v>
       </c>
       <c r="D52" s="3">
-        <v>409200</v>
+        <v>400400</v>
       </c>
       <c r="E52" s="3">
-        <v>428400</v>
+        <v>419200</v>
       </c>
       <c r="F52" s="3">
-        <v>303300</v>
+        <v>296800</v>
       </c>
       <c r="G52" s="3">
-        <v>337400</v>
+        <v>330100</v>
       </c>
       <c r="H52" s="3">
-        <v>348700</v>
+        <v>341200</v>
       </c>
       <c r="I52" s="3">
-        <v>424800</v>
+        <v>415700</v>
       </c>
       <c r="J52" s="3">
-        <v>351800</v>
+        <v>344200</v>
       </c>
       <c r="K52" s="3">
         <v>350100</v>
@@ -2578,25 +2578,25 @@
         <v>46</v>
       </c>
       <c r="D54" s="3">
-        <v>17720600</v>
+        <v>17340400</v>
       </c>
       <c r="E54" s="3">
-        <v>16892400</v>
+        <v>16529900</v>
       </c>
       <c r="F54" s="3">
-        <v>14717700</v>
+        <v>14401900</v>
       </c>
       <c r="G54" s="3">
-        <v>11963500</v>
+        <v>11706800</v>
       </c>
       <c r="H54" s="3">
-        <v>11731200</v>
+        <v>11479500</v>
       </c>
       <c r="I54" s="3">
-        <v>11554300</v>
+        <v>11306400</v>
       </c>
       <c r="J54" s="3">
-        <v>12489000</v>
+        <v>12221000</v>
       </c>
       <c r="K54" s="3">
         <v>12121600</v>
@@ -2661,25 +2661,25 @@
         <v>49</v>
       </c>
       <c r="D57" s="3">
-        <v>238500</v>
+        <v>233400</v>
       </c>
       <c r="E57" s="3">
-        <v>284700</v>
+        <v>278500</v>
       </c>
       <c r="F57" s="3">
-        <v>265100</v>
+        <v>259400</v>
       </c>
       <c r="G57" s="3">
-        <v>249200</v>
+        <v>243800</v>
       </c>
       <c r="H57" s="3">
-        <v>281300</v>
+        <v>275300</v>
       </c>
       <c r="I57" s="3">
-        <v>215500</v>
+        <v>210900</v>
       </c>
       <c r="J57" s="3">
-        <v>207100</v>
+        <v>202700</v>
       </c>
       <c r="K57" s="3">
         <v>214900</v>
@@ -2706,25 +2706,25 @@
         <v>50</v>
       </c>
       <c r="D58" s="3">
-        <v>952300</v>
+        <v>931900</v>
       </c>
       <c r="E58" s="3">
-        <v>257400</v>
+        <v>251900</v>
       </c>
       <c r="F58" s="3">
-        <v>1261700</v>
+        <v>1234600</v>
       </c>
       <c r="G58" s="3">
-        <v>1223000</v>
+        <v>1196700</v>
       </c>
       <c r="H58" s="3">
-        <v>1184600</v>
+        <v>1159200</v>
       </c>
       <c r="I58" s="3">
-        <v>577600</v>
+        <v>565200</v>
       </c>
       <c r="J58" s="3">
-        <v>1673500</v>
+        <v>1637600</v>
       </c>
       <c r="K58" s="3">
         <v>973500</v>
@@ -2751,25 +2751,25 @@
         <v>51</v>
       </c>
       <c r="D59" s="3">
-        <v>1947000</v>
+        <v>1905200</v>
       </c>
       <c r="E59" s="3">
-        <v>2898300</v>
+        <v>2836100</v>
       </c>
       <c r="F59" s="3">
-        <v>1815100</v>
+        <v>1776100</v>
       </c>
       <c r="G59" s="3">
-        <v>1007400</v>
+        <v>985800</v>
       </c>
       <c r="H59" s="3">
-        <v>838400</v>
+        <v>820400</v>
       </c>
       <c r="I59" s="3">
-        <v>788200</v>
+        <v>771300</v>
       </c>
       <c r="J59" s="3">
-        <v>910000</v>
+        <v>890500</v>
       </c>
       <c r="K59" s="3">
         <v>1068200</v>
@@ -2796,25 +2796,25 @@
         <v>52</v>
       </c>
       <c r="D60" s="3">
-        <v>3137800</v>
+        <v>3070400</v>
       </c>
       <c r="E60" s="3">
-        <v>3440400</v>
+        <v>3366600</v>
       </c>
       <c r="F60" s="3">
-        <v>3341800</v>
+        <v>3270100</v>
       </c>
       <c r="G60" s="3">
-        <v>2479500</v>
+        <v>2426300</v>
       </c>
       <c r="H60" s="3">
-        <v>2304300</v>
+        <v>2254900</v>
       </c>
       <c r="I60" s="3">
-        <v>1581300</v>
+        <v>1547400</v>
       </c>
       <c r="J60" s="3">
-        <v>2790700</v>
+        <v>2730800</v>
       </c>
       <c r="K60" s="3">
         <v>2256500</v>
@@ -2841,25 +2841,25 @@
         <v>53</v>
       </c>
       <c r="D61" s="3">
-        <v>1588100</v>
+        <v>1554100</v>
       </c>
       <c r="E61" s="3">
-        <v>1428500</v>
+        <v>1397800</v>
       </c>
       <c r="F61" s="3">
-        <v>1405100</v>
+        <v>1375000</v>
       </c>
       <c r="G61" s="3">
-        <v>944300</v>
+        <v>924000</v>
       </c>
       <c r="H61" s="3">
-        <v>1690600</v>
+        <v>1654400</v>
       </c>
       <c r="I61" s="3">
-        <v>2125900</v>
+        <v>2080200</v>
       </c>
       <c r="J61" s="3">
-        <v>1689700</v>
+        <v>1653400</v>
       </c>
       <c r="K61" s="3">
         <v>1903800</v>
@@ -2886,25 +2886,25 @@
         <v>54</v>
       </c>
       <c r="D62" s="3">
-        <v>1599700</v>
+        <v>1565300</v>
       </c>
       <c r="E62" s="3">
-        <v>1393100</v>
+        <v>1363200</v>
       </c>
       <c r="F62" s="3">
-        <v>1059400</v>
+        <v>1036700</v>
       </c>
       <c r="G62" s="3">
-        <v>1068000</v>
+        <v>1045100</v>
       </c>
       <c r="H62" s="3">
-        <v>1169700</v>
+        <v>1144600</v>
       </c>
       <c r="I62" s="3">
-        <v>1302000</v>
+        <v>1274100</v>
       </c>
       <c r="J62" s="3">
-        <v>1225800</v>
+        <v>1199500</v>
       </c>
       <c r="K62" s="3">
         <v>1103700</v>
@@ -3066,25 +3066,25 @@
         <v>57</v>
       </c>
       <c r="D66" s="3">
-        <v>6336400</v>
+        <v>6200400</v>
       </c>
       <c r="E66" s="3">
-        <v>6272900</v>
+        <v>6138300</v>
       </c>
       <c r="F66" s="3">
-        <v>5813400</v>
+        <v>5688700</v>
       </c>
       <c r="G66" s="3">
-        <v>4495400</v>
+        <v>4399000</v>
       </c>
       <c r="H66" s="3">
-        <v>5177600</v>
+        <v>5066500</v>
       </c>
       <c r="I66" s="3">
-        <v>5024000</v>
+        <v>4916200</v>
       </c>
       <c r="J66" s="3">
-        <v>5736500</v>
+        <v>5613400</v>
       </c>
       <c r="K66" s="3">
         <v>5331900</v>
@@ -3310,25 +3310,25 @@
         <v>63</v>
       </c>
       <c r="D72" s="3">
-        <v>6878400</v>
+        <v>6730800</v>
       </c>
       <c r="E72" s="3">
-        <v>6409200</v>
+        <v>6271700</v>
       </c>
       <c r="F72" s="3">
-        <v>3656300</v>
+        <v>3577800</v>
       </c>
       <c r="G72" s="3">
-        <v>2540800</v>
+        <v>2486300</v>
       </c>
       <c r="H72" s="3">
-        <v>1937900</v>
+        <v>1896400</v>
       </c>
       <c r="I72" s="3">
-        <v>1951700</v>
+        <v>1909900</v>
       </c>
       <c r="J72" s="3">
-        <v>1523200</v>
+        <v>1490500</v>
       </c>
       <c r="K72" s="3">
         <v>1494000</v>
@@ -3490,25 +3490,25 @@
         <v>67</v>
       </c>
       <c r="D76" s="3">
-        <v>11384200</v>
+        <v>11140000</v>
       </c>
       <c r="E76" s="3">
-        <v>10619500</v>
+        <v>10391700</v>
       </c>
       <c r="F76" s="3">
-        <v>8904200</v>
+        <v>8713200</v>
       </c>
       <c r="G76" s="3">
-        <v>7468100</v>
+        <v>7307800</v>
       </c>
       <c r="H76" s="3">
-        <v>6553600</v>
+        <v>6413000</v>
       </c>
       <c r="I76" s="3">
-        <v>6530300</v>
+        <v>6390200</v>
       </c>
       <c r="J76" s="3">
-        <v>6752500</v>
+        <v>6607600</v>
       </c>
       <c r="K76" s="3">
         <v>6789800</v>
@@ -3630,25 +3630,25 @@
         <v>27</v>
       </c>
       <c r="D81" s="3">
-        <v>1932800</v>
+        <v>1891300</v>
       </c>
       <c r="E81" s="3">
-        <v>2763300</v>
+        <v>2704000</v>
       </c>
       <c r="F81" s="3">
-        <v>1767700</v>
+        <v>1729700</v>
       </c>
       <c r="G81" s="3">
-        <v>925000</v>
+        <v>905200</v>
       </c>
       <c r="H81" s="3">
-        <v>307600</v>
+        <v>301000</v>
       </c>
       <c r="I81" s="3">
-        <v>224100</v>
+        <v>219300</v>
       </c>
       <c r="J81" s="3">
-        <v>305100</v>
+        <v>298600</v>
       </c>
       <c r="K81" s="3">
         <v>260700</v>
@@ -3694,25 +3694,25 @@
         <v>71</v>
       </c>
       <c r="D83" s="3">
-        <v>1282900</v>
+        <v>1255400</v>
       </c>
       <c r="E83" s="3">
-        <v>1399700</v>
+        <v>1369700</v>
       </c>
       <c r="F83" s="3">
-        <v>1491800</v>
+        <v>1459800</v>
       </c>
       <c r="G83" s="3">
-        <v>1549900</v>
+        <v>1516600</v>
       </c>
       <c r="H83" s="3">
-        <v>1565200</v>
+        <v>1531600</v>
       </c>
       <c r="I83" s="3">
-        <v>1649400</v>
+        <v>1614000</v>
       </c>
       <c r="J83" s="3">
-        <v>1682700</v>
+        <v>1646600</v>
       </c>
       <c r="K83" s="3">
         <v>1629700</v>
@@ -3964,25 +3964,25 @@
         <v>77</v>
       </c>
       <c r="D89" s="3">
-        <v>2725300</v>
+        <v>2666900</v>
       </c>
       <c r="E89" s="3">
-        <v>4622300</v>
+        <v>4523100</v>
       </c>
       <c r="F89" s="3">
-        <v>2863300</v>
+        <v>2801800</v>
       </c>
       <c r="G89" s="3">
-        <v>2083500</v>
+        <v>2038800</v>
       </c>
       <c r="H89" s="3">
-        <v>1739900</v>
+        <v>1702600</v>
       </c>
       <c r="I89" s="3">
-        <v>1614100</v>
+        <v>1579500</v>
       </c>
       <c r="J89" s="3">
-        <v>1662900</v>
+        <v>1627200</v>
       </c>
       <c r="K89" s="3">
         <v>1456200</v>
@@ -4028,25 +4028,25 @@
         <v>79</v>
       </c>
       <c r="D91" s="3">
-        <v>-2898800</v>
+        <v>-2836600</v>
       </c>
       <c r="E91" s="3">
-        <v>-2539200</v>
+        <v>-2484800</v>
       </c>
       <c r="F91" s="3">
-        <v>-1522200</v>
+        <v>-1489600</v>
       </c>
       <c r="G91" s="3">
-        <v>-834900</v>
+        <v>-817000</v>
       </c>
       <c r="H91" s="3">
-        <v>-523500</v>
+        <v>-512200</v>
       </c>
       <c r="I91" s="3">
-        <v>-620800</v>
+        <v>-607500</v>
       </c>
       <c r="J91" s="3">
-        <v>-1401800</v>
+        <v>-1371800</v>
       </c>
       <c r="K91" s="3">
         <v>-2870400</v>
@@ -4163,25 +4163,25 @@
         <v>82</v>
       </c>
       <c r="D94" s="3">
-        <v>-3098900</v>
+        <v>-3032400</v>
       </c>
       <c r="E94" s="3">
-        <v>-1724800</v>
+        <v>-1687800</v>
       </c>
       <c r="F94" s="3">
-        <v>-1970000</v>
+        <v>-1927700</v>
       </c>
       <c r="G94" s="3">
-        <v>-1271100</v>
+        <v>-1243900</v>
       </c>
       <c r="H94" s="3">
-        <v>-1004000</v>
+        <v>-982400</v>
       </c>
       <c r="I94" s="3">
-        <v>-491200</v>
+        <v>-480600</v>
       </c>
       <c r="J94" s="3">
-        <v>-1122300</v>
+        <v>-1098200</v>
       </c>
       <c r="K94" s="3">
         <v>-2510700</v>
@@ -4227,25 +4227,25 @@
         <v>84</v>
       </c>
       <c r="D96" s="3">
-        <v>-1426500</v>
+        <v>-1395900</v>
       </c>
       <c r="E96" s="3">
-        <v>-1186600</v>
+        <v>-1161200</v>
       </c>
       <c r="F96" s="3">
-        <v>-629700</v>
+        <v>-616200</v>
       </c>
       <c r="G96" s="3">
-        <v>-309500</v>
+        <v>-302800</v>
       </c>
       <c r="H96" s="3">
-        <v>-219000</v>
+        <v>-214300</v>
       </c>
       <c r="I96" s="3">
-        <v>-271200</v>
+        <v>-265400</v>
       </c>
       <c r="J96" s="3">
-        <v>-193400</v>
+        <v>-189300</v>
       </c>
       <c r="K96" s="3">
         <v>-216500</v>
@@ -4407,25 +4407,25 @@
         <v>88</v>
       </c>
       <c r="D100" s="3">
-        <v>-921700</v>
+        <v>-902000</v>
       </c>
       <c r="E100" s="3">
-        <v>-1814400</v>
+        <v>-1775500</v>
       </c>
       <c r="F100" s="3">
-        <v>395800</v>
+        <v>387300</v>
       </c>
       <c r="G100" s="3">
-        <v>-811300</v>
+        <v>-793900</v>
       </c>
       <c r="H100" s="3">
-        <v>-312700</v>
+        <v>-306000</v>
       </c>
       <c r="I100" s="3">
-        <v>-1061100</v>
+        <v>-1038400</v>
       </c>
       <c r="J100" s="3">
-        <v>290300</v>
+        <v>284100</v>
       </c>
       <c r="K100" s="3">
         <v>1216200</v>
@@ -4452,25 +4452,25 @@
         <v>89</v>
       </c>
       <c r="D101" s="3">
-        <v>-12400</v>
+        <v>-12200</v>
       </c>
       <c r="E101" s="3">
-        <v>222400</v>
+        <v>217600</v>
       </c>
       <c r="F101" s="3">
-        <v>-66700</v>
+        <v>-65300</v>
       </c>
       <c r="G101" s="3">
-        <v>-46800</v>
+        <v>-45800</v>
       </c>
       <c r="H101" s="3">
-        <v>-48300</v>
+        <v>-47300</v>
       </c>
       <c r="I101" s="3">
-        <v>1200</v>
+        <v>1100</v>
       </c>
       <c r="J101" s="3">
-        <v>-67300</v>
+        <v>-65900</v>
       </c>
       <c r="K101" s="3">
         <v>-27300</v>
@@ -4497,25 +4497,25 @@
         <v>90</v>
       </c>
       <c r="D102" s="3">
-        <v>-1307700</v>
+        <v>-1279600</v>
       </c>
       <c r="E102" s="3">
-        <v>1305500</v>
+        <v>1277500</v>
       </c>
       <c r="F102" s="3">
-        <v>1222400</v>
+        <v>1196200</v>
       </c>
       <c r="G102" s="3">
-        <v>-45800</v>
+        <v>-44800</v>
       </c>
       <c r="H102" s="3">
-        <v>374900</v>
+        <v>366900</v>
       </c>
       <c r="I102" s="3">
-        <v>63000</v>
+        <v>61600</v>
       </c>
       <c r="J102" s="3">
-        <v>763600</v>
+        <v>747200</v>
       </c>
       <c r="K102" s="3">
         <v>134400</v>

--- a/AAII_Financials/Yearly/UMC_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/UMC_YR_FIN.xlsx
@@ -726,25 +726,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>6900700</v>
+        <v>6967500</v>
       </c>
       <c r="E8" s="3">
-        <v>8642700</v>
+        <v>8726300</v>
       </c>
       <c r="F8" s="3">
-        <v>6605500</v>
+        <v>6669400</v>
       </c>
       <c r="G8" s="3">
-        <v>5483200</v>
+        <v>5536300</v>
       </c>
       <c r="H8" s="3">
-        <v>4595700</v>
+        <v>4640200</v>
       </c>
       <c r="I8" s="3">
-        <v>4690300</v>
+        <v>4735700</v>
       </c>
       <c r="J8" s="3">
-        <v>4629300</v>
+        <v>4674100</v>
       </c>
       <c r="K8" s="3">
         <v>4635700</v>
@@ -771,25 +771,25 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>4489900</v>
+        <v>4533300</v>
       </c>
       <c r="E9" s="3">
-        <v>4742700</v>
+        <v>4788600</v>
       </c>
       <c r="F9" s="3">
-        <v>4371200</v>
+        <v>4413500</v>
       </c>
       <c r="G9" s="3">
-        <v>4273900</v>
+        <v>4315300</v>
       </c>
       <c r="H9" s="3">
-        <v>3934800</v>
+        <v>3972800</v>
       </c>
       <c r="I9" s="3">
-        <v>3982100</v>
+        <v>4020600</v>
       </c>
       <c r="J9" s="3">
-        <v>3790300</v>
+        <v>3826900</v>
       </c>
       <c r="K9" s="3">
         <v>3683300</v>
@@ -816,25 +816,25 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>2410800</v>
+        <v>2434200</v>
       </c>
       <c r="E10" s="3">
-        <v>3900000</v>
+        <v>3937700</v>
       </c>
       <c r="F10" s="3">
-        <v>2234300</v>
+        <v>2255900</v>
       </c>
       <c r="G10" s="3">
-        <v>1209300</v>
+        <v>1221000</v>
       </c>
       <c r="H10" s="3">
-        <v>661000</v>
+        <v>667400</v>
       </c>
       <c r="I10" s="3">
-        <v>708300</v>
+        <v>715100</v>
       </c>
       <c r="J10" s="3">
-        <v>839100</v>
+        <v>847200</v>
       </c>
       <c r="K10" s="3">
         <v>952400</v>
@@ -880,25 +880,25 @@
         <v>7</v>
       </c>
       <c r="D12" s="3">
-        <v>411900</v>
+        <v>415900</v>
       </c>
       <c r="E12" s="3">
-        <v>401700</v>
+        <v>405600</v>
       </c>
       <c r="F12" s="3">
-        <v>401100</v>
+        <v>405000</v>
       </c>
       <c r="G12" s="3">
-        <v>399900</v>
+        <v>403800</v>
       </c>
       <c r="H12" s="3">
-        <v>367800</v>
+        <v>371300</v>
       </c>
       <c r="I12" s="3">
-        <v>403900</v>
+        <v>407800</v>
       </c>
       <c r="J12" s="3">
-        <v>423900</v>
+        <v>428000</v>
       </c>
       <c r="K12" s="3">
         <v>424200</v>
@@ -970,7 +970,7 @@
         <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>-15300</v>
+        <v>-15500</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>91</v>
@@ -988,7 +988,7 @@
         <v>1400</v>
       </c>
       <c r="J14" s="3">
-        <v>29300</v>
+        <v>29600</v>
       </c>
       <c r="K14" s="3">
         <v>65100</v>
@@ -1076,25 +1076,25 @@
         <v>11</v>
       </c>
       <c r="D17" s="3">
-        <v>5090200</v>
+        <v>5139500</v>
       </c>
       <c r="E17" s="3">
-        <v>5408500</v>
+        <v>5460900</v>
       </c>
       <c r="F17" s="3">
-        <v>5002700</v>
+        <v>5051100</v>
       </c>
       <c r="G17" s="3">
-        <v>4800800</v>
+        <v>4847200</v>
       </c>
       <c r="H17" s="3">
-        <v>4445800</v>
+        <v>4488800</v>
       </c>
       <c r="I17" s="3">
-        <v>4512000</v>
+        <v>4555700</v>
       </c>
       <c r="J17" s="3">
-        <v>4454900</v>
+        <v>4498000</v>
       </c>
       <c r="K17" s="3">
         <v>4492400</v>
@@ -1121,25 +1121,25 @@
         <v>12</v>
       </c>
       <c r="D18" s="3">
-        <v>1810500</v>
+        <v>1828000</v>
       </c>
       <c r="E18" s="3">
-        <v>3234100</v>
+        <v>3265400</v>
       </c>
       <c r="F18" s="3">
-        <v>1602800</v>
+        <v>1618300</v>
       </c>
       <c r="G18" s="3">
-        <v>682400</v>
+        <v>689100</v>
       </c>
       <c r="H18" s="3">
-        <v>150000</v>
+        <v>151400</v>
       </c>
       <c r="I18" s="3">
-        <v>178300</v>
+        <v>180100</v>
       </c>
       <c r="J18" s="3">
-        <v>174400</v>
+        <v>176100</v>
       </c>
       <c r="K18" s="3">
         <v>143300</v>
@@ -1185,25 +1185,25 @@
         <v>14</v>
       </c>
       <c r="D20" s="3">
-        <v>434200</v>
+        <v>438400</v>
       </c>
       <c r="E20" s="3">
-        <v>111300</v>
+        <v>112400</v>
       </c>
       <c r="F20" s="3">
-        <v>371700</v>
+        <v>375300</v>
       </c>
       <c r="G20" s="3">
-        <v>245700</v>
+        <v>248100</v>
       </c>
       <c r="H20" s="3">
-        <v>118900</v>
+        <v>120000</v>
       </c>
       <c r="I20" s="3">
-        <v>-24700</v>
+        <v>-25000</v>
       </c>
       <c r="J20" s="3">
-        <v>142100</v>
+        <v>143500</v>
       </c>
       <c r="K20" s="3">
         <v>47800</v>
@@ -1230,25 +1230,25 @@
         <v>15</v>
       </c>
       <c r="D21" s="3">
-        <v>3495600</v>
+        <v>3529100</v>
       </c>
       <c r="E21" s="3">
-        <v>4710300</v>
+        <v>4755500</v>
       </c>
       <c r="F21" s="3">
-        <v>3429100</v>
+        <v>3461800</v>
       </c>
       <c r="G21" s="3">
-        <v>2439400</v>
+        <v>2462600</v>
       </c>
       <c r="H21" s="3">
-        <v>1795000</v>
+        <v>1811900</v>
       </c>
       <c r="I21" s="3">
-        <v>1761900</v>
+        <v>1778500</v>
       </c>
       <c r="J21" s="3">
-        <v>1957200</v>
+        <v>1975700</v>
       </c>
       <c r="K21" s="3">
         <v>1817200</v>
@@ -1275,25 +1275,25 @@
         <v>16</v>
       </c>
       <c r="D22" s="3">
-        <v>45700</v>
+        <v>46100</v>
       </c>
       <c r="E22" s="3">
-        <v>55400</v>
+        <v>55900</v>
       </c>
       <c r="F22" s="3">
-        <v>57900</v>
+        <v>58500</v>
       </c>
       <c r="G22" s="3">
-        <v>62200</v>
+        <v>62800</v>
       </c>
       <c r="H22" s="3">
-        <v>91000</v>
+        <v>91900</v>
       </c>
       <c r="I22" s="3">
-        <v>85900</v>
+        <v>86700</v>
       </c>
       <c r="J22" s="3">
-        <v>74600</v>
+        <v>75400</v>
       </c>
       <c r="K22" s="3">
         <v>39200</v>
@@ -1320,25 +1320,25 @@
         <v>17</v>
       </c>
       <c r="D23" s="3">
-        <v>2199000</v>
+        <v>2220300</v>
       </c>
       <c r="E23" s="3">
-        <v>3290100</v>
+        <v>3321900</v>
       </c>
       <c r="F23" s="3">
-        <v>1916500</v>
+        <v>1935100</v>
       </c>
       <c r="G23" s="3">
-        <v>866000</v>
+        <v>874400</v>
       </c>
       <c r="H23" s="3">
-        <v>177900</v>
+        <v>179600</v>
       </c>
       <c r="I23" s="3">
-        <v>67700</v>
+        <v>68400</v>
       </c>
       <c r="J23" s="3">
-        <v>241800</v>
+        <v>244200</v>
       </c>
       <c r="K23" s="3">
         <v>151900</v>
@@ -1365,25 +1365,25 @@
         <v>18</v>
       </c>
       <c r="D24" s="3">
-        <v>293700</v>
+        <v>296600</v>
       </c>
       <c r="E24" s="3">
-        <v>560600</v>
+        <v>566100</v>
       </c>
       <c r="F24" s="3">
-        <v>207500</v>
+        <v>209500</v>
       </c>
       <c r="G24" s="3">
-        <v>23100</v>
+        <v>23300</v>
       </c>
       <c r="H24" s="3">
-        <v>-12200</v>
+        <v>-12300</v>
       </c>
       <c r="I24" s="3">
-        <v>-14200</v>
+        <v>-14400</v>
       </c>
       <c r="J24" s="3">
-        <v>36200</v>
+        <v>36500</v>
       </c>
       <c r="K24" s="3">
         <v>30800</v>
@@ -1455,25 +1455,25 @@
         <v>20</v>
       </c>
       <c r="D26" s="3">
-        <v>1905200</v>
+        <v>1923700</v>
       </c>
       <c r="E26" s="3">
-        <v>2729400</v>
+        <v>2755900</v>
       </c>
       <c r="F26" s="3">
-        <v>1709000</v>
+        <v>1725600</v>
       </c>
       <c r="G26" s="3">
-        <v>842900</v>
+        <v>851000</v>
       </c>
       <c r="H26" s="3">
-        <v>190100</v>
+        <v>191900</v>
       </c>
       <c r="I26" s="3">
-        <v>82000</v>
+        <v>82800</v>
       </c>
       <c r="J26" s="3">
-        <v>205600</v>
+        <v>207600</v>
       </c>
       <c r="K26" s="3">
         <v>121100</v>
@@ -1500,25 +1500,25 @@
         <v>21</v>
       </c>
       <c r="D27" s="3">
-        <v>1891300</v>
+        <v>1909600</v>
       </c>
       <c r="E27" s="3">
-        <v>2704000</v>
+        <v>2730200</v>
       </c>
       <c r="F27" s="3">
-        <v>1729700</v>
+        <v>1746500</v>
       </c>
       <c r="G27" s="3">
-        <v>905200</v>
+        <v>913900</v>
       </c>
       <c r="H27" s="3">
-        <v>301000</v>
+        <v>303900</v>
       </c>
       <c r="I27" s="3">
-        <v>219300</v>
+        <v>221500</v>
       </c>
       <c r="J27" s="3">
-        <v>298600</v>
+        <v>301500</v>
       </c>
       <c r="K27" s="3">
         <v>260700</v>
@@ -1725,25 +1725,25 @@
         <v>26</v>
       </c>
       <c r="D32" s="3">
-        <v>-434200</v>
+        <v>-438400</v>
       </c>
       <c r="E32" s="3">
-        <v>-111300</v>
+        <v>-112400</v>
       </c>
       <c r="F32" s="3">
-        <v>-371700</v>
+        <v>-375300</v>
       </c>
       <c r="G32" s="3">
-        <v>-245700</v>
+        <v>-248100</v>
       </c>
       <c r="H32" s="3">
-        <v>-118900</v>
+        <v>-120000</v>
       </c>
       <c r="I32" s="3">
-        <v>24700</v>
+        <v>25000</v>
       </c>
       <c r="J32" s="3">
-        <v>-142100</v>
+        <v>-143500</v>
       </c>
       <c r="K32" s="3">
         <v>-47800</v>
@@ -1770,25 +1770,25 @@
         <v>27</v>
       </c>
       <c r="D33" s="3">
-        <v>1891300</v>
+        <v>1909600</v>
       </c>
       <c r="E33" s="3">
-        <v>2704000</v>
+        <v>2730200</v>
       </c>
       <c r="F33" s="3">
-        <v>1729700</v>
+        <v>1746500</v>
       </c>
       <c r="G33" s="3">
-        <v>905200</v>
+        <v>913900</v>
       </c>
       <c r="H33" s="3">
-        <v>301000</v>
+        <v>303900</v>
       </c>
       <c r="I33" s="3">
-        <v>219300</v>
+        <v>221500</v>
       </c>
       <c r="J33" s="3">
-        <v>298600</v>
+        <v>301500</v>
       </c>
       <c r="K33" s="3">
         <v>260700</v>
@@ -1860,25 +1860,25 @@
         <v>29</v>
       </c>
       <c r="D35" s="3">
-        <v>1891300</v>
+        <v>1909600</v>
       </c>
       <c r="E35" s="3">
-        <v>2704000</v>
+        <v>2730200</v>
       </c>
       <c r="F35" s="3">
-        <v>1729700</v>
+        <v>1746500</v>
       </c>
       <c r="G35" s="3">
-        <v>905200</v>
+        <v>913900</v>
       </c>
       <c r="H35" s="3">
-        <v>301000</v>
+        <v>303900</v>
       </c>
       <c r="I35" s="3">
-        <v>219300</v>
+        <v>221500</v>
       </c>
       <c r="J35" s="3">
-        <v>298600</v>
+        <v>301500</v>
       </c>
       <c r="K35" s="3">
         <v>260700</v>
@@ -1993,25 +1993,25 @@
         <v>33</v>
       </c>
       <c r="D41" s="3">
-        <v>4110500</v>
+        <v>4150300</v>
       </c>
       <c r="E41" s="3">
-        <v>5390100</v>
+        <v>5442300</v>
       </c>
       <c r="F41" s="3">
-        <v>4112600</v>
+        <v>4152400</v>
       </c>
       <c r="G41" s="3">
-        <v>2916400</v>
+        <v>2944600</v>
       </c>
       <c r="H41" s="3">
-        <v>2961200</v>
+        <v>2989900</v>
       </c>
       <c r="I41" s="3">
-        <v>2594400</v>
+        <v>2619400</v>
       </c>
       <c r="J41" s="3">
-        <v>2532700</v>
+        <v>2557200</v>
       </c>
       <c r="K41" s="3">
         <v>1805100</v>
@@ -2038,25 +2038,25 @@
         <v>34</v>
       </c>
       <c r="D42" s="3">
-        <v>382300</v>
+        <v>386000</v>
       </c>
       <c r="E42" s="3">
-        <v>148300</v>
+        <v>149700</v>
       </c>
       <c r="F42" s="3">
-        <v>293000</v>
+        <v>295800</v>
       </c>
       <c r="G42" s="3">
-        <v>37700</v>
+        <v>38100</v>
       </c>
       <c r="H42" s="3">
+        <v>22600</v>
+      </c>
+      <c r="I42" s="3">
+        <v>16500</v>
+      </c>
+      <c r="J42" s="3">
         <v>22400</v>
-      </c>
-      <c r="I42" s="3">
-        <v>16400</v>
-      </c>
-      <c r="J42" s="3">
-        <v>22200</v>
       </c>
       <c r="K42" s="3">
         <v>22400</v>
@@ -2083,25 +2083,25 @@
         <v>35</v>
       </c>
       <c r="D43" s="3">
-        <v>1028400</v>
+        <v>1038300</v>
       </c>
       <c r="E43" s="3">
-        <v>1215500</v>
+        <v>1227200</v>
       </c>
       <c r="F43" s="3">
-        <v>1127800</v>
+        <v>1138700</v>
       </c>
       <c r="G43" s="3">
-        <v>906700</v>
+        <v>915400</v>
       </c>
       <c r="H43" s="3">
-        <v>825600</v>
+        <v>833600</v>
       </c>
       <c r="I43" s="3">
-        <v>765800</v>
+        <v>773200</v>
       </c>
       <c r="J43" s="3">
-        <v>702600</v>
+        <v>709400</v>
       </c>
       <c r="K43" s="3">
         <v>752500</v>
@@ -2128,25 +2128,25 @@
         <v>36</v>
       </c>
       <c r="D44" s="3">
-        <v>1107400</v>
+        <v>1118200</v>
       </c>
       <c r="E44" s="3">
-        <v>963500</v>
+        <v>972800</v>
       </c>
       <c r="F44" s="3">
-        <v>713600</v>
+        <v>720500</v>
       </c>
       <c r="G44" s="3">
-        <v>699400</v>
+        <v>706100</v>
       </c>
       <c r="H44" s="3">
-        <v>673400</v>
+        <v>679900</v>
       </c>
       <c r="I44" s="3">
-        <v>564500</v>
+        <v>569900</v>
       </c>
       <c r="J44" s="3">
-        <v>566200</v>
+        <v>571600</v>
       </c>
       <c r="K44" s="3">
         <v>532900</v>
@@ -2173,25 +2173,25 @@
         <v>37</v>
       </c>
       <c r="D45" s="3">
-        <v>94300</v>
+        <v>95200</v>
       </c>
       <c r="E45" s="3">
-        <v>108700</v>
+        <v>109700</v>
       </c>
       <c r="F45" s="3">
-        <v>986800</v>
+        <v>996400</v>
       </c>
       <c r="G45" s="3">
-        <v>535000</v>
+        <v>540100</v>
       </c>
       <c r="H45" s="3">
-        <v>285400</v>
+        <v>288200</v>
       </c>
       <c r="I45" s="3">
-        <v>437400</v>
+        <v>441600</v>
       </c>
       <c r="J45" s="3">
-        <v>491600</v>
+        <v>496400</v>
       </c>
       <c r="K45" s="3">
         <v>350400</v>
@@ -2218,25 +2218,25 @@
         <v>38</v>
       </c>
       <c r="D46" s="3">
-        <v>6722900</v>
+        <v>6787900</v>
       </c>
       <c r="E46" s="3">
-        <v>7826000</v>
+        <v>7901700</v>
       </c>
       <c r="F46" s="3">
-        <v>7233800</v>
+        <v>7303800</v>
       </c>
       <c r="G46" s="3">
-        <v>5095100</v>
+        <v>5144400</v>
       </c>
       <c r="H46" s="3">
-        <v>4768000</v>
+        <v>4814100</v>
       </c>
       <c r="I46" s="3">
-        <v>4378400</v>
+        <v>4420800</v>
       </c>
       <c r="J46" s="3">
-        <v>4315400</v>
+        <v>4357100</v>
       </c>
       <c r="K46" s="3">
         <v>3463200</v>
@@ -2263,25 +2263,25 @@
         <v>39</v>
       </c>
       <c r="D47" s="3">
-        <v>2302600</v>
+        <v>2324900</v>
       </c>
       <c r="E47" s="3">
-        <v>2011200</v>
+        <v>2030600</v>
       </c>
       <c r="F47" s="3">
-        <v>2249700</v>
+        <v>2271400</v>
       </c>
       <c r="G47" s="3">
-        <v>1754500</v>
+        <v>1771500</v>
       </c>
       <c r="H47" s="3">
-        <v>1282100</v>
+        <v>1294500</v>
       </c>
       <c r="I47" s="3">
-        <v>1039000</v>
+        <v>1049100</v>
       </c>
       <c r="J47" s="3">
-        <v>1055000</v>
+        <v>1065300</v>
       </c>
       <c r="K47" s="3">
         <v>1089900</v>
@@ -2308,25 +2308,25 @@
         <v>40</v>
       </c>
       <c r="D48" s="3">
-        <v>7778800</v>
+        <v>7854100</v>
       </c>
       <c r="E48" s="3">
-        <v>6141000</v>
+        <v>6200400</v>
       </c>
       <c r="F48" s="3">
-        <v>4508600</v>
+        <v>4552200</v>
       </c>
       <c r="G48" s="3">
-        <v>4375800</v>
+        <v>4418100</v>
       </c>
       <c r="H48" s="3">
-        <v>4927000</v>
+        <v>4974600</v>
       </c>
       <c r="I48" s="3">
-        <v>5380500</v>
+        <v>5432500</v>
       </c>
       <c r="J48" s="3">
-        <v>6388900</v>
+        <v>6450700</v>
       </c>
       <c r="K48" s="3">
         <v>7090200</v>
@@ -2353,25 +2353,25 @@
         <v>41</v>
       </c>
       <c r="D49" s="3">
-        <v>135600</v>
+        <v>136900</v>
       </c>
       <c r="E49" s="3">
-        <v>132600</v>
+        <v>133900</v>
       </c>
       <c r="F49" s="3">
-        <v>113000</v>
+        <v>114100</v>
       </c>
       <c r="G49" s="3">
-        <v>151300</v>
+        <v>152700</v>
       </c>
       <c r="H49" s="3">
-        <v>161200</v>
+        <v>162800</v>
       </c>
       <c r="I49" s="3">
-        <v>92800</v>
+        <v>93700</v>
       </c>
       <c r="J49" s="3">
-        <v>117500</v>
+        <v>118600</v>
       </c>
       <c r="K49" s="3">
         <v>128200</v>
@@ -2488,25 +2488,25 @@
         <v>44</v>
       </c>
       <c r="D52" s="3">
-        <v>400400</v>
+        <v>404300</v>
       </c>
       <c r="E52" s="3">
-        <v>419200</v>
+        <v>423200</v>
       </c>
       <c r="F52" s="3">
-        <v>296800</v>
+        <v>299600</v>
       </c>
       <c r="G52" s="3">
-        <v>330100</v>
+        <v>333300</v>
       </c>
       <c r="H52" s="3">
-        <v>341200</v>
+        <v>344500</v>
       </c>
       <c r="I52" s="3">
-        <v>415700</v>
+        <v>419800</v>
       </c>
       <c r="J52" s="3">
-        <v>344200</v>
+        <v>347600</v>
       </c>
       <c r="K52" s="3">
         <v>350100</v>
@@ -2578,25 +2578,25 @@
         <v>46</v>
       </c>
       <c r="D54" s="3">
-        <v>17340400</v>
+        <v>17508100</v>
       </c>
       <c r="E54" s="3">
-        <v>16529900</v>
+        <v>16689900</v>
       </c>
       <c r="F54" s="3">
-        <v>14401900</v>
+        <v>14541200</v>
       </c>
       <c r="G54" s="3">
-        <v>11706800</v>
+        <v>11820000</v>
       </c>
       <c r="H54" s="3">
-        <v>11479500</v>
+        <v>11590600</v>
       </c>
       <c r="I54" s="3">
-        <v>11306400</v>
+        <v>11415800</v>
       </c>
       <c r="J54" s="3">
-        <v>12221000</v>
+        <v>12339200</v>
       </c>
       <c r="K54" s="3">
         <v>12121600</v>
@@ -2661,25 +2661,25 @@
         <v>49</v>
       </c>
       <c r="D57" s="3">
-        <v>233400</v>
+        <v>235600</v>
       </c>
       <c r="E57" s="3">
-        <v>278500</v>
+        <v>281200</v>
       </c>
       <c r="F57" s="3">
-        <v>259400</v>
+        <v>261900</v>
       </c>
       <c r="G57" s="3">
-        <v>243800</v>
+        <v>246200</v>
       </c>
       <c r="H57" s="3">
-        <v>275300</v>
+        <v>277900</v>
       </c>
       <c r="I57" s="3">
-        <v>210900</v>
+        <v>213000</v>
       </c>
       <c r="J57" s="3">
-        <v>202700</v>
+        <v>204600</v>
       </c>
       <c r="K57" s="3">
         <v>214900</v>
@@ -2706,25 +2706,25 @@
         <v>50</v>
       </c>
       <c r="D58" s="3">
-        <v>931900</v>
+        <v>940900</v>
       </c>
       <c r="E58" s="3">
-        <v>251900</v>
+        <v>254400</v>
       </c>
       <c r="F58" s="3">
-        <v>1234600</v>
+        <v>1246600</v>
       </c>
       <c r="G58" s="3">
-        <v>1196700</v>
+        <v>1208300</v>
       </c>
       <c r="H58" s="3">
-        <v>1159200</v>
+        <v>1170400</v>
       </c>
       <c r="I58" s="3">
-        <v>565200</v>
+        <v>570600</v>
       </c>
       <c r="J58" s="3">
-        <v>1637600</v>
+        <v>1653500</v>
       </c>
       <c r="K58" s="3">
         <v>973500</v>
@@ -2751,25 +2751,25 @@
         <v>51</v>
       </c>
       <c r="D59" s="3">
-        <v>1905200</v>
+        <v>1923600</v>
       </c>
       <c r="E59" s="3">
-        <v>2836100</v>
+        <v>2863600</v>
       </c>
       <c r="F59" s="3">
-        <v>1776100</v>
+        <v>1793300</v>
       </c>
       <c r="G59" s="3">
-        <v>985800</v>
+        <v>995300</v>
       </c>
       <c r="H59" s="3">
-        <v>820400</v>
+        <v>828400</v>
       </c>
       <c r="I59" s="3">
-        <v>771300</v>
+        <v>778800</v>
       </c>
       <c r="J59" s="3">
-        <v>890500</v>
+        <v>899100</v>
       </c>
       <c r="K59" s="3">
         <v>1068200</v>
@@ -2796,25 +2796,25 @@
         <v>52</v>
       </c>
       <c r="D60" s="3">
-        <v>3070400</v>
+        <v>3100200</v>
       </c>
       <c r="E60" s="3">
-        <v>3366600</v>
+        <v>3399200</v>
       </c>
       <c r="F60" s="3">
-        <v>3270100</v>
+        <v>3301800</v>
       </c>
       <c r="G60" s="3">
-        <v>2426300</v>
+        <v>2449800</v>
       </c>
       <c r="H60" s="3">
-        <v>2254900</v>
+        <v>2276700</v>
       </c>
       <c r="I60" s="3">
-        <v>1547400</v>
+        <v>1562300</v>
       </c>
       <c r="J60" s="3">
-        <v>2730800</v>
+        <v>2757200</v>
       </c>
       <c r="K60" s="3">
         <v>2256500</v>
@@ -2841,25 +2841,25 @@
         <v>53</v>
       </c>
       <c r="D61" s="3">
-        <v>1554100</v>
+        <v>1569100</v>
       </c>
       <c r="E61" s="3">
-        <v>1397800</v>
+        <v>1411400</v>
       </c>
       <c r="F61" s="3">
-        <v>1375000</v>
+        <v>1388300</v>
       </c>
       <c r="G61" s="3">
-        <v>924000</v>
+        <v>933000</v>
       </c>
       <c r="H61" s="3">
-        <v>1654400</v>
+        <v>1670400</v>
       </c>
       <c r="I61" s="3">
-        <v>2080200</v>
+        <v>2100400</v>
       </c>
       <c r="J61" s="3">
-        <v>1653400</v>
+        <v>1669400</v>
       </c>
       <c r="K61" s="3">
         <v>1903800</v>
@@ -2886,25 +2886,25 @@
         <v>54</v>
       </c>
       <c r="D62" s="3">
-        <v>1565300</v>
+        <v>1580500</v>
       </c>
       <c r="E62" s="3">
-        <v>1363200</v>
+        <v>1376400</v>
       </c>
       <c r="F62" s="3">
-        <v>1036700</v>
+        <v>1046700</v>
       </c>
       <c r="G62" s="3">
-        <v>1045100</v>
+        <v>1055200</v>
       </c>
       <c r="H62" s="3">
-        <v>1144600</v>
+        <v>1155600</v>
       </c>
       <c r="I62" s="3">
-        <v>1274100</v>
+        <v>1286400</v>
       </c>
       <c r="J62" s="3">
-        <v>1199500</v>
+        <v>1211100</v>
       </c>
       <c r="K62" s="3">
         <v>1103700</v>
@@ -3066,25 +3066,25 @@
         <v>57</v>
       </c>
       <c r="D66" s="3">
-        <v>6200400</v>
+        <v>6260400</v>
       </c>
       <c r="E66" s="3">
-        <v>6138300</v>
+        <v>6197700</v>
       </c>
       <c r="F66" s="3">
-        <v>5688700</v>
+        <v>5743700</v>
       </c>
       <c r="G66" s="3">
-        <v>4399000</v>
+        <v>4441500</v>
       </c>
       <c r="H66" s="3">
-        <v>5066500</v>
+        <v>5115500</v>
       </c>
       <c r="I66" s="3">
-        <v>4916200</v>
+        <v>4963700</v>
       </c>
       <c r="J66" s="3">
-        <v>5613400</v>
+        <v>5667700</v>
       </c>
       <c r="K66" s="3">
         <v>5331900</v>
@@ -3310,25 +3310,25 @@
         <v>63</v>
       </c>
       <c r="D72" s="3">
-        <v>6730800</v>
+        <v>6795900</v>
       </c>
       <c r="E72" s="3">
-        <v>6271700</v>
+        <v>6332400</v>
       </c>
       <c r="F72" s="3">
-        <v>3577800</v>
+        <v>3612400</v>
       </c>
       <c r="G72" s="3">
-        <v>2486300</v>
+        <v>2510300</v>
       </c>
       <c r="H72" s="3">
-        <v>1896400</v>
+        <v>1914700</v>
       </c>
       <c r="I72" s="3">
-        <v>1909900</v>
+        <v>1928300</v>
       </c>
       <c r="J72" s="3">
-        <v>1490500</v>
+        <v>1504900</v>
       </c>
       <c r="K72" s="3">
         <v>1494000</v>
@@ -3490,25 +3490,25 @@
         <v>67</v>
       </c>
       <c r="D76" s="3">
-        <v>11140000</v>
+        <v>11247700</v>
       </c>
       <c r="E76" s="3">
-        <v>10391700</v>
+        <v>10492200</v>
       </c>
       <c r="F76" s="3">
-        <v>8713200</v>
+        <v>8797500</v>
       </c>
       <c r="G76" s="3">
-        <v>7307800</v>
+        <v>7378500</v>
       </c>
       <c r="H76" s="3">
-        <v>6413000</v>
+        <v>6475000</v>
       </c>
       <c r="I76" s="3">
-        <v>6390200</v>
+        <v>6452000</v>
       </c>
       <c r="J76" s="3">
-        <v>6607600</v>
+        <v>6671600</v>
       </c>
       <c r="K76" s="3">
         <v>6789800</v>
@@ -3630,25 +3630,25 @@
         <v>27</v>
       </c>
       <c r="D81" s="3">
-        <v>1891300</v>
+        <v>1909600</v>
       </c>
       <c r="E81" s="3">
-        <v>2704000</v>
+        <v>2730200</v>
       </c>
       <c r="F81" s="3">
-        <v>1729700</v>
+        <v>1746500</v>
       </c>
       <c r="G81" s="3">
-        <v>905200</v>
+        <v>913900</v>
       </c>
       <c r="H81" s="3">
-        <v>301000</v>
+        <v>303900</v>
       </c>
       <c r="I81" s="3">
-        <v>219300</v>
+        <v>221500</v>
       </c>
       <c r="J81" s="3">
-        <v>298600</v>
+        <v>301500</v>
       </c>
       <c r="K81" s="3">
         <v>260700</v>
@@ -3694,25 +3694,25 @@
         <v>71</v>
       </c>
       <c r="D83" s="3">
-        <v>1255400</v>
+        <v>1267600</v>
       </c>
       <c r="E83" s="3">
-        <v>1369700</v>
+        <v>1383000</v>
       </c>
       <c r="F83" s="3">
-        <v>1459800</v>
+        <v>1473900</v>
       </c>
       <c r="G83" s="3">
-        <v>1516600</v>
+        <v>1531300</v>
       </c>
       <c r="H83" s="3">
-        <v>1531600</v>
+        <v>1546400</v>
       </c>
       <c r="I83" s="3">
-        <v>1614000</v>
+        <v>1629600</v>
       </c>
       <c r="J83" s="3">
-        <v>1646600</v>
+        <v>1662500</v>
       </c>
       <c r="K83" s="3">
         <v>1629700</v>
@@ -3964,25 +3964,25 @@
         <v>77</v>
       </c>
       <c r="D89" s="3">
-        <v>2666900</v>
+        <v>2692700</v>
       </c>
       <c r="E89" s="3">
-        <v>4523100</v>
+        <v>4566900</v>
       </c>
       <c r="F89" s="3">
-        <v>2801800</v>
+        <v>2828900</v>
       </c>
       <c r="G89" s="3">
-        <v>2038800</v>
+        <v>2058500</v>
       </c>
       <c r="H89" s="3">
-        <v>1702600</v>
+        <v>1719000</v>
       </c>
       <c r="I89" s="3">
-        <v>1579500</v>
+        <v>1594800</v>
       </c>
       <c r="J89" s="3">
-        <v>1627200</v>
+        <v>1643000</v>
       </c>
       <c r="K89" s="3">
         <v>1456200</v>
@@ -4028,25 +4028,25 @@
         <v>79</v>
       </c>
       <c r="D91" s="3">
-        <v>-2836600</v>
+        <v>-2864000</v>
       </c>
       <c r="E91" s="3">
-        <v>-2484800</v>
+        <v>-2508800</v>
       </c>
       <c r="F91" s="3">
-        <v>-1489600</v>
+        <v>-1504000</v>
       </c>
       <c r="G91" s="3">
-        <v>-817000</v>
+        <v>-824900</v>
       </c>
       <c r="H91" s="3">
-        <v>-512200</v>
+        <v>-517200</v>
       </c>
       <c r="I91" s="3">
-        <v>-607500</v>
+        <v>-613400</v>
       </c>
       <c r="J91" s="3">
-        <v>-1371800</v>
+        <v>-1385000</v>
       </c>
       <c r="K91" s="3">
         <v>-2870400</v>
@@ -4163,25 +4163,25 @@
         <v>82</v>
       </c>
       <c r="D94" s="3">
-        <v>-3032400</v>
+        <v>-3061700</v>
       </c>
       <c r="E94" s="3">
-        <v>-1687800</v>
+        <v>-1704100</v>
       </c>
       <c r="F94" s="3">
-        <v>-1927700</v>
+        <v>-1946300</v>
       </c>
       <c r="G94" s="3">
-        <v>-1243900</v>
+        <v>-1255900</v>
       </c>
       <c r="H94" s="3">
-        <v>-982400</v>
+        <v>-991900</v>
       </c>
       <c r="I94" s="3">
-        <v>-480600</v>
+        <v>-485300</v>
       </c>
       <c r="J94" s="3">
-        <v>-1098200</v>
+        <v>-1108900</v>
       </c>
       <c r="K94" s="3">
         <v>-2510700</v>
@@ -4227,25 +4227,25 @@
         <v>84</v>
       </c>
       <c r="D96" s="3">
-        <v>-1395900</v>
+        <v>-1409400</v>
       </c>
       <c r="E96" s="3">
-        <v>-1161200</v>
+        <v>-1172400</v>
       </c>
       <c r="F96" s="3">
-        <v>-616200</v>
+        <v>-622200</v>
       </c>
       <c r="G96" s="3">
-        <v>-302800</v>
+        <v>-305800</v>
       </c>
       <c r="H96" s="3">
-        <v>-214300</v>
+        <v>-216400</v>
       </c>
       <c r="I96" s="3">
-        <v>-265400</v>
+        <v>-267900</v>
       </c>
       <c r="J96" s="3">
-        <v>-189300</v>
+        <v>-191100</v>
       </c>
       <c r="K96" s="3">
         <v>-216500</v>
@@ -4407,25 +4407,25 @@
         <v>88</v>
       </c>
       <c r="D100" s="3">
-        <v>-902000</v>
+        <v>-910700</v>
       </c>
       <c r="E100" s="3">
-        <v>-1775500</v>
+        <v>-1792600</v>
       </c>
       <c r="F100" s="3">
-        <v>387300</v>
+        <v>391100</v>
       </c>
       <c r="G100" s="3">
-        <v>-793900</v>
+        <v>-801600</v>
       </c>
       <c r="H100" s="3">
-        <v>-306000</v>
+        <v>-308900</v>
       </c>
       <c r="I100" s="3">
-        <v>-1038400</v>
+        <v>-1048400</v>
       </c>
       <c r="J100" s="3">
-        <v>284100</v>
+        <v>286800</v>
       </c>
       <c r="K100" s="3">
         <v>1216200</v>
@@ -4452,25 +4452,25 @@
         <v>89</v>
       </c>
       <c r="D101" s="3">
-        <v>-12200</v>
+        <v>-12300</v>
       </c>
       <c r="E101" s="3">
-        <v>217600</v>
+        <v>219700</v>
       </c>
       <c r="F101" s="3">
-        <v>-65300</v>
+        <v>-65900</v>
       </c>
       <c r="G101" s="3">
-        <v>-45800</v>
+        <v>-46200</v>
       </c>
       <c r="H101" s="3">
-        <v>-47300</v>
+        <v>-47700</v>
       </c>
       <c r="I101" s="3">
         <v>1100</v>
       </c>
       <c r="J101" s="3">
-        <v>-65900</v>
+        <v>-66500</v>
       </c>
       <c r="K101" s="3">
         <v>-27300</v>
@@ -4497,25 +4497,25 @@
         <v>90</v>
       </c>
       <c r="D102" s="3">
-        <v>-1279600</v>
+        <v>-1292000</v>
       </c>
       <c r="E102" s="3">
-        <v>1277500</v>
+        <v>1289900</v>
       </c>
       <c r="F102" s="3">
-        <v>1196200</v>
+        <v>1207800</v>
       </c>
       <c r="G102" s="3">
-        <v>-44800</v>
+        <v>-45200</v>
       </c>
       <c r="H102" s="3">
-        <v>366900</v>
+        <v>370400</v>
       </c>
       <c r="I102" s="3">
-        <v>61600</v>
+        <v>62200</v>
       </c>
       <c r="J102" s="3">
-        <v>747200</v>
+        <v>754400</v>
       </c>
       <c r="K102" s="3">
         <v>134400</v>

--- a/AAII_Financials/Yearly/UMC_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/UMC_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="91">
   <si>
     <t>UMC</t>
   </si>
@@ -295,9 +295,6 @@
   </si>
   <si>
     <t xml:space="preserve">Change In Cash and Cash Equivalents </t>
-  </si>
-  <si>
-    <t>NA</t>
   </si>
 </sst>
 </file>
@@ -726,25 +723,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>6967500</v>
+        <v>7263300</v>
       </c>
       <c r="E8" s="3">
-        <v>8726300</v>
+        <v>9072100</v>
       </c>
       <c r="F8" s="3">
-        <v>6669400</v>
+        <v>7686300</v>
       </c>
       <c r="G8" s="3">
-        <v>5536300</v>
+        <v>6294100</v>
       </c>
       <c r="H8" s="3">
-        <v>4640200</v>
+        <v>4954100</v>
       </c>
       <c r="I8" s="3">
-        <v>4735700</v>
+        <v>4941300</v>
       </c>
       <c r="J8" s="3">
-        <v>4674100</v>
+        <v>5032200</v>
       </c>
       <c r="K8" s="3">
         <v>4635700</v>
@@ -771,25 +768,25 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>4533300</v>
+        <v>4725800</v>
       </c>
       <c r="E9" s="3">
-        <v>4788600</v>
+        <v>4978400</v>
       </c>
       <c r="F9" s="3">
-        <v>4413500</v>
+        <v>5086500</v>
       </c>
       <c r="G9" s="3">
-        <v>4315300</v>
+        <v>4906000</v>
       </c>
       <c r="H9" s="3">
-        <v>3972800</v>
+        <v>4241600</v>
       </c>
       <c r="I9" s="3">
-        <v>4020600</v>
+        <v>4195100</v>
       </c>
       <c r="J9" s="3">
-        <v>3826900</v>
+        <v>4120100</v>
       </c>
       <c r="K9" s="3">
         <v>3683300</v>
@@ -816,25 +813,25 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>2434200</v>
+        <v>2537500</v>
       </c>
       <c r="E10" s="3">
-        <v>3937700</v>
+        <v>4093800</v>
       </c>
       <c r="F10" s="3">
-        <v>2255900</v>
+        <v>2599800</v>
       </c>
       <c r="G10" s="3">
-        <v>1221000</v>
+        <v>1388100</v>
       </c>
       <c r="H10" s="3">
-        <v>667400</v>
+        <v>712500</v>
       </c>
       <c r="I10" s="3">
-        <v>715100</v>
+        <v>746200</v>
       </c>
       <c r="J10" s="3">
-        <v>847200</v>
+        <v>912100</v>
       </c>
       <c r="K10" s="3">
         <v>952400</v>
@@ -880,25 +877,25 @@
         <v>7</v>
       </c>
       <c r="D12" s="3">
-        <v>415900</v>
+        <v>433600</v>
       </c>
       <c r="E12" s="3">
-        <v>405600</v>
+        <v>421700</v>
       </c>
       <c r="F12" s="3">
-        <v>405000</v>
+        <v>466700</v>
       </c>
       <c r="G12" s="3">
-        <v>403800</v>
+        <v>459000</v>
       </c>
       <c r="H12" s="3">
-        <v>371300</v>
+        <v>396500</v>
       </c>
       <c r="I12" s="3">
-        <v>407800</v>
+        <v>425500</v>
       </c>
       <c r="J12" s="3">
-        <v>428000</v>
+        <v>460800</v>
       </c>
       <c r="K12" s="3">
         <v>424200</v>
@@ -970,25 +967,25 @@
         <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>-15500</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>91</v>
+        <v>-28900</v>
+      </c>
+      <c r="E14" s="3">
+        <v>23300</v>
+      </c>
+      <c r="F14" s="3">
+        <v>-109000</v>
       </c>
       <c r="G14" s="3">
-        <v>0</v>
+        <v>-37200</v>
       </c>
       <c r="H14" s="3">
-        <v>-1700</v>
+        <v>-2700</v>
       </c>
       <c r="I14" s="3">
-        <v>1400</v>
+        <v>-1300</v>
       </c>
       <c r="J14" s="3">
-        <v>29600</v>
+        <v>-13700</v>
       </c>
       <c r="K14" s="3">
         <v>65100</v>
@@ -1015,25 +1012,25 @@
         <v>10</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>1242000</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>1361000</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>1698600</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>1740900</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>1604000</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>1700400</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>1778500</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1076,25 +1073,25 @@
         <v>11</v>
       </c>
       <c r="D17" s="3">
-        <v>5139500</v>
+        <v>5382600</v>
       </c>
       <c r="E17" s="3">
-        <v>5460900</v>
+        <v>5693000</v>
       </c>
       <c r="F17" s="3">
-        <v>5051100</v>
+        <v>5826500</v>
       </c>
       <c r="G17" s="3">
-        <v>4847200</v>
+        <v>5553900</v>
       </c>
       <c r="H17" s="3">
-        <v>4488800</v>
+        <v>4789200</v>
       </c>
       <c r="I17" s="3">
-        <v>4555700</v>
+        <v>4760200</v>
       </c>
       <c r="J17" s="3">
-        <v>4498000</v>
+        <v>4813600</v>
       </c>
       <c r="K17" s="3">
         <v>4492400</v>
@@ -1121,25 +1118,25 @@
         <v>12</v>
       </c>
       <c r="D18" s="3">
-        <v>1828000</v>
+        <v>1880700</v>
       </c>
       <c r="E18" s="3">
-        <v>3265400</v>
+        <v>3379100</v>
       </c>
       <c r="F18" s="3">
-        <v>1618300</v>
+        <v>1859900</v>
       </c>
       <c r="G18" s="3">
-        <v>689100</v>
+        <v>740200</v>
       </c>
       <c r="H18" s="3">
-        <v>151400</v>
+        <v>164900</v>
       </c>
       <c r="I18" s="3">
-        <v>180100</v>
+        <v>181100</v>
       </c>
       <c r="J18" s="3">
-        <v>176100</v>
+        <v>218600</v>
       </c>
       <c r="K18" s="3">
         <v>143300</v>
@@ -1185,25 +1182,25 @@
         <v>14</v>
       </c>
       <c r="D20" s="3">
-        <v>438400</v>
+        <v>-214200</v>
       </c>
       <c r="E20" s="3">
-        <v>112400</v>
+        <v>-204900</v>
       </c>
       <c r="F20" s="3">
-        <v>375300</v>
+        <v>-188600</v>
       </c>
       <c r="G20" s="3">
-        <v>248100</v>
+        <v>-70100</v>
       </c>
       <c r="H20" s="3">
-        <v>120000</v>
+        <v>-57900</v>
       </c>
       <c r="I20" s="3">
-        <v>-25000</v>
+        <v>48500</v>
       </c>
       <c r="J20" s="3">
-        <v>143500</v>
+        <v>-107400</v>
       </c>
       <c r="K20" s="3">
         <v>47800</v>
@@ -1230,25 +1227,25 @@
         <v>15</v>
       </c>
       <c r="D21" s="3">
-        <v>3529100</v>
+        <v>3336900</v>
       </c>
       <c r="E21" s="3">
-        <v>4755500</v>
+        <v>4945000</v>
       </c>
       <c r="F21" s="3">
-        <v>3461800</v>
+        <v>3747100</v>
       </c>
       <c r="G21" s="3">
-        <v>2462600</v>
+        <v>2551200</v>
       </c>
       <c r="H21" s="3">
-        <v>1811900</v>
+        <v>1826900</v>
       </c>
       <c r="I21" s="3">
-        <v>1778500</v>
+        <v>1833000</v>
       </c>
       <c r="J21" s="3">
-        <v>1975700</v>
+        <v>2104500</v>
       </c>
       <c r="K21" s="3">
         <v>1817200</v>
@@ -1275,25 +1272,25 @@
         <v>16</v>
       </c>
       <c r="D22" s="3">
-        <v>46100</v>
+        <v>48100</v>
       </c>
       <c r="E22" s="3">
-        <v>55900</v>
+        <v>58100</v>
       </c>
       <c r="F22" s="3">
-        <v>58500</v>
+        <v>67400</v>
       </c>
       <c r="G22" s="3">
-        <v>62800</v>
+        <v>71300</v>
       </c>
       <c r="H22" s="3">
-        <v>91900</v>
+        <v>98100</v>
       </c>
       <c r="I22" s="3">
-        <v>86700</v>
+        <v>90400</v>
       </c>
       <c r="J22" s="3">
-        <v>75400</v>
+        <v>81100</v>
       </c>
       <c r="K22" s="3">
         <v>39200</v>
@@ -1320,25 +1317,25 @@
         <v>17</v>
       </c>
       <c r="D23" s="3">
-        <v>2220300</v>
+        <v>2234200</v>
       </c>
       <c r="E23" s="3">
-        <v>3321900</v>
+        <v>3568400</v>
       </c>
       <c r="F23" s="3">
-        <v>1935100</v>
+        <v>2110800</v>
       </c>
       <c r="G23" s="3">
-        <v>874400</v>
+        <v>802400</v>
       </c>
       <c r="H23" s="3">
-        <v>179600</v>
+        <v>160700</v>
       </c>
       <c r="I23" s="3">
-        <v>68400</v>
+        <v>69200</v>
       </c>
       <c r="J23" s="3">
-        <v>244200</v>
+        <v>258600</v>
       </c>
       <c r="K23" s="3">
         <v>151900</v>
@@ -1365,25 +1362,25 @@
         <v>18</v>
       </c>
       <c r="D24" s="3">
-        <v>296600</v>
+        <v>271300</v>
       </c>
       <c r="E24" s="3">
-        <v>566100</v>
+        <v>629100</v>
       </c>
       <c r="F24" s="3">
-        <v>209500</v>
+        <v>285700</v>
       </c>
       <c r="G24" s="3">
-        <v>23300</v>
+        <v>60200</v>
       </c>
       <c r="H24" s="3">
-        <v>-12300</v>
+        <v>7700</v>
       </c>
       <c r="I24" s="3">
-        <v>-14400</v>
+        <v>-36900</v>
       </c>
       <c r="J24" s="3">
-        <v>36500</v>
+        <v>33500</v>
       </c>
       <c r="K24" s="3">
         <v>30800</v>
@@ -1455,25 +1452,25 @@
         <v>20</v>
       </c>
       <c r="D26" s="3">
-        <v>1923700</v>
+        <v>1962900</v>
       </c>
       <c r="E26" s="3">
-        <v>2755900</v>
+        <v>2939300</v>
       </c>
       <c r="F26" s="3">
-        <v>1725600</v>
+        <v>1825100</v>
       </c>
       <c r="G26" s="3">
-        <v>851000</v>
+        <v>742200</v>
       </c>
       <c r="H26" s="3">
-        <v>191900</v>
+        <v>153000</v>
       </c>
       <c r="I26" s="3">
-        <v>82800</v>
+        <v>106100</v>
       </c>
       <c r="J26" s="3">
-        <v>207600</v>
+        <v>225100</v>
       </c>
       <c r="K26" s="3">
         <v>121100</v>
@@ -1500,25 +1497,25 @@
         <v>21</v>
       </c>
       <c r="D27" s="3">
-        <v>1909600</v>
+        <v>1948200</v>
       </c>
       <c r="E27" s="3">
-        <v>2730200</v>
+        <v>2912600</v>
       </c>
       <c r="F27" s="3">
-        <v>1746500</v>
+        <v>1849200</v>
       </c>
       <c r="G27" s="3">
-        <v>913900</v>
+        <v>813800</v>
       </c>
       <c r="H27" s="3">
-        <v>303900</v>
+        <v>272600</v>
       </c>
       <c r="I27" s="3">
-        <v>221500</v>
+        <v>250800</v>
       </c>
       <c r="J27" s="3">
-        <v>301500</v>
+        <v>326200</v>
       </c>
       <c r="K27" s="3">
         <v>260700</v>
@@ -1725,25 +1722,25 @@
         <v>26</v>
       </c>
       <c r="D32" s="3">
-        <v>-438400</v>
+        <v>214200</v>
       </c>
       <c r="E32" s="3">
-        <v>-112400</v>
+        <v>204900</v>
       </c>
       <c r="F32" s="3">
-        <v>-375300</v>
+        <v>188600</v>
       </c>
       <c r="G32" s="3">
-        <v>-248100</v>
+        <v>70100</v>
       </c>
       <c r="H32" s="3">
-        <v>-120000</v>
+        <v>57900</v>
       </c>
       <c r="I32" s="3">
-        <v>25000</v>
+        <v>-48500</v>
       </c>
       <c r="J32" s="3">
-        <v>-143500</v>
+        <v>107400</v>
       </c>
       <c r="K32" s="3">
         <v>-47800</v>
@@ -1770,25 +1767,25 @@
         <v>27</v>
       </c>
       <c r="D33" s="3">
-        <v>1909600</v>
+        <v>1948200</v>
       </c>
       <c r="E33" s="3">
-        <v>2730200</v>
+        <v>2912600</v>
       </c>
       <c r="F33" s="3">
-        <v>1746500</v>
+        <v>1849200</v>
       </c>
       <c r="G33" s="3">
-        <v>913900</v>
+        <v>813800</v>
       </c>
       <c r="H33" s="3">
-        <v>303900</v>
+        <v>272600</v>
       </c>
       <c r="I33" s="3">
-        <v>221500</v>
+        <v>250800</v>
       </c>
       <c r="J33" s="3">
-        <v>301500</v>
+        <v>326200</v>
       </c>
       <c r="K33" s="3">
         <v>260700</v>
@@ -1860,25 +1857,25 @@
         <v>29</v>
       </c>
       <c r="D35" s="3">
-        <v>1909600</v>
+        <v>1948200</v>
       </c>
       <c r="E35" s="3">
-        <v>2730200</v>
+        <v>2912600</v>
       </c>
       <c r="F35" s="3">
-        <v>1746500</v>
+        <v>1849200</v>
       </c>
       <c r="G35" s="3">
-        <v>913900</v>
+        <v>813800</v>
       </c>
       <c r="H35" s="3">
-        <v>303900</v>
+        <v>272600</v>
       </c>
       <c r="I35" s="3">
-        <v>221500</v>
+        <v>250800</v>
       </c>
       <c r="J35" s="3">
-        <v>301500</v>
+        <v>326200</v>
       </c>
       <c r="K35" s="3">
         <v>260700</v>
@@ -1993,25 +1990,25 @@
         <v>33</v>
       </c>
       <c r="D41" s="3">
-        <v>4150300</v>
+        <v>4326400</v>
       </c>
       <c r="E41" s="3">
-        <v>5442300</v>
+        <v>5658000</v>
       </c>
       <c r="F41" s="3">
-        <v>4152400</v>
+        <v>4785600</v>
       </c>
       <c r="G41" s="3">
-        <v>2944600</v>
+        <v>3347700</v>
       </c>
       <c r="H41" s="3">
-        <v>2989900</v>
+        <v>3192100</v>
       </c>
       <c r="I41" s="3">
-        <v>2619400</v>
+        <v>2733200</v>
       </c>
       <c r="J41" s="3">
-        <v>2557200</v>
+        <v>2753100</v>
       </c>
       <c r="K41" s="3">
         <v>1805100</v>
@@ -2038,25 +2035,25 @@
         <v>34</v>
       </c>
       <c r="D42" s="3">
-        <v>386000</v>
+        <v>402400</v>
       </c>
       <c r="E42" s="3">
-        <v>149700</v>
+        <v>155600</v>
       </c>
       <c r="F42" s="3">
-        <v>295800</v>
+        <v>1381400</v>
       </c>
       <c r="G42" s="3">
-        <v>38100</v>
+        <v>552500</v>
       </c>
       <c r="H42" s="3">
-        <v>22600</v>
+        <v>102800</v>
       </c>
       <c r="I42" s="3">
-        <v>16500</v>
+        <v>17300</v>
       </c>
       <c r="J42" s="3">
-        <v>22400</v>
+        <v>24200</v>
       </c>
       <c r="K42" s="3">
         <v>22400</v>
@@ -2083,25 +2080,25 @@
         <v>35</v>
       </c>
       <c r="D43" s="3">
-        <v>1038300</v>
+        <v>1082400</v>
       </c>
       <c r="E43" s="3">
-        <v>1227200</v>
+        <v>1275900</v>
       </c>
       <c r="F43" s="3">
-        <v>1138700</v>
+        <v>1312400</v>
       </c>
       <c r="G43" s="3">
-        <v>915400</v>
+        <v>1040700</v>
       </c>
       <c r="H43" s="3">
-        <v>833600</v>
+        <v>892500</v>
       </c>
       <c r="I43" s="3">
-        <v>773200</v>
+        <v>806800</v>
       </c>
       <c r="J43" s="3">
-        <v>709400</v>
+        <v>767700</v>
       </c>
       <c r="K43" s="3">
         <v>752500</v>
@@ -2128,25 +2125,25 @@
         <v>36</v>
       </c>
       <c r="D44" s="3">
-        <v>1118200</v>
+        <v>1165600</v>
       </c>
       <c r="E44" s="3">
-        <v>972800</v>
+        <v>1011400</v>
       </c>
       <c r="F44" s="3">
-        <v>720500</v>
+        <v>830300</v>
       </c>
       <c r="G44" s="3">
-        <v>706100</v>
+        <v>802800</v>
       </c>
       <c r="H44" s="3">
-        <v>679900</v>
+        <v>725900</v>
       </c>
       <c r="I44" s="3">
-        <v>569900</v>
+        <v>594700</v>
       </c>
       <c r="J44" s="3">
-        <v>571600</v>
+        <v>615400</v>
       </c>
       <c r="K44" s="3">
         <v>532900</v>
@@ -2173,25 +2170,25 @@
         <v>37</v>
       </c>
       <c r="D45" s="3">
-        <v>95200</v>
+        <v>99200</v>
       </c>
       <c r="E45" s="3">
-        <v>109700</v>
+        <v>114100</v>
       </c>
       <c r="F45" s="3">
-        <v>996400</v>
+        <v>107800</v>
       </c>
       <c r="G45" s="3">
-        <v>540100</v>
+        <v>22200</v>
       </c>
       <c r="H45" s="3">
-        <v>288200</v>
+        <v>229000</v>
       </c>
       <c r="I45" s="3">
-        <v>441600</v>
+        <v>94000</v>
       </c>
       <c r="J45" s="3">
-        <v>496400</v>
+        <v>534400</v>
       </c>
       <c r="K45" s="3">
         <v>350400</v>
@@ -2218,25 +2215,25 @@
         <v>38</v>
       </c>
       <c r="D46" s="3">
-        <v>6787900</v>
+        <v>7076100</v>
       </c>
       <c r="E46" s="3">
-        <v>7901700</v>
+        <v>8214900</v>
       </c>
       <c r="F46" s="3">
-        <v>7303800</v>
+        <v>8417500</v>
       </c>
       <c r="G46" s="3">
-        <v>5144400</v>
+        <v>5848600</v>
       </c>
       <c r="H46" s="3">
-        <v>4814100</v>
+        <v>5142300</v>
       </c>
       <c r="I46" s="3">
-        <v>4420800</v>
+        <v>4612700</v>
       </c>
       <c r="J46" s="3">
-        <v>4357100</v>
+        <v>4694900</v>
       </c>
       <c r="K46" s="3">
         <v>3463200</v>
@@ -2263,25 +2260,25 @@
         <v>39</v>
       </c>
       <c r="D47" s="3">
-        <v>2324900</v>
+        <v>2011700</v>
       </c>
       <c r="E47" s="3">
-        <v>2030600</v>
+        <v>1831800</v>
       </c>
       <c r="F47" s="3">
-        <v>2271400</v>
+        <v>2129000</v>
       </c>
       <c r="G47" s="3">
-        <v>1771500</v>
+        <v>2014000</v>
       </c>
       <c r="H47" s="3">
-        <v>1294500</v>
+        <v>1256400</v>
       </c>
       <c r="I47" s="3">
-        <v>1049100</v>
+        <v>1094600</v>
       </c>
       <c r="J47" s="3">
-        <v>1065300</v>
+        <v>1041400</v>
       </c>
       <c r="K47" s="3">
         <v>1089900</v>
@@ -2308,25 +2305,25 @@
         <v>40</v>
       </c>
       <c r="D48" s="3">
-        <v>7854100</v>
+        <v>8033300</v>
       </c>
       <c r="E48" s="3">
-        <v>6200400</v>
+        <v>5813400</v>
       </c>
       <c r="F48" s="3">
-        <v>4552200</v>
+        <v>4946000</v>
       </c>
       <c r="G48" s="3">
-        <v>4418100</v>
+        <v>5002100</v>
       </c>
       <c r="H48" s="3">
-        <v>4974600</v>
+        <v>5303900</v>
       </c>
       <c r="I48" s="3">
-        <v>5432500</v>
+        <v>5646700</v>
       </c>
       <c r="J48" s="3">
-        <v>6450700</v>
+        <v>6935300</v>
       </c>
       <c r="K48" s="3">
         <v>7090200</v>
@@ -2353,25 +2350,25 @@
         <v>41</v>
       </c>
       <c r="D49" s="3">
-        <v>136900</v>
+        <v>142700</v>
       </c>
       <c r="E49" s="3">
-        <v>133900</v>
+        <v>139200</v>
       </c>
       <c r="F49" s="3">
-        <v>114100</v>
+        <v>131500</v>
       </c>
       <c r="G49" s="3">
-        <v>152700</v>
+        <v>173600</v>
       </c>
       <c r="H49" s="3">
-        <v>162800</v>
+        <v>173800</v>
       </c>
       <c r="I49" s="3">
-        <v>93700</v>
+        <v>97700</v>
       </c>
       <c r="J49" s="3">
-        <v>118600</v>
+        <v>127700</v>
       </c>
       <c r="K49" s="3">
         <v>128200</v>
@@ -2488,25 +2485,25 @@
         <v>44</v>
       </c>
       <c r="D52" s="3">
-        <v>404300</v>
+        <v>408600</v>
       </c>
       <c r="E52" s="3">
-        <v>423200</v>
+        <v>908400</v>
       </c>
       <c r="F52" s="3">
-        <v>299600</v>
+        <v>450600</v>
       </c>
       <c r="G52" s="3">
-        <v>333300</v>
+        <v>156600</v>
       </c>
       <c r="H52" s="3">
-        <v>344500</v>
+        <v>114100</v>
       </c>
       <c r="I52" s="3">
-        <v>419800</v>
+        <v>250900</v>
       </c>
       <c r="J52" s="3">
-        <v>347600</v>
+        <v>179200</v>
       </c>
       <c r="K52" s="3">
         <v>350100</v>
@@ -2578,25 +2575,25 @@
         <v>46</v>
       </c>
       <c r="D54" s="3">
-        <v>17508100</v>
+        <v>17839800</v>
       </c>
       <c r="E54" s="3">
-        <v>16689900</v>
+        <v>17077800</v>
       </c>
       <c r="F54" s="3">
-        <v>14541200</v>
+        <v>16272300</v>
       </c>
       <c r="G54" s="3">
-        <v>11820000</v>
+        <v>13438100</v>
       </c>
       <c r="H54" s="3">
-        <v>11590600</v>
+        <v>12243400</v>
       </c>
       <c r="I54" s="3">
-        <v>11415800</v>
+        <v>11911300</v>
       </c>
       <c r="J54" s="3">
-        <v>12339200</v>
+        <v>13184500</v>
       </c>
       <c r="K54" s="3">
         <v>12121600</v>
@@ -2661,25 +2658,25 @@
         <v>49</v>
       </c>
       <c r="D57" s="3">
-        <v>235600</v>
+        <v>245600</v>
       </c>
       <c r="E57" s="3">
-        <v>281200</v>
+        <v>292400</v>
       </c>
       <c r="F57" s="3">
-        <v>261900</v>
+        <v>301800</v>
       </c>
       <c r="G57" s="3">
-        <v>246200</v>
+        <v>279900</v>
       </c>
       <c r="H57" s="3">
-        <v>277900</v>
+        <v>296700</v>
       </c>
       <c r="I57" s="3">
-        <v>213000</v>
+        <v>222200</v>
       </c>
       <c r="J57" s="3">
-        <v>204600</v>
+        <v>220300</v>
       </c>
       <c r="K57" s="3">
         <v>214900</v>
@@ -2706,25 +2703,25 @@
         <v>50</v>
       </c>
       <c r="D58" s="3">
-        <v>940900</v>
+        <v>980800</v>
       </c>
       <c r="E58" s="3">
-        <v>254400</v>
+        <v>264400</v>
       </c>
       <c r="F58" s="3">
-        <v>1246600</v>
+        <v>1436700</v>
       </c>
       <c r="G58" s="3">
-        <v>1208300</v>
+        <v>1373700</v>
       </c>
       <c r="H58" s="3">
-        <v>1170400</v>
+        <v>1249600</v>
       </c>
       <c r="I58" s="3">
-        <v>570600</v>
+        <v>595400</v>
       </c>
       <c r="J58" s="3">
-        <v>1653500</v>
+        <v>1780100</v>
       </c>
       <c r="K58" s="3">
         <v>973500</v>
@@ -2751,25 +2748,25 @@
         <v>51</v>
       </c>
       <c r="D59" s="3">
-        <v>1923600</v>
+        <v>2074800</v>
       </c>
       <c r="E59" s="3">
-        <v>2863600</v>
+        <v>3082300</v>
       </c>
       <c r="F59" s="3">
-        <v>1793300</v>
+        <v>2147400</v>
       </c>
       <c r="G59" s="3">
-        <v>995300</v>
+        <v>1112600</v>
       </c>
       <c r="H59" s="3">
-        <v>828400</v>
+        <v>892400</v>
       </c>
       <c r="I59" s="3">
-        <v>778800</v>
+        <v>812600</v>
       </c>
       <c r="J59" s="3">
-        <v>899100</v>
+        <v>993400</v>
       </c>
       <c r="K59" s="3">
         <v>1068200</v>
@@ -2796,25 +2793,25 @@
         <v>52</v>
       </c>
       <c r="D60" s="3">
-        <v>3100200</v>
+        <v>3325800</v>
       </c>
       <c r="E60" s="3">
-        <v>3399200</v>
+        <v>3665500</v>
       </c>
       <c r="F60" s="3">
-        <v>3301800</v>
+        <v>3906100</v>
       </c>
       <c r="G60" s="3">
-        <v>2449800</v>
+        <v>2785200</v>
       </c>
       <c r="H60" s="3">
-        <v>2276700</v>
+        <v>2438800</v>
       </c>
       <c r="I60" s="3">
-        <v>1562300</v>
+        <v>1630200</v>
       </c>
       <c r="J60" s="3">
-        <v>2757200</v>
+        <v>2993800</v>
       </c>
       <c r="K60" s="3">
         <v>2256500</v>
@@ -2841,25 +2838,25 @@
         <v>53</v>
       </c>
       <c r="D61" s="3">
-        <v>1569100</v>
+        <v>1635700</v>
       </c>
       <c r="E61" s="3">
-        <v>1411400</v>
+        <v>1467300</v>
       </c>
       <c r="F61" s="3">
-        <v>1388300</v>
+        <v>1600000</v>
       </c>
       <c r="G61" s="3">
-        <v>933000</v>
+        <v>1060700</v>
       </c>
       <c r="H61" s="3">
-        <v>1670400</v>
+        <v>1783400</v>
       </c>
       <c r="I61" s="3">
-        <v>2100400</v>
+        <v>2191500</v>
       </c>
       <c r="J61" s="3">
-        <v>1669400</v>
+        <v>1797300</v>
       </c>
       <c r="K61" s="3">
         <v>1903800</v>
@@ -2886,25 +2883,25 @@
         <v>54</v>
       </c>
       <c r="D62" s="3">
-        <v>1580500</v>
+        <v>1330100</v>
       </c>
       <c r="E62" s="3">
-        <v>1376400</v>
+        <v>1148500</v>
       </c>
       <c r="F62" s="3">
-        <v>1046700</v>
+        <v>819100</v>
       </c>
       <c r="G62" s="3">
-        <v>1055200</v>
+        <v>750400</v>
       </c>
       <c r="H62" s="3">
-        <v>1155600</v>
+        <v>686700</v>
       </c>
       <c r="I62" s="3">
-        <v>1286400</v>
+        <v>696000</v>
       </c>
       <c r="J62" s="3">
-        <v>1211100</v>
+        <v>712500</v>
       </c>
       <c r="K62" s="3">
         <v>1103700</v>
@@ -3066,25 +3063,25 @@
         <v>57</v>
       </c>
       <c r="D66" s="3">
-        <v>6260400</v>
+        <v>6621200</v>
       </c>
       <c r="E66" s="3">
-        <v>6197700</v>
+        <v>6569900</v>
       </c>
       <c r="F66" s="3">
-        <v>5743700</v>
+        <v>6732600</v>
       </c>
       <c r="G66" s="3">
-        <v>4441500</v>
+        <v>5045500</v>
       </c>
       <c r="H66" s="3">
-        <v>5115500</v>
+        <v>5460400</v>
       </c>
       <c r="I66" s="3">
-        <v>4963700</v>
+        <v>5163900</v>
       </c>
       <c r="J66" s="3">
-        <v>5667700</v>
+        <v>6118500</v>
       </c>
       <c r="K66" s="3">
         <v>5331900</v>
@@ -3310,25 +3307,25 @@
         <v>63</v>
       </c>
       <c r="D72" s="3">
-        <v>6795900</v>
+        <v>6841100</v>
       </c>
       <c r="E72" s="3">
-        <v>6332400</v>
+        <v>6386700</v>
       </c>
       <c r="F72" s="3">
-        <v>3612400</v>
+        <v>3863000</v>
       </c>
       <c r="G72" s="3">
-        <v>2510300</v>
+        <v>2854000</v>
       </c>
       <c r="H72" s="3">
-        <v>1914700</v>
+        <v>2138100</v>
       </c>
       <c r="I72" s="3">
-        <v>1928300</v>
+        <v>2012000</v>
       </c>
       <c r="J72" s="3">
-        <v>1504900</v>
+        <v>1788500</v>
       </c>
       <c r="K72" s="3">
         <v>1494000</v>
@@ -3490,25 +3487,25 @@
         <v>67</v>
       </c>
       <c r="D76" s="3">
-        <v>11247700</v>
+        <v>11207500</v>
       </c>
       <c r="E76" s="3">
-        <v>10492200</v>
+        <v>10496600</v>
       </c>
       <c r="F76" s="3">
-        <v>8797500</v>
+        <v>9531700</v>
       </c>
       <c r="G76" s="3">
-        <v>7378500</v>
+        <v>8388600</v>
       </c>
       <c r="H76" s="3">
-        <v>6475000</v>
+        <v>6769300</v>
       </c>
       <c r="I76" s="3">
-        <v>6452000</v>
+        <v>6732100</v>
       </c>
       <c r="J76" s="3">
-        <v>6671600</v>
+        <v>7033800</v>
       </c>
       <c r="K76" s="3">
         <v>6789800</v>
@@ -3630,25 +3627,25 @@
         <v>27</v>
       </c>
       <c r="D81" s="3">
-        <v>1909600</v>
+        <v>1948200</v>
       </c>
       <c r="E81" s="3">
-        <v>2730200</v>
+        <v>2912600</v>
       </c>
       <c r="F81" s="3">
-        <v>1746500</v>
+        <v>1849200</v>
       </c>
       <c r="G81" s="3">
-        <v>913900</v>
+        <v>813800</v>
       </c>
       <c r="H81" s="3">
-        <v>303900</v>
+        <v>272600</v>
       </c>
       <c r="I81" s="3">
-        <v>221500</v>
+        <v>250800</v>
       </c>
       <c r="J81" s="3">
-        <v>301500</v>
+        <v>326200</v>
       </c>
       <c r="K81" s="3">
         <v>260700</v>
@@ -3694,25 +3691,25 @@
         <v>71</v>
       </c>
       <c r="D83" s="3">
-        <v>1267600</v>
+        <v>1232400</v>
       </c>
       <c r="E83" s="3">
-        <v>1383000</v>
+        <v>1345300</v>
       </c>
       <c r="F83" s="3">
-        <v>1473900</v>
+        <v>1594200</v>
       </c>
       <c r="G83" s="3">
-        <v>1531300</v>
+        <v>1643200</v>
       </c>
       <c r="H83" s="3">
-        <v>1546400</v>
+        <v>1576900</v>
       </c>
       <c r="I83" s="3">
-        <v>1629600</v>
+        <v>1631800</v>
       </c>
       <c r="J83" s="3">
-        <v>1662500</v>
+        <v>1718000</v>
       </c>
       <c r="K83" s="3">
         <v>1629700</v>
@@ -3964,25 +3961,25 @@
         <v>77</v>
       </c>
       <c r="D89" s="3">
-        <v>2692700</v>
+        <v>2807000</v>
       </c>
       <c r="E89" s="3">
-        <v>4566900</v>
+        <v>4747900</v>
       </c>
       <c r="F89" s="3">
-        <v>2828900</v>
+        <v>3260300</v>
       </c>
       <c r="G89" s="3">
-        <v>2058500</v>
+        <v>2340300</v>
       </c>
       <c r="H89" s="3">
-        <v>1719000</v>
+        <v>1835300</v>
       </c>
       <c r="I89" s="3">
-        <v>1594800</v>
+        <v>1664000</v>
       </c>
       <c r="J89" s="3">
-        <v>1643000</v>
+        <v>1768800</v>
       </c>
       <c r="K89" s="3">
         <v>1456200</v>
@@ -4028,25 +4025,25 @@
         <v>79</v>
       </c>
       <c r="D91" s="3">
-        <v>-2864000</v>
+        <v>-2985600</v>
       </c>
       <c r="E91" s="3">
-        <v>-2508800</v>
+        <v>-2608200</v>
       </c>
       <c r="F91" s="3">
-        <v>-1504000</v>
+        <v>-1733300</v>
       </c>
       <c r="G91" s="3">
-        <v>-824900</v>
+        <v>-937800</v>
       </c>
       <c r="H91" s="3">
-        <v>-517200</v>
+        <v>-552200</v>
       </c>
       <c r="I91" s="3">
-        <v>-613400</v>
+        <v>-640000</v>
       </c>
       <c r="J91" s="3">
-        <v>-1385000</v>
+        <v>-1491100</v>
       </c>
       <c r="K91" s="3">
         <v>-2870400</v>
@@ -4163,25 +4160,25 @@
         <v>82</v>
       </c>
       <c r="D94" s="3">
-        <v>-3061700</v>
+        <v>-3191700</v>
       </c>
       <c r="E94" s="3">
-        <v>-1704100</v>
+        <v>-1771700</v>
       </c>
       <c r="F94" s="3">
-        <v>-1946300</v>
+        <v>-2243100</v>
       </c>
       <c r="G94" s="3">
-        <v>-1255900</v>
+        <v>-1427800</v>
       </c>
       <c r="H94" s="3">
-        <v>-991900</v>
+        <v>-1059100</v>
       </c>
       <c r="I94" s="3">
-        <v>-485300</v>
+        <v>-506400</v>
       </c>
       <c r="J94" s="3">
-        <v>-1108900</v>
+        <v>-1193800</v>
       </c>
       <c r="K94" s="3">
         <v>-2510700</v>
@@ -4227,25 +4224,25 @@
         <v>84</v>
       </c>
       <c r="D96" s="3">
-        <v>-1409400</v>
+        <v>1469200</v>
       </c>
       <c r="E96" s="3">
-        <v>-1172400</v>
+        <v>1218900</v>
       </c>
       <c r="F96" s="3">
-        <v>-622200</v>
+        <v>717000</v>
       </c>
       <c r="G96" s="3">
-        <v>-305800</v>
+        <v>347600</v>
       </c>
       <c r="H96" s="3">
-        <v>-216400</v>
+        <v>231000</v>
       </c>
       <c r="I96" s="3">
-        <v>-267900</v>
+        <v>279600</v>
       </c>
       <c r="J96" s="3">
-        <v>-191100</v>
+        <v>205700</v>
       </c>
       <c r="K96" s="3">
         <v>-216500</v>
@@ -4407,25 +4404,25 @@
         <v>88</v>
       </c>
       <c r="D100" s="3">
-        <v>-910700</v>
+        <v>-949300</v>
       </c>
       <c r="E100" s="3">
-        <v>-1792600</v>
+        <v>-1863700</v>
       </c>
       <c r="F100" s="3">
-        <v>391100</v>
+        <v>450700</v>
       </c>
       <c r="G100" s="3">
-        <v>-801600</v>
+        <v>-911300</v>
       </c>
       <c r="H100" s="3">
-        <v>-308900</v>
+        <v>-329800</v>
       </c>
       <c r="I100" s="3">
-        <v>-1048400</v>
+        <v>-1093900</v>
       </c>
       <c r="J100" s="3">
-        <v>286800</v>
+        <v>308800</v>
       </c>
       <c r="K100" s="3">
         <v>1216200</v>
@@ -4452,25 +4449,25 @@
         <v>89</v>
       </c>
       <c r="D101" s="3">
-        <v>-12300</v>
+        <v>-12800</v>
       </c>
       <c r="E101" s="3">
-        <v>219700</v>
+        <v>228400</v>
       </c>
       <c r="F101" s="3">
-        <v>-65900</v>
+        <v>-75900</v>
       </c>
       <c r="G101" s="3">
-        <v>-46200</v>
+        <v>-52600</v>
       </c>
       <c r="H101" s="3">
-        <v>-47700</v>
+        <v>-51000</v>
       </c>
       <c r="I101" s="3">
-        <v>1100</v>
+        <v>1200</v>
       </c>
       <c r="J101" s="3">
-        <v>-66500</v>
+        <v>-71600</v>
       </c>
       <c r="K101" s="3">
         <v>-27300</v>
@@ -4497,25 +4494,25 @@
         <v>90</v>
       </c>
       <c r="D102" s="3">
-        <v>-1292000</v>
+        <v>-1346900</v>
       </c>
       <c r="E102" s="3">
-        <v>1289900</v>
+        <v>1341000</v>
       </c>
       <c r="F102" s="3">
-        <v>1207800</v>
+        <v>1391900</v>
       </c>
       <c r="G102" s="3">
-        <v>-45200</v>
+        <v>-51400</v>
       </c>
       <c r="H102" s="3">
-        <v>370400</v>
+        <v>395500</v>
       </c>
       <c r="I102" s="3">
-        <v>62200</v>
+        <v>64900</v>
       </c>
       <c r="J102" s="3">
-        <v>754400</v>
+        <v>812200</v>
       </c>
       <c r="K102" s="3">
         <v>134400</v>

--- a/AAII_Financials/Yearly/UMC_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/UMC_YR_FIN.xlsx
@@ -653,207 +653,219 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44926</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44561</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44196</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43830</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43465</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43100</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42735</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42369</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42004</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41639</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41274</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>40908</v>
       </c>
-      <c r="Q7" s="2"/>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R7" s="2"/>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>7086700</v>
+      </c>
+      <c r="E8" s="3">
         <v>7263300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>9072100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>7686300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>6294100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>4954100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>4941300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>5032200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>4635700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>4617200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>5043200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>4343300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>3847300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>3805700</v>
       </c>
-      <c r="Q8" s="3"/>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R8" s="3"/>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>4778800</v>
+      </c>
+      <c r="E9" s="3">
         <v>4725800</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>4978400</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>5086500</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>4906000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>4241600</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>4195100</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>4120100</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>3683300</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>3604400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>3895900</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>3516700</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>6406800</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>3111500</v>
       </c>
-      <c r="Q9" s="3"/>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R9" s="3"/>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>2307900</v>
+      </c>
+      <c r="E10" s="3">
         <v>2537500</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>4093800</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>2599800</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1388100</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>712500</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>746200</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>912100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>952400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1012800</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1147300</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>826600</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>-2559500</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>694100</v>
       </c>
-      <c r="Q10" s="3"/>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R10" s="3"/>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -871,53 +883,57 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>476400</v>
+      </c>
+      <c r="E12" s="3">
         <v>433600</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>421700</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>466700</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>459000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>396500</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>425500</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>460800</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>424200</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>388100</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>492200</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>438300</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>651000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>306400</v>
       </c>
-      <c r="Q12" s="3"/>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R12" s="3"/>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -960,81 +976,87 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-      <c r="Q13" s="3"/>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+      <c r="R13" s="3"/>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>-28900</v>
+        <v>7600</v>
       </c>
       <c r="E14" s="3">
+        <v>-24200</v>
+      </c>
+      <c r="F14" s="3">
         <v>23300</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-109000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-37200</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-2700</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-1300</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-13700</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>65100</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>72300</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>32500</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>46800</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>236100</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>68700</v>
       </c>
-      <c r="Q14" s="3"/>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R14" s="3"/>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>1397600</v>
+      </c>
+      <c r="E15" s="3">
         <v>1242000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>1361000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>1698600</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>1740900</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>1604000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>1700400</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>1778500</v>
       </c>
-      <c r="K15" s="3">
-        <v>0</v>
-      </c>
       <c r="L15" s="3">
         <v>0</v>
       </c>
@@ -1050,9 +1072,12 @@
       <c r="P15" s="3">
         <v>0</v>
       </c>
-      <c r="Q15" s="3"/>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3">
+        <v>0</v>
+      </c>
+      <c r="R15" s="3"/>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1067,98 +1092,105 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>5514400</v>
+      </c>
+      <c r="E17" s="3">
         <v>5382600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>5693000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>5826500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>5553900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>4789200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>4760200</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>4813600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>4492400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>4311500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>4691300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>4246600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>3849100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>3710000</v>
       </c>
-      <c r="Q17" s="3"/>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R17" s="3"/>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>1572300</v>
+      </c>
+      <c r="E18" s="3">
         <v>1880700</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>3379100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>1859900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>740200</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>164900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>181100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>218600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>143300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>305700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>352000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>96700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-1800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>95700</v>
       </c>
-      <c r="Q18" s="3"/>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R18" s="3"/>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1176,233 +1208,249 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
-        <v>-214200</v>
+        <v>-89600</v>
       </c>
       <c r="E20" s="3">
+        <v>-299300</v>
+      </c>
+      <c r="F20" s="3">
         <v>-204900</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-188600</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-70100</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-57900</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>48500</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-107400</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>47800</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>146400</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>161600</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>430900</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>249700</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>222000</v>
       </c>
-      <c r="Q20" s="3"/>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R20" s="3"/>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
-        <v>3336900</v>
+        <v>3059400</v>
       </c>
       <c r="E21" s="3">
+        <v>3422000</v>
+      </c>
+      <c r="F21" s="3">
         <v>4945000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>3747100</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>2551200</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>1826900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>1833000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>2104500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1817200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1876300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>1973200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1876200</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>1442200</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>1371900</v>
       </c>
-      <c r="Q21" s="3"/>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R21" s="3"/>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
+        <v>51200</v>
+      </c>
+      <c r="E22" s="3">
         <v>48100</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>58100</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>67400</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>71300</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>98100</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>90400</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>81100</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>39200</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>15000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>26900</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>23800</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>35800</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>11700</v>
       </c>
-      <c r="Q22" s="3"/>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R22" s="3"/>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
-        <v>2234200</v>
+        <v>1715100</v>
       </c>
       <c r="E23" s="3">
+        <v>2314500</v>
+      </c>
+      <c r="F23" s="3">
         <v>3568400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>2110800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>802400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>160700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>69200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>258600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>151900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>437100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>486700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>503800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>212100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>305900</v>
       </c>
-      <c r="Q23" s="3"/>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R23" s="3"/>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
-        <v>271300</v>
+        <v>278000</v>
       </c>
       <c r="E24" s="3">
+        <v>309200</v>
+      </c>
+      <c r="F24" s="3">
         <v>629100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>285700</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>60200</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>7700</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-36900</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>33500</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>30800</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>27900</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>73300</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>79200</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>71400</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>29800</v>
       </c>
-      <c r="Q24" s="3"/>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R24" s="3"/>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -1445,99 +1493,108 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-      <c r="Q25" s="3"/>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+      <c r="R25" s="3"/>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
-        <v>1962900</v>
+        <v>1437000</v>
       </c>
       <c r="E26" s="3">
+        <v>2005300</v>
+      </c>
+      <c r="F26" s="3">
         <v>2939300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>1825100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>742200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>153000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>106100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>225100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>121100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>409200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>413500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>424600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>140700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>276100</v>
       </c>
-      <c r="Q26" s="3"/>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R26" s="3"/>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
-        <v>1948200</v>
+        <v>1440200</v>
       </c>
       <c r="E27" s="3">
+        <v>1990700</v>
+      </c>
+      <c r="F27" s="3">
         <v>2912600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>1849200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>813800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>272600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>250800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>326200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>260700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>428700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>437300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>443100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>113500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>215400</v>
       </c>
-      <c r="Q27" s="3"/>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R27" s="3"/>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -1580,9 +1637,12 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-      <c r="Q28" s="3"/>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+      <c r="R28" s="3"/>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -1625,9 +1685,12 @@
       <c r="P29" s="3">
         <v>0</v>
       </c>
-      <c r="Q29" s="3"/>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+      <c r="R29" s="3"/>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>24</v>
       </c>
@@ -1670,9 +1733,12 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-      <c r="Q30" s="3"/>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+      <c r="R30" s="3"/>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>25</v>
       </c>
@@ -1715,99 +1781,108 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-      <c r="Q31" s="3"/>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+      <c r="R31" s="3"/>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>26</v>
       </c>
       <c r="D32" s="3">
-        <v>214200</v>
+        <v>89600</v>
       </c>
       <c r="E32" s="3">
+        <v>299300</v>
+      </c>
+      <c r="F32" s="3">
         <v>204900</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>188600</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>70100</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>57900</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-48500</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>107400</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-47800</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-146400</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-161600</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-430900</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-249700</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-222000</v>
       </c>
-      <c r="Q32" s="3"/>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R32" s="3"/>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D33" s="3">
-        <v>1948200</v>
+        <v>1440200</v>
       </c>
       <c r="E33" s="3">
+        <v>1990700</v>
+      </c>
+      <c r="F33" s="3">
         <v>2912600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>1849200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>813800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>272600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>250800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>326200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>260700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>428700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>437300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>443100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>113500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>215400</v>
       </c>
-      <c r="Q33" s="3"/>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R33" s="3"/>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>28</v>
       </c>
@@ -1850,104 +1925,113 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-      <c r="Q34" s="3"/>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+      <c r="R34" s="3"/>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D35" s="3">
-        <v>1948200</v>
+        <v>1440200</v>
       </c>
       <c r="E35" s="3">
+        <v>1990700</v>
+      </c>
+      <c r="F35" s="3">
         <v>2912600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>1849200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>813800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>272600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>250800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>326200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>260700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>428700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>437300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>443100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>113500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>215400</v>
       </c>
-      <c r="Q35" s="3"/>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R35" s="3"/>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44926</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44561</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44196</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43830</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43465</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43100</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42735</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42369</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42004</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41639</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41274</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>40908</v>
       </c>
-      <c r="Q38" s="2"/>
-    </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R38" s="2"/>
+    </row>
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>31</v>
       </c>
@@ -1965,8 +2049,9 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>32</v>
       </c>
@@ -1984,413 +2069,441 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D41" s="3">
+        <v>3203200</v>
+      </c>
+      <c r="E41" s="3">
         <v>4326400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>5658000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>4785600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>3347700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>3192100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>2733200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>2753100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1805100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1698900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1646200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1783100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1565800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>115300</v>
       </c>
-      <c r="Q41" s="3"/>
-    </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R41" s="3"/>
+    </row>
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D42" s="3">
+        <v>312300</v>
+      </c>
+      <c r="E42" s="3">
         <v>402400</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>155600</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>1381400</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>552500</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>102800</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>17300</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>24200</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>22400</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>21200</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>26700</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>97100</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>1595700</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>1675100</v>
       </c>
-      <c r="Q42" s="3"/>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R42" s="3"/>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D43" s="3">
+        <v>1089200</v>
+      </c>
+      <c r="E43" s="3">
         <v>1082400</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1275900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1312400</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1040700</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>892500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>806800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>767700</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>752500</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>637300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>830700</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>617600</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1142100</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>499600</v>
       </c>
-      <c r="Q43" s="3"/>
-    </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R43" s="3"/>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D44" s="3">
+        <v>1091600</v>
+      </c>
+      <c r="E44" s="3">
         <v>1165600</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1011400</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>830300</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>802800</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>725900</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>594700</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>615400</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>532900</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>562400</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>493000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>490900</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>866300</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>414400</v>
       </c>
-      <c r="Q44" s="3"/>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R44" s="3"/>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D45" s="3">
-        <v>99200</v>
+        <v>18800</v>
       </c>
       <c r="E45" s="3">
+        <v>28600</v>
+      </c>
+      <c r="F45" s="3">
         <v>114100</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>107800</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>22200</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>229000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>94000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>534400</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>350400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>103000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>436500</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>126400</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>183000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>36600</v>
       </c>
-      <c r="Q45" s="3"/>
-    </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R45" s="3"/>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D46" s="3">
+        <v>5786400</v>
+      </c>
+      <c r="E46" s="3">
         <v>7076100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>8214900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>8417500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>5848600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>5142300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>4612700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>4694900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>3463200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>3022800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>3489000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>3115000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>2661700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>2741100</v>
       </c>
-      <c r="Q46" s="3"/>
-    </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R46" s="3"/>
+    </row>
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D47" s="3">
-        <v>2011700</v>
+        <v>2211300</v>
       </c>
       <c r="E47" s="3">
+        <v>2423600</v>
+      </c>
+      <c r="F47" s="3">
         <v>1831800</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>2129000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>2014000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>1256400</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>1094600</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>1041400</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>1089900</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>1280000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>2227500</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>1056700</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>2310700</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>1301900</v>
       </c>
-      <c r="Q47" s="3"/>
-    </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R47" s="3"/>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D48" s="3">
+        <v>8758300</v>
+      </c>
+      <c r="E48" s="3">
         <v>8033300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>5813400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>4946000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>5002100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>5303900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>5646700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>6935300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>7090200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>6017900</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>6042500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>11405100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>10614700</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>4869500</v>
       </c>
-      <c r="Q48" s="3"/>
-    </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R48" s="3"/>
+    </row>
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D49" s="3">
+        <v>126700</v>
+      </c>
+      <c r="E49" s="3">
         <v>142700</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>139200</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>131500</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>173600</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>173800</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>97700</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>127700</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>128200</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>143600</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>163300</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>332500</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>138200</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>11400</v>
       </c>
-      <c r="Q49" s="3"/>
-    </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R49" s="3"/>
+    </row>
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>42</v>
       </c>
@@ -2433,9 +2546,12 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-      <c r="Q50" s="3"/>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+      <c r="R50" s="3"/>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>43</v>
       </c>
@@ -2478,54 +2594,60 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-      <c r="Q51" s="3"/>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+      <c r="R51" s="3"/>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>44</v>
       </c>
       <c r="D52" s="3">
+        <v>353000</v>
+      </c>
+      <c r="E52" s="3">
         <v>408600</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>908400</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>450600</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>156600</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>114100</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>250900</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>179200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>350100</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>291000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>238400</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>262800</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>281300</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>201400</v>
       </c>
-      <c r="Q52" s="3"/>
-    </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R52" s="3"/>
+    </row>
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>45</v>
       </c>
@@ -2568,54 +2690,60 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-      <c r="Q53" s="3"/>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+      <c r="R53" s="3"/>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>46</v>
       </c>
       <c r="D54" s="3">
-        <v>17839800</v>
+        <v>17394800</v>
       </c>
       <c r="E54" s="3">
+        <v>18251400</v>
+      </c>
+      <c r="F54" s="3">
         <v>17077800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>16272300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>13438100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>12243400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>11911300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>13184500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>12121600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>10755300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>11283100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>10310500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>9353200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>9125300</v>
       </c>
-      <c r="Q54" s="3"/>
-    </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R54" s="3"/>
+    </row>
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>47</v>
       </c>
@@ -2633,8 +2761,9 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>48</v>
       </c>
@@ -2652,278 +2781,297 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>49</v>
       </c>
       <c r="D57" s="3">
+        <v>232900</v>
+      </c>
+      <c r="E57" s="3">
         <v>245600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>292400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>301800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>279900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>296700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>222200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>220300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>214900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>189800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>222100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>260100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>416800</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>163400</v>
       </c>
-      <c r="Q57" s="3"/>
-    </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R57" s="3"/>
+    </row>
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D58" s="3">
+        <v>614600</v>
+      </c>
+      <c r="E58" s="3">
         <v>980800</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>264400</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1436700</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1373700</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1249600</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>595400</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>1780100</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>973500</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>386000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>361100</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>743300</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>975200</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>567900</v>
       </c>
-      <c r="Q58" s="3"/>
-    </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R58" s="3"/>
+    </row>
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D59" s="3">
-        <v>2074800</v>
+        <v>1429500</v>
       </c>
       <c r="E59" s="3">
+        <v>1980700</v>
+      </c>
+      <c r="F59" s="3">
         <v>3082300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>2147400</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>1112600</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>892400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>812600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>993400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1068200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>962300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1149500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>687700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1274000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>667900</v>
       </c>
-      <c r="Q59" s="3"/>
-    </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R59" s="3"/>
+    </row>
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D60" s="3">
-        <v>3325800</v>
+        <v>2295900</v>
       </c>
       <c r="E60" s="3">
+        <v>3231800</v>
+      </c>
+      <c r="F60" s="3">
         <v>3665500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>3906100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>2785200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>2438800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1630200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>2993800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>2256500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1538100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1732800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1691000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>1334400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>1399200</v>
       </c>
-      <c r="Q60" s="3"/>
-    </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R60" s="3"/>
+    </row>
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D61" s="3">
+        <v>1870500</v>
+      </c>
+      <c r="E61" s="3">
         <v>1635700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1467300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1600000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1060700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1783400</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>2191500</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1797300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1903800</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1515100</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>1203100</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>996800</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>1069500</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>687900</v>
       </c>
-      <c r="Q61" s="3"/>
-    </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R61" s="3"/>
+    </row>
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D62" s="3">
+        <v>1302100</v>
+      </c>
+      <c r="E62" s="3">
         <v>1330100</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>1148500</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>819100</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>750400</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>686700</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>696000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>712500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1103700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>407400</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>242400</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>268400</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>365900</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>120800</v>
       </c>
-      <c r="Q62" s="3"/>
-    </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R62" s="3"/>
+    </row>
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>55</v>
       </c>
@@ -2966,9 +3114,12 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-      <c r="Q63" s="3"/>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+      <c r="R63" s="3"/>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -3011,9 +3162,12 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-      <c r="Q64" s="3"/>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+      <c r="R64" s="3"/>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>56</v>
       </c>
@@ -3056,54 +3210,60 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-      <c r="Q65" s="3"/>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+      <c r="R65" s="3"/>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>57</v>
       </c>
       <c r="D66" s="3">
-        <v>6621200</v>
+        <v>5857700</v>
       </c>
       <c r="E66" s="3">
+        <v>6515100</v>
+      </c>
+      <c r="F66" s="3">
         <v>6569900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>6732600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>5045500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>5460400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>5163900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>6118500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>5331900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>3525200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>3317000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>3107700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>2730600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>2351000</v>
       </c>
-      <c r="Q66" s="3"/>
-    </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R66" s="3"/>
+    </row>
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>58</v>
       </c>
@@ -3121,8 +3281,9 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>59</v>
       </c>
@@ -3165,9 +3326,12 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-      <c r="Q68" s="3"/>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+      <c r="R68" s="3"/>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>60</v>
       </c>
@@ -3210,9 +3374,12 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-      <c r="Q69" s="3"/>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+      <c r="R69" s="3"/>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>61</v>
       </c>
@@ -3255,9 +3422,12 @@
       <c r="P70" s="3">
         <v>0</v>
       </c>
-      <c r="Q70" s="3"/>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+      <c r="R70" s="3"/>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>62</v>
       </c>
@@ -3300,54 +3470,60 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-      <c r="Q71" s="3"/>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+      <c r="R71" s="3"/>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>63</v>
       </c>
       <c r="D72" s="3">
-        <v>6841100</v>
+        <v>6920300</v>
       </c>
       <c r="E72" s="3">
+        <v>7084400</v>
+      </c>
+      <c r="F72" s="3">
         <v>6386700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>3863000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>2854000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>2138100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>2012000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>1788500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>1494000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>1616600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>1597100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>1343700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>1872000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>798900</v>
       </c>
-      <c r="Q72" s="3"/>
-    </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R72" s="3"/>
+    </row>
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>64</v>
       </c>
@@ -3390,9 +3566,12 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-      <c r="Q73" s="3"/>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+      <c r="R73" s="3"/>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>65</v>
       </c>
@@ -3435,9 +3614,12 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-      <c r="Q74" s="3"/>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+      <c r="R74" s="3"/>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>66</v>
       </c>
@@ -3480,54 +3662,60 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-      <c r="Q75" s="3"/>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+      <c r="R75" s="3"/>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>67</v>
       </c>
       <c r="D76" s="3">
-        <v>11207500</v>
+        <v>11529200</v>
       </c>
       <c r="E76" s="3">
+        <v>11725200</v>
+      </c>
+      <c r="F76" s="3">
         <v>10496600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>9531700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>8388600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>6769300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>6732100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>7033800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>6789800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>7230100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>7966100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>7202800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>6622600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>6774300</v>
       </c>
-      <c r="Q76" s="3"/>
-    </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R76" s="3"/>
+    </row>
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>68</v>
       </c>
@@ -3570,104 +3758,113 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-      <c r="Q77" s="3"/>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+      <c r="R77" s="3"/>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44926</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44561</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44196</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43830</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43465</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43100</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42735</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42369</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42004</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41639</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41274</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>40908</v>
       </c>
-      <c r="Q80" s="2"/>
-    </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R80" s="2"/>
+    </row>
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D81" s="3">
-        <v>1948200</v>
+        <v>1440200</v>
       </c>
       <c r="E81" s="3">
+        <v>1990700</v>
+      </c>
+      <c r="F81" s="3">
         <v>2912600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>1849200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>813800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>272600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>250800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>326200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>260700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>428700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>437300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>443100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>113500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>215400</v>
       </c>
-      <c r="Q81" s="3"/>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R81" s="3"/>
+    </row>
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>70</v>
       </c>
@@ -3685,53 +3882,57 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>71</v>
       </c>
       <c r="D83" s="3">
+        <v>1387200</v>
+      </c>
+      <c r="E83" s="3">
         <v>1232400</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>1345300</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>1594200</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>1643200</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>1576900</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>1631800</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>1718000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>1629700</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>1449700</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>1464500</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>1348200</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>1192100</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>1055600</v>
       </c>
-      <c r="Q83" s="3"/>
-    </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R83" s="3"/>
+    </row>
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>72</v>
       </c>
@@ -3774,9 +3975,12 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-      <c r="Q84" s="3"/>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+      <c r="R84" s="3"/>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>73</v>
       </c>
@@ -3819,9 +4023,12 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-      <c r="Q85" s="3"/>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+      <c r="R85" s="3"/>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>74</v>
       </c>
@@ -3864,9 +4071,12 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-      <c r="Q86" s="3"/>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+      <c r="R86" s="3"/>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>75</v>
       </c>
@@ -3909,9 +4119,12 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-      <c r="Q87" s="3"/>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+      <c r="R87" s="3"/>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>76</v>
       </c>
@@ -3954,54 +4167,60 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-      <c r="Q88" s="3"/>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+      <c r="R88" s="3"/>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>77</v>
       </c>
       <c r="D89" s="3">
+        <v>2863700</v>
+      </c>
+      <c r="E89" s="3">
         <v>2807000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>4747900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>3260300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>2340300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>1835300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>1664000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>1768800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1456200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>1906000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>1613300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>1525000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>1343600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>1358300</v>
       </c>
-      <c r="Q89" s="3"/>
-    </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R89" s="3"/>
+    </row>
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>78</v>
       </c>
@@ -4019,53 +4238,57 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>79</v>
       </c>
       <c r="D91" s="3">
+        <v>-2701100</v>
+      </c>
+      <c r="E91" s="3">
         <v>-2985600</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-2608200</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1733300</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-937800</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-552200</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-640000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-1491100</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-2870400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-1928900</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-1557400</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-1154500</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-1754100</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-1751400</v>
       </c>
-      <c r="Q91" s="3"/>
-    </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R91" s="3"/>
+    </row>
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>80</v>
       </c>
@@ -4108,9 +4331,12 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-      <c r="Q92" s="3"/>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+      <c r="R92" s="3"/>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>81</v>
       </c>
@@ -4153,54 +4379,60 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-      <c r="Q93" s="3"/>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+      <c r="R93" s="3"/>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>82</v>
       </c>
       <c r="D94" s="3">
+        <v>-2621800</v>
+      </c>
+      <c r="E94" s="3">
         <v>-3191700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-1771700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-2243100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-1427800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-1059100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-506400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-1193800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-2510700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-2183200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-1534700</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-1105600</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-1633800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-1797500</v>
       </c>
-      <c r="Q94" s="3"/>
-    </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R94" s="3"/>
+    </row>
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>83</v>
       </c>
@@ -4218,53 +4450,57 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>84</v>
       </c>
       <c r="D96" s="3">
+        <v>1146600</v>
+      </c>
+      <c r="E96" s="3">
         <v>1469200</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>1218900</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>717000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>347600</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>231000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>279600</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>205700</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-216500</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-221200</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-225200</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-177600</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-210100</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-457100</v>
       </c>
-      <c r="Q96" s="3"/>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R96" s="3"/>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>85</v>
       </c>
@@ -4307,9 +4543,12 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-      <c r="Q97" s="3"/>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+      <c r="R97" s="3"/>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>86</v>
       </c>
@@ -4352,9 +4591,12 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-      <c r="Q98" s="3"/>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+      <c r="R98" s="3"/>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>87</v>
       </c>
@@ -4397,142 +4639,154 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-      <c r="Q99" s="3"/>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+      <c r="R99" s="3"/>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D100" s="3">
+        <v>-1195800</v>
+      </c>
+      <c r="E100" s="3">
         <v>-949300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-1863700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>450700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-911300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-329800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-1093900</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>308800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>1216200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>479800</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-297400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-137700</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>119300</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>323600</v>
       </c>
-      <c r="Q100" s="3"/>
-    </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R100" s="3"/>
+    </row>
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D101" s="3">
+        <v>113300</v>
+      </c>
+      <c r="E101" s="3">
         <v>-12800</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>228400</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-75900</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-52600</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-51000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>1200</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-71600</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-27300</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>23000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>52500</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>10900</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-47800</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>43800</v>
       </c>
-      <c r="Q101" s="3"/>
-    </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R101" s="3"/>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D102" s="3">
+        <v>-840600</v>
+      </c>
+      <c r="E102" s="3">
         <v>-1346900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>1341000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>1391900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-51400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>395500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>64900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>812200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>134400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>225600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-166300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>292600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-218600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-71800</v>
       </c>
-      <c r="Q102" s="3"/>
+      <c r="R102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/UMC_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/UMC_YR_FIN.xlsx
@@ -653,219 +653,231 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:R102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44561</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44196</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43830</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43465</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>43100</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42735</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42369</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>42004</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41639</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>41274</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>40908</v>
       </c>
-      <c r="R7" s="2"/>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S7" s="2"/>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>7564900</v>
+      </c>
+      <c r="E8" s="3">
         <v>7086700</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>7263300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>9072100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>7686300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>6294100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>4954100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>4941300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>5032200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>4635700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>4617200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>5043200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>4343300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>3847300</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>3805700</v>
       </c>
-      <c r="R8" s="3"/>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S8" s="3"/>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>5370600</v>
+      </c>
+      <c r="E9" s="3">
         <v>4778800</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>4725800</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>4978400</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>5086500</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>4906000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>4241600</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>4195100</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>4120100</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>3683300</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>3604400</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>3895900</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>3516700</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>6406800</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>3111500</v>
       </c>
-      <c r="R9" s="3"/>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S9" s="3"/>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>2194300</v>
+      </c>
+      <c r="E10" s="3">
         <v>2307900</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>2537500</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>4093800</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>2599800</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1388100</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>712500</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>746200</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>912100</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>952400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1012800</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1147300</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>826600</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>-2559500</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>694100</v>
       </c>
-      <c r="R10" s="3"/>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S10" s="3"/>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -884,56 +896,60 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>564400</v>
+      </c>
+      <c r="E12" s="3">
         <v>476400</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>433600</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>421700</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>466700</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>459000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>396500</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>425500</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>460800</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>424200</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>388100</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>492200</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>438300</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>651000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>306400</v>
       </c>
-      <c r="R12" s="3"/>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S12" s="3"/>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -979,87 +995,93 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-      <c r="R13" s="3"/>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+      <c r="S13" s="3"/>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>-26400</v>
+      </c>
+      <c r="E14" s="3">
         <v>7600</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-24200</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>23300</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-109000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-37200</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-2700</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-1300</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-13700</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>65100</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>72300</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>32500</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>46800</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>236100</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>68700</v>
       </c>
-      <c r="R14" s="3"/>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S14" s="3"/>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>1809300</v>
+      </c>
+      <c r="E15" s="3">
         <v>1397600</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>1242000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>1361000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>1698600</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>1740900</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>1604000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>1700400</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>1778500</v>
       </c>
-      <c r="L15" s="3">
-        <v>0</v>
-      </c>
       <c r="M15" s="3">
         <v>0</v>
       </c>
@@ -1075,9 +1097,12 @@
       <c r="Q15" s="3">
         <v>0</v>
       </c>
-      <c r="R15" s="3"/>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R15" s="3">
+        <v>0</v>
+      </c>
+      <c r="S15" s="3"/>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1093,104 +1118,111 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>6168500</v>
+      </c>
+      <c r="E17" s="3">
         <v>5514400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>5382600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>5693000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>5826500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>5553900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>4789200</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>4760200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>4813600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>4492400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>4311500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>4691300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>4246600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>3849100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>3710000</v>
       </c>
-      <c r="R17" s="3"/>
-    </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S17" s="3"/>
+    </row>
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>1396400</v>
+      </c>
+      <c r="E18" s="3">
         <v>1572300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>1880700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>3379100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>1859900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>740200</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>164900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>181100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>218600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>143300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>305700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>352000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>96700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-1800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>95700</v>
       </c>
-      <c r="R18" s="3"/>
-    </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S18" s="3"/>
+    </row>
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1209,248 +1241,264 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>-134400</v>
+      </c>
+      <c r="E20" s="3">
         <v>-89600</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-299300</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-204900</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-188600</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-70100</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-57900</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>48500</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-107400</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>47800</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>146400</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>161600</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>430900</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>249700</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>222000</v>
       </c>
-      <c r="R20" s="3"/>
-    </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S20" s="3"/>
+    </row>
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>3340100</v>
+      </c>
+      <c r="E21" s="3">
         <v>3059400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>3422000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>4945000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>3747100</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>2551200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>1826900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1833000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>2104500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1817200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>1876300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1973200</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>1876200</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>1442200</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>1371900</v>
       </c>
-      <c r="R21" s="3"/>
-    </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S21" s="3"/>
+    </row>
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
+        <v>48700</v>
+      </c>
+      <c r="E22" s="3">
         <v>51200</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>48100</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>58100</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>67400</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>71300</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>98100</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>90400</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>81100</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>39200</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>15000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>26900</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>23800</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>35800</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>11700</v>
       </c>
-      <c r="R22" s="3"/>
-    </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S22" s="3"/>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>1581000</v>
+      </c>
+      <c r="E23" s="3">
         <v>1715100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>2314500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>3568400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>2110800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>802400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>160700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>69200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>258600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>151900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>437100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>486700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>503800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>212100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>305900</v>
       </c>
-      <c r="R23" s="3"/>
-    </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S23" s="3"/>
+    </row>
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
+        <v>258400</v>
+      </c>
+      <c r="E24" s="3">
         <v>278000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>309200</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>629100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>285700</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>60200</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>7700</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-36900</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>33500</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>30800</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>27900</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>73300</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>79200</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>71400</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>29800</v>
       </c>
-      <c r="R24" s="3"/>
-    </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S24" s="3"/>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -1496,105 +1544,114 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-      <c r="R25" s="3"/>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+      <c r="S25" s="3"/>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>1322700</v>
+      </c>
+      <c r="E26" s="3">
         <v>1437000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>2005300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>2939300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>1825100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>742200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>153000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>106100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>225100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>121100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>409200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>413500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>424600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>140700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>276100</v>
       </c>
-      <c r="R26" s="3"/>
-    </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S26" s="3"/>
+    </row>
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>1328500</v>
+      </c>
+      <c r="E27" s="3">
         <v>1440200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>1990700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>2912600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>1849200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>813800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>272600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>250800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>326200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>260700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>428700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>437300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>443100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>113500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>215400</v>
       </c>
-      <c r="R27" s="3"/>
-    </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S27" s="3"/>
+    </row>
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -1640,9 +1697,12 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-      <c r="R28" s="3"/>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+      <c r="S28" s="3"/>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -1688,9 +1748,12 @@
       <c r="Q29" s="3">
         <v>0</v>
       </c>
-      <c r="R29" s="3"/>
-    </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R29" s="3">
+        <v>0</v>
+      </c>
+      <c r="S29" s="3"/>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>24</v>
       </c>
@@ -1736,9 +1799,12 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-      <c r="R30" s="3"/>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+      <c r="S30" s="3"/>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>25</v>
       </c>
@@ -1784,105 +1850,114 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-      <c r="R31" s="3"/>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+      <c r="S31" s="3"/>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>26</v>
       </c>
       <c r="D32" s="3">
+        <v>134400</v>
+      </c>
+      <c r="E32" s="3">
         <v>89600</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>299300</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>204900</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>188600</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>70100</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>57900</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-48500</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>107400</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-47800</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-146400</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-161600</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-430900</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-249700</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-222000</v>
       </c>
-      <c r="R32" s="3"/>
-    </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S32" s="3"/>
+    </row>
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D33" s="3">
+        <v>1328500</v>
+      </c>
+      <c r="E33" s="3">
         <v>1440200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>1990700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>2912600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>1849200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>813800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>272600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>250800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>326200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>260700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>428700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>437300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>443100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>113500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>215400</v>
       </c>
-      <c r="R33" s="3"/>
-    </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S33" s="3"/>
+    </row>
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>28</v>
       </c>
@@ -1928,110 +2003,119 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-      <c r="R34" s="3"/>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+      <c r="S34" s="3"/>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D35" s="3">
+        <v>1328500</v>
+      </c>
+      <c r="E35" s="3">
         <v>1440200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>1990700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>2912600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>1849200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>813800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>272600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>250800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>326200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>260700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>428700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>437300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>443100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>113500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>215400</v>
       </c>
-      <c r="R35" s="3"/>
-    </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S35" s="3"/>
+    </row>
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44561</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44196</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43830</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43465</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>43100</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42735</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42369</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>42004</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41639</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>41274</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>40908</v>
       </c>
-      <c r="R38" s="2"/>
-    </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S38" s="2"/>
+    </row>
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>31</v>
       </c>
@@ -2050,8 +2134,9 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>32</v>
       </c>
@@ -2070,440 +2155,468 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D41" s="3">
+        <v>3524000</v>
+      </c>
+      <c r="E41" s="3">
         <v>3203200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>4326400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>5658000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>4785600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>3347700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>3192100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>2733200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>2753100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1805100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1698900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1646200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1783100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1565800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>115300</v>
       </c>
-      <c r="R41" s="3"/>
-    </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S41" s="3"/>
+    </row>
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D42" s="3">
+        <v>563800</v>
+      </c>
+      <c r="E42" s="3">
         <v>312300</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>402400</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>155600</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>1381400</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>552500</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>102800</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>17300</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>24200</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>22400</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>21200</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>26700</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>97100</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>1595700</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>1675100</v>
       </c>
-      <c r="R42" s="3"/>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S42" s="3"/>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D43" s="3">
+        <v>1098800</v>
+      </c>
+      <c r="E43" s="3">
         <v>1089200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1082400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1275900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1312400</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1040700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>892500</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>806800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>767700</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>752500</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>637300</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>830700</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>617600</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1142100</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>499600</v>
       </c>
-      <c r="R43" s="3"/>
-    </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S43" s="3"/>
+    </row>
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D44" s="3">
+        <v>1185500</v>
+      </c>
+      <c r="E44" s="3">
         <v>1091600</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1165600</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1011400</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>830300</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>802800</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>725900</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>594700</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>615400</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>532900</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>562400</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>493000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>490900</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>866300</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>414400</v>
       </c>
-      <c r="R44" s="3"/>
-    </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S44" s="3"/>
+    </row>
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D45" s="3">
+        <v>37900</v>
+      </c>
+      <c r="E45" s="3">
         <v>18800</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>28600</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>114100</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>107800</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>22200</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>229000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>94000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>534400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>350400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>103000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>436500</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>126400</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>183000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>36600</v>
       </c>
-      <c r="R45" s="3"/>
-    </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S45" s="3"/>
+    </row>
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D46" s="3">
+        <v>6521300</v>
+      </c>
+      <c r="E46" s="3">
         <v>5786400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>7076100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>8214900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>8417500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>5848600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>5142300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>4612700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>4694900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>3463200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>3022800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>3489000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>3115000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>2661700</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>2741100</v>
       </c>
-      <c r="R46" s="3"/>
-    </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S46" s="3"/>
+    </row>
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D47" s="3">
+        <v>2400200</v>
+      </c>
+      <c r="E47" s="3">
         <v>2211300</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>2423600</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>1831800</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>2129000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>2014000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>1256400</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>1094600</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>1041400</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>1089900</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>1280000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>2227500</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>1056700</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>2310700</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>1301900</v>
       </c>
-      <c r="R47" s="3"/>
-    </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S47" s="3"/>
+    </row>
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D48" s="3">
+        <v>8880700</v>
+      </c>
+      <c r="E48" s="3">
         <v>8758300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>8033300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>5813400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>4946000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>5002100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>5303900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>5646700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>6935300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>7090200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>6017900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>6042500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>11405100</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>10614700</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>4869500</v>
       </c>
-      <c r="R48" s="3"/>
-    </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S48" s="3"/>
+    </row>
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D49" s="3">
+        <v>151000</v>
+      </c>
+      <c r="E49" s="3">
         <v>126700</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>142700</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>139200</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>131500</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>173600</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>173800</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>97700</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>127700</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>128200</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>143600</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>163300</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>332500</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>138200</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>11400</v>
       </c>
-      <c r="R49" s="3"/>
-    </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S49" s="3"/>
+    </row>
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>42</v>
       </c>
@@ -2549,9 +2662,12 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-      <c r="R50" s="3"/>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+      <c r="S50" s="3"/>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>43</v>
       </c>
@@ -2597,57 +2713,63 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-      <c r="R51" s="3"/>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+      <c r="S51" s="3"/>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>44</v>
       </c>
       <c r="D52" s="3">
+        <v>213500</v>
+      </c>
+      <c r="E52" s="3">
         <v>353000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>408600</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>908400</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>450600</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>156600</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>114100</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>250900</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>179200</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>350100</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>291000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>238400</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>262800</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>281300</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>201400</v>
       </c>
-      <c r="R52" s="3"/>
-    </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S52" s="3"/>
+    </row>
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>45</v>
       </c>
@@ -2693,57 +2815,63 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-      <c r="R53" s="3"/>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+      <c r="S53" s="3"/>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>46</v>
       </c>
       <c r="D54" s="3">
+        <v>18438200</v>
+      </c>
+      <c r="E54" s="3">
         <v>17394800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>18251400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>17077800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>16272300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>13438100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>12243400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>11911300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>13184500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>12121600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>10755300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>11283100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>10310500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>9353200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>9125300</v>
       </c>
-      <c r="R54" s="3"/>
-    </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S54" s="3"/>
+    </row>
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>47</v>
       </c>
@@ -2762,8 +2890,9 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>48</v>
       </c>
@@ -2782,296 +2911,315 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>49</v>
       </c>
       <c r="D57" s="3">
+        <v>292000</v>
+      </c>
+      <c r="E57" s="3">
         <v>232900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>245600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>292400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>301800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>279900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>296700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>222200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>220300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>214900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>189800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>222100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>260100</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>416800</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>163400</v>
       </c>
-      <c r="R57" s="3"/>
-    </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S57" s="3"/>
+    </row>
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D58" s="3">
+        <v>898700</v>
+      </c>
+      <c r="E58" s="3">
         <v>614600</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>980800</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>264400</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1436700</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1373700</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>1249600</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>595400</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1780100</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>973500</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>386000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>361100</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>743300</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>975200</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>567900</v>
       </c>
-      <c r="R58" s="3"/>
-    </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S58" s="3"/>
+    </row>
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D59" s="3">
+        <v>1574000</v>
+      </c>
+      <c r="E59" s="3">
         <v>1429500</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1980700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>3082300</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>2147400</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>1112600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>892400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>812600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>993400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1068200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>962300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1149500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>687700</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1274000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>667900</v>
       </c>
-      <c r="R59" s="3"/>
-    </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S59" s="3"/>
+    </row>
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D60" s="3">
+        <v>2789600</v>
+      </c>
+      <c r="E60" s="3">
         <v>2295900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>3231800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>3665500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>3906100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>2785200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>2438800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1630200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>2993800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>2256500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1538100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1732800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>1691000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>1334400</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>1399200</v>
       </c>
-      <c r="R60" s="3"/>
-    </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S60" s="3"/>
+    </row>
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D61" s="3">
+        <v>1616100</v>
+      </c>
+      <c r="E61" s="3">
         <v>1870500</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1635700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1467300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1600000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1060700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1783400</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>2191500</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1797300</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1903800</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>1515100</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1203100</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>996800</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>1069500</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>687900</v>
       </c>
-      <c r="R61" s="3"/>
-    </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S61" s="3"/>
+    </row>
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D62" s="3">
+        <v>1297200</v>
+      </c>
+      <c r="E62" s="3">
         <v>1302100</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>1330100</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>1148500</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>819100</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>750400</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>686700</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>696000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>712500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>1103700</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>407400</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>242400</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>268400</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>365900</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>120800</v>
       </c>
-      <c r="R62" s="3"/>
-    </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S62" s="3"/>
+    </row>
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>55</v>
       </c>
@@ -3117,9 +3265,12 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-      <c r="R63" s="3"/>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+      <c r="S63" s="3"/>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -3165,9 +3316,12 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-      <c r="R64" s="3"/>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+      <c r="S64" s="3"/>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>56</v>
       </c>
@@ -3213,57 +3367,63 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-      <c r="R65" s="3"/>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+      <c r="S65" s="3"/>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>57</v>
       </c>
       <c r="D66" s="3">
+        <v>6341700</v>
+      </c>
+      <c r="E66" s="3">
         <v>5857700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>6515100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>6569900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>6732600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>5045500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>5460400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>5163900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>6118500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>5331900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>3525200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>3317000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>3107700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>2730600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>2351000</v>
       </c>
-      <c r="R66" s="3"/>
-    </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S66" s="3"/>
+    </row>
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>58</v>
       </c>
@@ -3282,8 +3442,9 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>59</v>
       </c>
@@ -3329,9 +3490,12 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-      <c r="R68" s="3"/>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+      <c r="S68" s="3"/>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>60</v>
       </c>
@@ -3377,9 +3541,12 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-      <c r="R69" s="3"/>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+      <c r="S69" s="3"/>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>61</v>
       </c>
@@ -3425,9 +3592,12 @@
       <c r="Q70" s="3">
         <v>0</v>
       </c>
-      <c r="R70" s="3"/>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+      <c r="S70" s="3"/>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>62</v>
       </c>
@@ -3473,57 +3643,63 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-      <c r="R71" s="3"/>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+      <c r="S71" s="3"/>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>63</v>
       </c>
       <c r="D72" s="3">
+        <v>7416200</v>
+      </c>
+      <c r="E72" s="3">
         <v>6920300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>7084400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>6386700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>3863000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>2854000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>2138100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>2012000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>1788500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>1494000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>1616600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>1597100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>1343700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>1872000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>798900</v>
       </c>
-      <c r="R72" s="3"/>
-    </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S72" s="3"/>
+    </row>
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>64</v>
       </c>
@@ -3569,9 +3745,12 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-      <c r="R73" s="3"/>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+      <c r="S73" s="3"/>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>65</v>
       </c>
@@ -3617,9 +3796,12 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-      <c r="R74" s="3"/>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+      <c r="S74" s="3"/>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>66</v>
       </c>
@@ -3665,57 +3847,63 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-      <c r="R75" s="3"/>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+      <c r="S75" s="3"/>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>67</v>
       </c>
       <c r="D76" s="3">
+        <v>12093800</v>
+      </c>
+      <c r="E76" s="3">
         <v>11529200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>11725200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>10496600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>9531700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>8388600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>6769300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>6732100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>7033800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>6789800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>7230100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>7966100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>7202800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>6622600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>6774300</v>
       </c>
-      <c r="R76" s="3"/>
-    </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S76" s="3"/>
+    </row>
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>68</v>
       </c>
@@ -3761,110 +3949,119 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-      <c r="R77" s="3"/>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+      <c r="S77" s="3"/>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44561</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44196</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43830</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43465</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>43100</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42735</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42369</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>42004</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41639</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>41274</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>40908</v>
       </c>
-      <c r="R80" s="2"/>
-    </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S80" s="2"/>
+    </row>
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D81" s="3">
+        <v>1328500</v>
+      </c>
+      <c r="E81" s="3">
         <v>1440200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>1990700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>2912600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>1849200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>813800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>272600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>250800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>326200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>260700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>428700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>437300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>443100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>113500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>215400</v>
       </c>
-      <c r="R81" s="3"/>
-    </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S81" s="3"/>
+    </row>
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>70</v>
       </c>
@@ -3883,56 +4080,60 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>71</v>
       </c>
       <c r="D83" s="3">
+        <v>1796900</v>
+      </c>
+      <c r="E83" s="3">
         <v>1387200</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>1232400</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>1345300</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>1594200</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>1643200</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>1576900</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>1631800</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>1718000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>1629700</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>1449700</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>1464500</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>1348200</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>1192100</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>1055600</v>
       </c>
-      <c r="R83" s="3"/>
-    </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S83" s="3"/>
+    </row>
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>72</v>
       </c>
@@ -3978,9 +4179,12 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-      <c r="R84" s="3"/>
-    </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+      <c r="S84" s="3"/>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>73</v>
       </c>
@@ -4026,9 +4230,12 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-      <c r="R85" s="3"/>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+      <c r="S85" s="3"/>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>74</v>
       </c>
@@ -4074,9 +4281,12 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-      <c r="R86" s="3"/>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+      <c r="S86" s="3"/>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>75</v>
       </c>
@@ -4122,9 +4332,12 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-      <c r="R87" s="3"/>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+      <c r="S87" s="3"/>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>76</v>
       </c>
@@ -4170,57 +4383,63 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-      <c r="R88" s="3"/>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+      <c r="S88" s="3"/>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>77</v>
       </c>
       <c r="D89" s="3">
+        <v>3180200</v>
+      </c>
+      <c r="E89" s="3">
         <v>2863700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>2807000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>4747900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>3260300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>2340300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>1835300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>1664000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1768800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>1456200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>1906000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>1613300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>1525000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>1343600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>1358300</v>
       </c>
-      <c r="R89" s="3"/>
-    </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S89" s="3"/>
+    </row>
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>78</v>
       </c>
@@ -4239,56 +4458,60 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>79</v>
       </c>
       <c r="D91" s="3">
+        <v>-1520400</v>
+      </c>
+      <c r="E91" s="3">
         <v>-2701100</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-2985600</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-2608200</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-1733300</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-937800</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-552200</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-640000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-1491100</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-2870400</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-1928900</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-1557400</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-1154500</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-1754100</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-1751400</v>
       </c>
-      <c r="R91" s="3"/>
-    </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S91" s="3"/>
+    </row>
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>80</v>
       </c>
@@ -4334,9 +4557,12 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-      <c r="R92" s="3"/>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+      <c r="S92" s="3"/>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>81</v>
       </c>
@@ -4382,57 +4608,63 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-      <c r="R93" s="3"/>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+      <c r="S93" s="3"/>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>82</v>
       </c>
       <c r="D94" s="3">
+        <v>-1692700</v>
+      </c>
+      <c r="E94" s="3">
         <v>-2621800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-3191700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1771700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-2243100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-1427800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-1059100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-506400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1193800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-2510700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-2183200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-1534700</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-1105600</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-1633800</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-1797500</v>
       </c>
-      <c r="R94" s="3"/>
-    </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S94" s="3"/>
+    </row>
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>83</v>
       </c>
@@ -4451,56 +4683,60 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>84</v>
       </c>
       <c r="D96" s="3">
+        <v>1139600</v>
+      </c>
+      <c r="E96" s="3">
         <v>1146600</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>1469200</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>1218900</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>717000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>347600</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>231000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>279600</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>205700</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-216500</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-221200</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-225200</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-177600</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-210100</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-457100</v>
       </c>
-      <c r="R96" s="3"/>
-    </row>
-    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S96" s="3"/>
+    </row>
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>85</v>
       </c>
@@ -4546,9 +4782,12 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-      <c r="R97" s="3"/>
-    </row>
-    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+      <c r="S97" s="3"/>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>86</v>
       </c>
@@ -4594,9 +4833,12 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-      <c r="R98" s="3"/>
-    </row>
-    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+      <c r="S98" s="3"/>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>87</v>
       </c>
@@ -4642,151 +4884,163 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-      <c r="R99" s="3"/>
-    </row>
-    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+      <c r="S99" s="3"/>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>88</v>
       </c>
       <c r="D100" s="3">
+        <v>-1248500</v>
+      </c>
+      <c r="E100" s="3">
         <v>-1195800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-949300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-1863700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>450700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-911300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-329800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-1093900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>308800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>1216200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>479800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-297400</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-137700</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>119300</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>323600</v>
       </c>
-      <c r="R100" s="3"/>
-    </row>
-    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S100" s="3"/>
+    </row>
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D101" s="3">
+        <v>-58800</v>
+      </c>
+      <c r="E101" s="3">
         <v>113300</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-12800</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>228400</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-75900</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-52600</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-51000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>1200</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-71600</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-27300</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>23000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>52500</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>10900</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-47800</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>43800</v>
       </c>
-      <c r="R101" s="3"/>
-    </row>
-    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S101" s="3"/>
+    </row>
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D102" s="3">
+        <v>180200</v>
+      </c>
+      <c r="E102" s="3">
         <v>-840600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-1346900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>1341000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>1391900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-51400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>395500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>64900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>812200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>134400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>225600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-166300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>292600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-218600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-71800</v>
       </c>
-      <c r="R102" s="3"/>
+      <c r="S102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/UMC_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/UMC_YR_FIN.xlsx
@@ -1005,13 +1005,13 @@
         <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>-26400</v>
+        <v>-3900</v>
       </c>
       <c r="E14" s="3">
-        <v>7600</v>
+        <v>-2200</v>
       </c>
       <c r="F14" s="3">
-        <v>-24200</v>
+        <v>-25500</v>
       </c>
       <c r="G14" s="3">
         <v>23300</v>
@@ -1248,13 +1248,13 @@
         <v>14</v>
       </c>
       <c r="D20" s="3">
-        <v>-134400</v>
+        <v>-156900</v>
       </c>
       <c r="E20" s="3">
-        <v>-89600</v>
+        <v>-79800</v>
       </c>
       <c r="F20" s="3">
-        <v>-299300</v>
+        <v>-297900</v>
       </c>
       <c r="G20" s="3">
         <v>-204900</v>
@@ -1299,13 +1299,13 @@
         <v>15</v>
       </c>
       <c r="D21" s="3">
-        <v>3340100</v>
+        <v>3362600</v>
       </c>
       <c r="E21" s="3">
-        <v>3059400</v>
+        <v>3049700</v>
       </c>
       <c r="F21" s="3">
-        <v>3422000</v>
+        <v>3420700</v>
       </c>
       <c r="G21" s="3">
         <v>4945000</v>
@@ -1860,13 +1860,13 @@
         <v>26</v>
       </c>
       <c r="D32" s="3">
-        <v>134400</v>
+        <v>156900</v>
       </c>
       <c r="E32" s="3">
-        <v>89600</v>
+        <v>79800</v>
       </c>
       <c r="F32" s="3">
-        <v>299300</v>
+        <v>297900</v>
       </c>
       <c r="G32" s="3">
         <v>204900</v>
